--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1E0EAD2-8DB5-425D-A23F-BD0F99137BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7379B17E-867F-4EBC-A110-47B53CC5822D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="376">
   <si>
     <t>order</t>
   </si>
@@ -1262,6 +1262,33 @@
   <dxfs count="26">
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1357,111 +1384,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1509,6 +1431,44 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="Segoe UI"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -1654,6 +1614,46 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1668,35 +1668,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:W71" headerRowDxfId="7" dataDxfId="8" totalsRowDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:W71" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="18">
       <calculatedColumnFormula>IF(D2="","",LEFT(TRIM(D2),1)&amp;".")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="19">
+    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="16">
       <calculatedColumnFormula>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="0"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
     <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1863,13 +1863,14 @@
     <col min="7" max="7" width="30.3984375" style="4" customWidth="1"/>
     <col min="8" max="8" width="23.5" style="4" customWidth="1"/>
     <col min="9" max="9" width="25.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="28" style="4" customWidth="1"/>
-    <col min="13" max="13" width="22.09765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31" style="4" customWidth="1"/>
+    <col min="11" max="12" width="28" style="4" customWidth="1"/>
+    <col min="13" max="13" width="32.8984375" style="4" customWidth="1"/>
     <col min="14" max="14" width="26.69921875" style="4" customWidth="1"/>
     <col min="15" max="15" width="20.09765625" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="45.19921875" style="7" customWidth="1"/>
     <col min="17" max="21" width="24.19921875" style="7" customWidth="1"/>
-    <col min="22" max="22" width="33.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="36.69921875" style="4" customWidth="1"/>
     <col min="23" max="23" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="8.796875" style="4"/>
   </cols>
@@ -2036,7 +2037,9 @@
         <v>17</v>
       </c>
       <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
+      <c r="Q3" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
@@ -2136,7 +2139,9 @@
         <v>17</v>
       </c>
       <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
+      <c r="Q5" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
@@ -2186,7 +2191,9 @@
         <v>14</v>
       </c>
       <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
+      <c r="Q6" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
@@ -2236,7 +2243,9 @@
         <v>14</v>
       </c>
       <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -2388,7 +2397,9 @@
         <v>14</v>
       </c>
       <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
@@ -2438,7 +2449,9 @@
         <v>17</v>
       </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
@@ -2488,7 +2501,9 @@
         <v>17</v>
       </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -2588,7 +2603,9 @@
         <v>17</v>
       </c>
       <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -2638,7 +2655,9 @@
         <v>14</v>
       </c>
       <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
+      <c r="Q15" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -2686,7 +2705,9 @@
         <v>17</v>
       </c>
       <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
+      <c r="Q16" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -2836,7 +2857,9 @@
         <v>14</v>
       </c>
       <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
@@ -2938,7 +2961,9 @@
         <v>17</v>
       </c>
       <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
       <c r="T21" s="6"/>
@@ -2988,7 +3013,9 @@
         <v>17</v>
       </c>
       <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
+      <c r="Q22" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
@@ -3038,7 +3065,9 @@
         <v>7</v>
       </c>
       <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
+      <c r="Q23" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
@@ -3088,7 +3117,9 @@
         <v>17</v>
       </c>
       <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
+      <c r="Q24" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
@@ -3138,7 +3169,9 @@
         <v>17</v>
       </c>
       <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
+      <c r="Q25" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
@@ -3188,7 +3221,9 @@
         <v>17</v>
       </c>
       <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
+      <c r="Q26" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
       <c r="T26" s="6"/>
@@ -3236,7 +3271,9 @@
         <v>17</v>
       </c>
       <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
+      <c r="Q27" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R27" s="6"/>
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
@@ -3286,7 +3323,9 @@
         <v>17</v>
       </c>
       <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
+      <c r="Q28" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R28" s="6"/>
       <c r="S28" s="6"/>
       <c r="T28" s="6"/>
@@ -3338,7 +3377,9 @@
         <v>14</v>
       </c>
       <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
+      <c r="Q29" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R29" s="6"/>
       <c r="S29" s="6"/>
       <c r="T29" s="6"/>
@@ -3388,7 +3429,9 @@
         <v>17</v>
       </c>
       <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
+      <c r="Q30" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R30" s="6"/>
       <c r="S30" s="6"/>
       <c r="T30" s="6"/>
@@ -3438,7 +3481,9 @@
         <v>17</v>
       </c>
       <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
+      <c r="Q31" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R31" s="6"/>
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
@@ -3488,7 +3533,9 @@
         <v>14</v>
       </c>
       <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
+      <c r="Q32" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
       <c r="T32" s="6"/>
@@ -3538,7 +3585,9 @@
         <v>17</v>
       </c>
       <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
+      <c r="Q33" s="6" t="s">
+        <v>370</v>
+      </c>
       <c r="R33" s="6"/>
       <c r="S33" s="6"/>
       <c r="T33" s="6"/>
@@ -3588,7 +3637,9 @@
         <v>17</v>
       </c>
       <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
+      <c r="Q34" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
       <c r="T34" s="6"/>
@@ -3638,7 +3689,9 @@
         <v>17</v>
       </c>
       <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
+      <c r="Q35" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R35" s="6"/>
       <c r="S35" s="6"/>
       <c r="T35" s="6"/>
@@ -3688,7 +3741,9 @@
         <v>17</v>
       </c>
       <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
+      <c r="Q36" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
       <c r="T36" s="6"/>
@@ -3738,7 +3793,9 @@
         <v>17</v>
       </c>
       <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
+      <c r="Q37" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R37" s="6"/>
       <c r="S37" s="6"/>
       <c r="T37" s="6"/>
@@ -3788,7 +3845,9 @@
         <v>17</v>
       </c>
       <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
+      <c r="Q38" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R38" s="6"/>
       <c r="S38" s="6"/>
       <c r="T38" s="6"/>
@@ -3838,7 +3897,9 @@
         <v>17</v>
       </c>
       <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
+      <c r="Q39" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
@@ -3888,7 +3949,9 @@
         <v>17</v>
       </c>
       <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
+      <c r="Q40" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
       <c r="T40" s="6"/>
@@ -3938,7 +4001,9 @@
         <v>17</v>
       </c>
       <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
+      <c r="Q41" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R41" s="6"/>
       <c r="S41" s="6"/>
       <c r="T41" s="6"/>
@@ -3986,7 +4051,9 @@
         <v>17</v>
       </c>
       <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
+      <c r="Q42" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
@@ -4036,7 +4103,9 @@
         <v>14</v>
       </c>
       <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
+      <c r="Q43" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R43" s="6"/>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -4049,7 +4118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="33.6">
+    <row r="44" spans="1:23">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -4072,7 +4141,7 @@
         <v>Richie Ryan C. Mabunay</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>291</v>
@@ -4094,7 +4163,9 @@
       <c r="P44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q44" s="6"/>
+      <c r="Q44" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
       <c r="T44" s="6"/>
@@ -4144,7 +4215,9 @@
         <v>17</v>
       </c>
       <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
+      <c r="Q45" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="6"/>
@@ -4194,7 +4267,9 @@
         <v>17</v>
       </c>
       <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
+      <c r="Q46" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
@@ -4244,7 +4319,9 @@
         <v>17</v>
       </c>
       <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
+      <c r="Q47" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R47" s="6"/>
       <c r="S47" s="6"/>
       <c r="T47" s="6"/>
@@ -4294,7 +4371,9 @@
         <v>17</v>
       </c>
       <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
+      <c r="Q48" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
@@ -4344,7 +4423,9 @@
         <v>17</v>
       </c>
       <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
+      <c r="Q49" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
       <c r="T49" s="6"/>
@@ -4394,7 +4475,9 @@
         <v>17</v>
       </c>
       <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
+      <c r="Q50" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
       <c r="T50" s="6"/>
@@ -4444,7 +4527,9 @@
         <v>17</v>
       </c>
       <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
+      <c r="Q51" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
       <c r="T51" s="6"/>
@@ -4494,7 +4579,9 @@
         <v>14</v>
       </c>
       <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
+      <c r="Q52" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
@@ -4544,7 +4631,9 @@
         <v>17</v>
       </c>
       <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
+      <c r="Q53" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R53" s="6"/>
       <c r="S53" s="6"/>
       <c r="T53" s="6"/>
@@ -4594,7 +4683,9 @@
         <v>17</v>
       </c>
       <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
+      <c r="Q54" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
       <c r="T54" s="6"/>
@@ -4644,7 +4735,9 @@
         <v>17</v>
       </c>
       <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
+      <c r="Q55" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R55" s="6"/>
       <c r="S55" s="6"/>
       <c r="T55" s="6"/>
@@ -4694,7 +4787,9 @@
         <v>17</v>
       </c>
       <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
+      <c r="Q56" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
       <c r="T56" s="6"/>
@@ -4744,7 +4839,9 @@
         <v>17</v>
       </c>
       <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
+      <c r="Q57" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R57" s="6"/>
       <c r="S57" s="6"/>
       <c r="T57" s="6"/>
@@ -4794,7 +4891,9 @@
         <v>17</v>
       </c>
       <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
+      <c r="Q58" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
       <c r="T58" s="6"/>
@@ -4844,7 +4943,9 @@
         <v>17</v>
       </c>
       <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
+      <c r="Q59" s="6" t="s">
+        <v>370</v>
+      </c>
       <c r="R59" s="6"/>
       <c r="S59" s="6"/>
       <c r="T59" s="6"/>
@@ -4894,7 +4995,9 @@
         <v>17</v>
       </c>
       <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
+      <c r="Q60" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
       <c r="T60" s="6"/>
@@ -4944,7 +5047,9 @@
         <v>17</v>
       </c>
       <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
+      <c r="Q61" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R61" s="6"/>
       <c r="S61" s="6"/>
       <c r="T61" s="6"/>
@@ -4957,7 +5062,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="33.6">
+    <row r="62" spans="1:23">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -4994,13 +5099,15 @@
         <v>17</v>
       </c>
       <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
+      <c r="Q62" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
       <c r="T62" s="6"/>
       <c r="U62" s="6"/>
       <c r="V62" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C62&amp;" "&amp;B62)," ","-"))&amp;".jpg"</f>
         <v>/personnel/bella-arquine-samontañez.jpg</v>
       </c>
       <c r="W62" s="6" t="s">
@@ -5044,7 +5151,9 @@
         <v>14</v>
       </c>
       <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
+      <c r="Q63" s="6" t="s">
+        <v>371</v>
+      </c>
       <c r="R63" s="6"/>
       <c r="S63" s="6"/>
       <c r="T63" s="6"/>
@@ -5094,7 +5203,9 @@
         <v>17</v>
       </c>
       <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
+      <c r="Q64" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="R64" s="6"/>
       <c r="S64" s="6"/>
       <c r="T64" s="6"/>
@@ -5146,7 +5257,9 @@
         <v>7</v>
       </c>
       <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
+      <c r="Q65" s="6" t="s">
+        <v>274</v>
+      </c>
       <c r="R65" s="6"/>
       <c r="S65" s="6"/>
       <c r="T65" s="6"/>
@@ -5196,7 +5309,9 @@
         <v>14</v>
       </c>
       <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
+      <c r="Q66" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
@@ -5246,7 +5361,9 @@
         <v>374</v>
       </c>
       <c r="P67" s="6"/>
-      <c r="Q67" s="6"/>
+      <c r="Q67" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="R67" s="6"/>
       <c r="S67" s="6"/>
       <c r="T67" s="6"/>
@@ -5259,7 +5376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="33.6">
+    <row r="68" spans="1:23">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -5296,7 +5413,9 @@
         <v>374</v>
       </c>
       <c r="P68" s="6"/>
-      <c r="Q68" s="6"/>
+      <c r="Q68" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="R68" s="6"/>
       <c r="S68" s="6"/>
       <c r="T68" s="6"/>
@@ -5346,7 +5465,9 @@
         <v>374</v>
       </c>
       <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
+      <c r="Q69" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="R69" s="6"/>
       <c r="S69" s="6"/>
       <c r="T69" s="6"/>
@@ -5396,7 +5517,9 @@
         <v>374</v>
       </c>
       <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
+      <c r="Q70" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
       <c r="T70" s="6"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7379B17E-867F-4EBC-A110-47B53CC5822D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C7BDA-DA1C-4B71-ABE9-1240B01A5A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="393">
   <si>
     <t>order</t>
   </si>
@@ -850,15 +850,6 @@
     <t>SHS-Teacher I</t>
   </si>
   <si>
-    <t>Lastname</t>
-  </si>
-  <si>
-    <t>MiddleName</t>
-  </si>
-  <si>
-    <t>Firstname</t>
-  </si>
-  <si>
     <t>School Head</t>
   </si>
   <si>
@@ -1163,6 +1154,66 @@
   </si>
   <si>
     <t>Job Order/Support Personnel</t>
+  </si>
+  <si>
+    <t>Cabs</t>
+  </si>
+  <si>
+    <t>Mans</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Luie</t>
+  </si>
+  <si>
+    <t>Senior High School In-Charge</t>
+  </si>
+  <si>
+    <t>Junior High School In-Charge</t>
+  </si>
+  <si>
+    <t>BSP Coordinator</t>
+  </si>
+  <si>
+    <t>SDRRM Coordinator</t>
+  </si>
+  <si>
+    <t>LIS/ICT/EBEIS Coordinator</t>
+  </si>
+  <si>
+    <t>SSLG Coordinator</t>
+  </si>
+  <si>
+    <t>GSP oordinator</t>
+  </si>
+  <si>
+    <t>Canteen Coordinator</t>
+  </si>
+  <si>
+    <t>Health Aid Coordinator</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>ICT/Progamming</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>EPP</t>
+  </si>
+  <si>
+    <t>Electronic Product Assembly and Servicing</t>
+  </si>
+  <si>
+    <t>Hairdressing/Beauty Care</t>
+  </si>
+  <si>
+    <t>Computer Systems Servicing / Filipino</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1255,11 +1306,61 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1487,47 +1588,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1681,22 +1741,22 @@
     <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="16">
       <calculatedColumnFormula>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="1"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="9"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1862,7 +1922,7 @@
     <col min="6" max="6" width="5.796875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.3984375" style="4" customWidth="1"/>
     <col min="8" max="8" width="23.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="25.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.69921875" style="11" customWidth="1"/>
     <col min="10" max="10" width="31" style="4" customWidth="1"/>
     <col min="11" max="12" width="28" style="4" customWidth="1"/>
     <col min="13" max="13" width="32.8984375" style="4" customWidth="1"/>
@@ -1901,19 +1961,19 @@
         <v>1</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>2</v>
@@ -1925,19 +1985,19 @@
         <v>4</v>
       </c>
       <c r="Q1" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="U1" s="8" t="s">
         <v>363</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>366</v>
       </c>
       <c r="V1" s="8" t="s">
         <v>5</v>
@@ -1971,8 +2031,8 @@
       <c r="H2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>330</v>
+      <c r="I2" s="9" t="s">
+        <v>327</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
@@ -1985,7 +2045,7 @@
         <v>11</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
@@ -2025,7 +2085,9 @@
       <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -2036,9 +2098,11 @@
       <c r="O3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="6"/>
+      <c r="P3" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q3" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
@@ -2077,7 +2141,7 @@
       <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="10"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -2088,7 +2152,9 @@
       <c r="O4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
@@ -2127,7 +2193,9 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -2138,9 +2206,11 @@
       <c r="O5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="6"/>
+      <c r="P5" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q5" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
@@ -2179,7 +2249,9 @@
       <c r="H6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -2190,9 +2262,11 @@
       <c r="O6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="6"/>
+      <c r="P6" s="6" t="s">
+        <v>387</v>
+      </c>
       <c r="Q6" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
@@ -2231,7 +2305,9 @@
       <c r="H7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -2242,9 +2318,11 @@
       <c r="O7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="6"/>
+      <c r="P7" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="Q7" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
@@ -2283,9 +2361,7 @@
       <c r="H8" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>307</v>
-      </c>
+      <c r="I8" s="10"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -2296,7 +2372,9 @@
       <c r="O8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="6"/>
+      <c r="P8" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
@@ -2335,7 +2413,7 @@
       <c r="H9" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="10"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -2346,7 +2424,9 @@
       <c r="O9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="6"/>
+      <c r="P9" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
@@ -2385,7 +2465,9 @@
       <c r="H10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -2396,9 +2478,11 @@
       <c r="O10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="6"/>
+      <c r="P10" s="6" t="s">
+        <v>389</v>
+      </c>
       <c r="Q10" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
@@ -2437,7 +2521,9 @@
       <c r="H11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -2450,7 +2536,7 @@
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
@@ -2489,8 +2575,12 @@
       <c r="H12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="I12" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>379</v>
+      </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
@@ -2502,7 +2592,7 @@
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
@@ -2541,7 +2631,7 @@
       <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="10"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -2552,7 +2642,9 @@
       <c r="O13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="6"/>
+      <c r="P13" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
@@ -2591,7 +2683,9 @@
       <c r="H14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -2602,9 +2696,11 @@
       <c r="O14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="6"/>
+      <c r="P14" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q14" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
@@ -2641,9 +2737,11 @@
         <v>Maine L. Bongas</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I15" s="5"/>
+        <v>252</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>331</v>
+      </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -2654,9 +2752,11 @@
       <c r="O15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P15" s="6"/>
+      <c r="P15" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q15" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
@@ -2693,7 +2793,9 @@
       <c r="H16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -2706,7 +2808,7 @@
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
@@ -2745,7 +2847,7 @@
       <c r="H17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="10"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
@@ -2795,7 +2897,9 @@
       <c r="H18" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="I18" s="5"/>
+      <c r="I18" s="10" t="s">
+        <v>377</v>
+      </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -2806,7 +2910,9 @@
       <c r="O18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="6"/>
+      <c r="P18" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
@@ -2843,9 +2949,11 @@
         <v>Gracelyn M. Cabunag</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="5"/>
+        <v>249</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>385</v>
+      </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
@@ -2856,9 +2964,11 @@
       <c r="O19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="6"/>
+      <c r="P19" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="Q19" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -2897,8 +3007,8 @@
       <c r="H20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>331</v>
+      <c r="I20" s="10" t="s">
+        <v>328</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -2910,7 +3020,9 @@
       <c r="O20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P20" s="6"/>
+      <c r="P20" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -2949,7 +3061,9 @@
       <c r="H21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -2960,9 +3074,11 @@
       <c r="O21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="6"/>
+      <c r="P21" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q21" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -3001,7 +3117,9 @@
       <c r="H22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -3014,7 +3132,7 @@
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
@@ -3053,7 +3171,9 @@
       <c r="H23" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="10" t="s">
+        <v>364</v>
+      </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -3064,9 +3184,11 @@
       <c r="O23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P23" s="6"/>
+      <c r="P23" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q23" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
@@ -3105,7 +3227,9 @@
       <c r="H24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -3116,9 +3240,11 @@
       <c r="O24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P24" s="6"/>
+      <c r="P24" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="Q24" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
@@ -3157,7 +3283,9 @@
       <c r="H25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -3168,9 +3296,11 @@
       <c r="O25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="6"/>
+      <c r="P25" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="Q25" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
@@ -3209,7 +3339,9 @@
       <c r="H26" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="I26" s="5"/>
+      <c r="I26" s="10" t="s">
+        <v>378</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -3220,9 +3352,11 @@
       <c r="O26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P26" s="6"/>
+      <c r="P26" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q26" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
@@ -3259,7 +3393,9 @@
       <c r="H27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
@@ -3270,9 +3406,11 @@
       <c r="O27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P27" s="6"/>
+      <c r="P27" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q27" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R27" s="6"/>
       <c r="S27" s="6"/>
@@ -3311,7 +3449,9 @@
       <c r="H28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I28" s="5"/>
+      <c r="I28" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -3322,9 +3462,11 @@
       <c r="O28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P28" s="6"/>
+      <c r="P28" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="Q28" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R28" s="6"/>
       <c r="S28" s="6"/>
@@ -3363,9 +3505,11 @@
         <v>Joseph C. Dagaraga Jr.</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="5"/>
+        <v>270</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
@@ -3376,9 +3520,11 @@
       <c r="O29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P29" s="6"/>
+      <c r="P29" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q29" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R29" s="6"/>
       <c r="S29" s="6"/>
@@ -3417,7 +3563,9 @@
       <c r="H30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="5"/>
+      <c r="I30" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
@@ -3428,9 +3576,11 @@
       <c r="O30" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P30" s="6"/>
+      <c r="P30" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="Q30" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R30" s="6"/>
       <c r="S30" s="6"/>
@@ -3467,9 +3617,11 @@
         <v>Lucille R. Echavez</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
@@ -3480,9 +3632,11 @@
       <c r="O31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P31" s="6"/>
+      <c r="P31" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q31" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R31" s="6"/>
       <c r="S31" s="6"/>
@@ -3519,9 +3673,11 @@
         <v>Benerando C. Erediano</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" s="5"/>
+        <v>270</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>279</v>
+      </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
@@ -3532,9 +3688,11 @@
       <c r="O32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P32" s="6"/>
+      <c r="P32" s="6" t="s">
+        <v>390</v>
+      </c>
       <c r="Q32" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
@@ -3573,7 +3731,9 @@
       <c r="H33" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="10" t="s">
+        <v>367</v>
+      </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
@@ -3584,9 +3744,11 @@
       <c r="O33" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P33" s="6"/>
+      <c r="P33" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="Q33" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="R33" s="6"/>
       <c r="S33" s="6"/>
@@ -3625,7 +3787,9 @@
       <c r="H34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="10" t="s">
+        <v>384</v>
+      </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
@@ -3636,9 +3800,11 @@
       <c r="O34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P34" s="6"/>
+      <c r="P34" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="Q34" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
@@ -3677,7 +3843,9 @@
       <c r="H35" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
@@ -3688,9 +3856,11 @@
       <c r="O35" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P35" s="6"/>
+      <c r="P35" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="Q35" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R35" s="6"/>
       <c r="S35" s="6"/>
@@ -3729,7 +3899,9 @@
       <c r="H36" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
@@ -3740,9 +3912,11 @@
       <c r="O36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P36" s="6"/>
+      <c r="P36" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="Q36" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
@@ -3781,7 +3955,9 @@
       <c r="H37" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
@@ -3792,9 +3968,11 @@
       <c r="O37" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P37" s="6"/>
+      <c r="P37" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="Q37" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R37" s="6"/>
       <c r="S37" s="6"/>
@@ -3833,7 +4011,9 @@
       <c r="H38" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I38" s="5"/>
+      <c r="I38" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
@@ -3844,9 +4024,11 @@
       <c r="O38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P38" s="6"/>
+      <c r="P38" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="Q38" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R38" s="6"/>
       <c r="S38" s="6"/>
@@ -3885,7 +4067,9 @@
       <c r="H39" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -3896,9 +4080,11 @@
       <c r="O39" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P39" s="6"/>
+      <c r="P39" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="Q39" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
@@ -3937,7 +4123,9 @@
       <c r="H40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I40" s="5"/>
+      <c r="I40" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
@@ -3950,7 +4138,7 @@
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
@@ -3989,7 +4177,9 @@
       <c r="H41" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I41" s="5"/>
+      <c r="I41" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
@@ -4000,9 +4190,11 @@
       <c r="O41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P41" s="6"/>
+      <c r="P41" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="Q41" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R41" s="6"/>
       <c r="S41" s="6"/>
@@ -4039,7 +4231,9 @@
       <c r="H42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I42" s="5"/>
+      <c r="I42" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
@@ -4052,7 +4246,7 @@
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
@@ -4089,9 +4283,11 @@
         <v>Lyka M. Mabanag</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I43" s="5"/>
+        <v>270</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>383</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
@@ -4104,7 +4300,7 @@
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R43" s="6"/>
       <c r="S43" s="6"/>
@@ -4143,16 +4339,16 @@
       <c r="H44" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>291</v>
+      <c r="I44" s="10" t="s">
+        <v>380</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>13</v>
@@ -4164,7 +4360,7 @@
         <v>15</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
@@ -4201,9 +4397,11 @@
         <v>Maria Jeziel H. Macanin</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I45" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
@@ -4214,9 +4412,11 @@
       <c r="O45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P45" s="6"/>
+      <c r="P45" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="Q45" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
@@ -4255,7 +4455,9 @@
       <c r="H46" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I46" s="5"/>
+      <c r="I46" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
@@ -4266,9 +4468,11 @@
       <c r="O46" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P46" s="6"/>
+      <c r="P46" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="Q46" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
@@ -4307,7 +4511,9 @@
       <c r="H47" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I47" s="5"/>
+      <c r="I47" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
@@ -4318,9 +4524,11 @@
       <c r="O47" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="6"/>
+      <c r="P47" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="Q47" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R47" s="6"/>
       <c r="S47" s="6"/>
@@ -4359,7 +4567,9 @@
       <c r="H48" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="I48" s="5"/>
+      <c r="I48" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
@@ -4372,7 +4582,7 @@
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
@@ -4411,7 +4621,9 @@
       <c r="H49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I49" s="5"/>
+      <c r="I49" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
@@ -4424,7 +4636,7 @@
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
@@ -4463,7 +4675,9 @@
       <c r="H50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I50" s="5"/>
+      <c r="I50" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
@@ -4474,9 +4688,11 @@
       <c r="O50" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P50" s="6"/>
+      <c r="P50" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="Q50" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
@@ -4515,7 +4731,9 @@
       <c r="H51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I51" s="5"/>
+      <c r="I51" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
@@ -4528,7 +4746,7 @@
       </c>
       <c r="P51" s="6"/>
       <c r="Q51" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
@@ -4567,7 +4785,9 @@
       <c r="H52" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I52" s="5"/>
+      <c r="I52" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
@@ -4578,9 +4798,11 @@
       <c r="O52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P52" s="6"/>
+      <c r="P52" s="6" t="s">
+        <v>391</v>
+      </c>
       <c r="Q52" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
@@ -4617,9 +4839,11 @@
         <v>Marissa J. Pintuan</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I53" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
@@ -4630,9 +4854,11 @@
       <c r="O53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P53" s="6"/>
+      <c r="P53" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q53" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R53" s="6"/>
       <c r="S53" s="6"/>
@@ -4671,7 +4897,9 @@
       <c r="H54" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I54" s="5"/>
+      <c r="I54" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
@@ -4682,9 +4910,11 @@
       <c r="O54" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P54" s="6"/>
+      <c r="P54" s="6" t="s">
+        <v>389</v>
+      </c>
       <c r="Q54" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
@@ -4723,7 +4953,9 @@
       <c r="H55" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I55" s="5"/>
+      <c r="I55" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
@@ -4736,7 +4968,7 @@
       </c>
       <c r="P55" s="6"/>
       <c r="Q55" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R55" s="6"/>
       <c r="S55" s="6"/>
@@ -4773,9 +5005,11 @@
         <v>Jhea N. Quiling</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I56" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
@@ -4786,9 +5020,11 @@
       <c r="O56" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P56" s="6"/>
+      <c r="P56" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="Q56" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
@@ -4827,7 +5063,9 @@
       <c r="H57" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I57" s="5"/>
+      <c r="I57" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
@@ -4838,9 +5076,11 @@
       <c r="O57" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P57" s="6"/>
+      <c r="P57" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="Q57" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R57" s="6"/>
       <c r="S57" s="6"/>
@@ -4879,7 +5119,9 @@
       <c r="H58" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I58" s="5"/>
+      <c r="I58" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
@@ -4890,9 +5132,11 @@
       <c r="O58" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P58" s="6"/>
+      <c r="P58" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="Q58" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
@@ -4931,7 +5175,9 @@
       <c r="H59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I59" s="5"/>
+      <c r="I59" s="10" t="s">
+        <v>367</v>
+      </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
@@ -4942,9 +5188,11 @@
       <c r="O59" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P59" s="6"/>
+      <c r="P59" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="Q59" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="R59" s="6"/>
       <c r="S59" s="6"/>
@@ -4983,7 +5231,9 @@
       <c r="H60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I60" s="5"/>
+      <c r="I60" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
@@ -4996,7 +5246,7 @@
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
@@ -5033,9 +5283,11 @@
         <v>Brendel B. Sacaris</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I61" s="5"/>
+        <v>244</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>381</v>
+      </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
@@ -5046,9 +5298,11 @@
       <c r="O61" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P61" s="6"/>
+      <c r="P61" s="6" t="s">
+        <v>392</v>
+      </c>
       <c r="Q61" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R61" s="6"/>
       <c r="S61" s="6"/>
@@ -5087,7 +5341,9 @@
       <c r="H62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I62" s="5"/>
+      <c r="I62" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
@@ -5100,7 +5356,7 @@
       </c>
       <c r="P62" s="6"/>
       <c r="Q62" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
@@ -5137,9 +5393,11 @@
         <v>Jevy Ann O. Uy</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I63" s="5"/>
+        <v>249</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>368</v>
+      </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
@@ -5150,9 +5408,11 @@
       <c r="O63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P63" s="6"/>
+      <c r="P63" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="Q63" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R63" s="6"/>
       <c r="S63" s="6"/>
@@ -5191,7 +5451,9 @@
       <c r="H64" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I64" s="5"/>
+      <c r="I64" s="10" t="s">
+        <v>382</v>
+      </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
@@ -5202,9 +5464,11 @@
       <c r="O64" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P64" s="6"/>
+      <c r="P64" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="Q64" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R64" s="6"/>
       <c r="S64" s="6"/>
@@ -5243,8 +5507,8 @@
       <c r="H65" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="I65" s="5" t="s">
-        <v>274</v>
+      <c r="I65" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
@@ -5256,9 +5520,11 @@
       <c r="O65" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P65" s="6"/>
+      <c r="P65" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q65" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="R65" s="6"/>
       <c r="S65" s="6"/>
@@ -5297,7 +5563,9 @@
       <c r="H66" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I66" s="5"/>
+      <c r="I66" s="10" t="s">
+        <v>369</v>
+      </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
@@ -5308,9 +5576,11 @@
       <c r="O66" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P66" s="6"/>
+      <c r="P66" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="Q66" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
@@ -5349,20 +5619,24 @@
       <c r="H67" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="I67" s="5"/>
+      <c r="I67" s="10" t="s">
+        <v>370</v>
+      </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="P67" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q67" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R67" s="6"/>
       <c r="S67" s="6"/>
@@ -5401,20 +5675,24 @@
       <c r="H68" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="I68" s="5"/>
+      <c r="I68" s="10" t="s">
+        <v>370</v>
+      </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="P68" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q68" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R68" s="6"/>
       <c r="S68" s="6"/>
@@ -5433,27 +5711,29 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>271</v>
+        <v>373</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>273</v>
+        <v>376</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="E69" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>M.</v>
+        <v>B.</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="str">
         <f t="shared" ref="G69:G70" si="10">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C69,IF(E69&lt;&gt;"",IF(RIGHT(E69,1)=".",E69,E69&amp;"."),D69),B69,F69))</f>
-        <v>Firstname M. Lastname</v>
+        <v>Luie B. Cabs</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="I69" s="5"/>
+      <c r="I69" s="10" t="s">
+        <v>370</v>
+      </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
@@ -5462,11 +5742,13 @@
         <v>240</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="P69" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q69" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R69" s="6"/>
       <c r="S69" s="6"/>
@@ -5474,7 +5756,7 @@
       <c r="U69" s="6"/>
       <c r="V69" s="5" t="str">
         <f t="shared" ref="V69:V70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
-        <v>/personnel/firstname-lastname.jpg</v>
+        <v>/personnel/luie-cabs.jpg</v>
       </c>
       <c r="W69" s="6" t="s">
         <v>9</v>
@@ -5485,27 +5767,29 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>271</v>
+        <v>374</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>273</v>
+        <v>375</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c r="E70" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>M.</v>
+        <v>B.</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Firstname M. Lastname</v>
+        <v>Luis B. Mans</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="I70" s="5"/>
+      <c r="I70" s="10" t="s">
+        <v>370</v>
+      </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
@@ -5514,11 +5798,13 @@
         <v>240</v>
       </c>
       <c r="O70" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="P70" s="6"/>
+        <v>371</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="Q70" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
@@ -5526,7 +5812,7 @@
       <c r="U70" s="6"/>
       <c r="V70" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>/personnel/firstname-lastname.jpg</v>
+        <v>/personnel/luis-mans.jpg</v>
       </c>
       <c r="W70" s="6" t="s">
         <v>9</v>
@@ -5546,7 +5832,7 @@
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
+      <c r="I71" s="9"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
@@ -5635,13 +5921,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>19</v>
@@ -5658,13 +5944,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -5681,13 +5967,13 @@
         <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -5704,13 +5990,13 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -5721,19 +6007,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B5" t="s">
         <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -5747,13 +6033,13 @@
         <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5761,13 +6047,13 @@
         <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5775,13 +6061,13 @@
         <v>245</v>
       </c>
       <c r="C8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5789,13 +6075,13 @@
         <v>270</v>
       </c>
       <c r="C9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5803,10 +6089,10 @@
         <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5814,10 +6100,10 @@
         <v>250</v>
       </c>
       <c r="C11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5825,10 +6111,10 @@
         <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E12" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5836,10 +6122,10 @@
         <v>252</v>
       </c>
       <c r="C13" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E13" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5847,7 +6133,7 @@
         <v>253</v>
       </c>
       <c r="E14" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5855,7 +6141,7 @@
         <v>254</v>
       </c>
       <c r="E15" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5863,10 +6149,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E16" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -5874,10 +6160,10 @@
         <v>246</v>
       </c>
       <c r="C17" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E17" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -5885,10 +6171,10 @@
         <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E18" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -5896,10 +6182,10 @@
         <v>248</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E19" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -5907,10 +6193,10 @@
         <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E20" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -5918,10 +6204,10 @@
         <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E21" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -5929,10 +6215,10 @@
         <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E22" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -5940,10 +6226,10 @@
         <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E23" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -5951,10 +6237,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E24" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -5962,7 +6248,7 @@
         <v>239</v>
       </c>
       <c r="C25" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -5970,7 +6256,7 @@
         <v>260</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -5978,7 +6264,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -5986,7 +6272,7 @@
         <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -5994,7 +6280,7 @@
         <v>263</v>
       </c>
       <c r="C29" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -6002,7 +6288,7 @@
         <v>264</v>
       </c>
       <c r="C30" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -6010,7 +6296,7 @@
         <v>265</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -6018,7 +6304,7 @@
         <v>266</v>
       </c>
       <c r="C32" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="2:3">
@@ -6026,7 +6312,7 @@
         <v>267</v>
       </c>
       <c r="C33" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="2:3">
@@ -6034,7 +6320,7 @@
         <v>268</v>
       </c>
       <c r="C34" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="2:3">
@@ -6042,137 +6328,137 @@
         <v>269</v>
       </c>
       <c r="C35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="C44" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="3:3">
       <c r="C51" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="3:3">
       <c r="C53" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="3:3">
       <c r="C54" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="3:3">
       <c r="C55" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="3:3">
       <c r="C56" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="3:3">
       <c r="C58" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="3:3">
       <c r="C60" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C7BDA-DA1C-4B71-ABE9-1240B01A5A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A22A98-65F6-4E30-9B68-709C7B3757D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="21315" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="395">
   <si>
     <t>order</t>
   </si>
@@ -1214,6 +1214,12 @@
   </si>
   <si>
     <t>Computer Systems Servicing / Filipino</t>
+  </si>
+  <si>
+    <t>7th Grade Level Chairpersons</t>
+  </si>
+  <si>
+    <t>8th Grade Level Chairpersons</t>
   </si>
 </sst>
 </file>
@@ -1320,47 +1326,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1588,6 +1553,47 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1741,22 +1747,22 @@
     <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="16">
       <calculatedColumnFormula>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="0"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="1"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="9"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2050,7 +2056,9 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
+      <c r="T2" s="6">
+        <v>2</v>
+      </c>
       <c r="U2" s="6"/>
       <c r="V2" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
@@ -2760,7 +2768,9 @@
       </c>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
+      <c r="T15" s="6">
+        <v>1</v>
+      </c>
       <c r="U15" s="6"/>
       <c r="V15" s="5" t="str">
         <f t="shared" si="2"/>
@@ -3026,7 +3036,9 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
+      <c r="T20" s="6">
+        <v>3</v>
+      </c>
       <c r="U20" s="6"/>
       <c r="V20" s="5" t="str">
         <f t="shared" si="2"/>
@@ -3732,7 +3744,7 @@
         <v>244</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -3752,7 +3764,9 @@
       </c>
       <c r="R33" s="6"/>
       <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
+      <c r="T33" s="6">
+        <v>4</v>
+      </c>
       <c r="U33" s="6"/>
       <c r="V33" s="5" t="str">
         <f t="shared" si="2"/>
@@ -5176,7 +5190,7 @@
         <v>12</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
@@ -5196,7 +5210,9 @@
       </c>
       <c r="R59" s="6"/>
       <c r="S59" s="6"/>
-      <c r="T59" s="6"/>
+      <c r="T59" s="6">
+        <v>5</v>
+      </c>
       <c r="U59" s="6"/>
       <c r="V59" s="5" t="str">
         <f t="shared" si="2"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A22A98-65F6-4E30-9B68-709C7B3757D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB6C8804-AD6D-4FAF-9623-3DB465BD80B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="21315" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="421">
   <si>
     <t>order</t>
   </si>
@@ -1180,9 +1180,6 @@
     <t>SDRRM Coordinator</t>
   </si>
   <si>
-    <t>LIS/ICT/EBEIS Coordinator</t>
-  </si>
-  <si>
     <t>SSLG Coordinator</t>
   </si>
   <si>
@@ -1220,6 +1217,87 @@
   </si>
   <si>
     <t>8th Grade Level Chairpersons</t>
+  </si>
+  <si>
+    <t>Subject Teacher</t>
+  </si>
+  <si>
+    <t>LIS/ICT/EBEIS Coordinator/SMIS Manager</t>
+  </si>
+  <si>
+    <t>advisoryGradeLevel</t>
+  </si>
+  <si>
+    <t>advisorySection</t>
+  </si>
+  <si>
+    <t>Swan</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>Maple</t>
+  </si>
+  <si>
+    <t>Ruby</t>
+  </si>
+  <si>
+    <t>Raven</t>
+  </si>
+  <si>
+    <t>Carrion</t>
+  </si>
+  <si>
+    <t>Olive</t>
+  </si>
+  <si>
+    <t>Emerald</t>
+  </si>
+  <si>
+    <t>Periwinkle</t>
+  </si>
+  <si>
+    <t>Cypress</t>
+  </si>
+  <si>
+    <t>Amethyst</t>
+  </si>
+  <si>
+    <t>Falcon</t>
+  </si>
+  <si>
+    <t>Dove</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>Aspen</t>
+  </si>
+  <si>
+    <t>Hyacinth</t>
+  </si>
+  <si>
+    <t>Canary</t>
+  </si>
+  <si>
+    <t>Stargazer</t>
+  </si>
+  <si>
+    <t>Sapphire</t>
+  </si>
+  <si>
+    <t>Eagle</t>
+  </si>
+  <si>
+    <t>Elm</t>
+  </si>
+  <si>
+    <t>Hazel</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1403,45 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1734,35 +1850,37 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:W71" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
-  <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:Y71" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+  <tableColumns count="25">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="20">
       <calculatedColumnFormula>IF(D2="","",LEFT(TRIM(D2),1)&amp;".")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="16">
+    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="18">
       <calculatedColumnFormula>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="1"/>
+    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1917,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:Y71"/>
   <sheetFormatPr defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.59765625" style="4" bestFit="1" customWidth="1"/>
@@ -1928,20 +2046,22 @@
     <col min="6" max="6" width="5.796875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.3984375" style="4" customWidth="1"/>
     <col min="8" max="8" width="23.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="27.69921875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="31" style="4" customWidth="1"/>
-    <col min="11" max="12" width="28" style="4" customWidth="1"/>
-    <col min="13" max="13" width="32.8984375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="26.69921875" style="4" customWidth="1"/>
-    <col min="15" max="15" width="20.09765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="45.19921875" style="7" customWidth="1"/>
-    <col min="17" max="21" width="24.19921875" style="7" customWidth="1"/>
-    <col min="22" max="22" width="36.69921875" style="4" customWidth="1"/>
-    <col min="23" max="23" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="8.796875" style="4"/>
+    <col min="9" max="9" width="40.796875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="19.296875" style="11" customWidth="1"/>
+    <col min="11" max="11" width="17.296875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="31" style="4" customWidth="1"/>
+    <col min="13" max="14" width="28" style="4" customWidth="1"/>
+    <col min="15" max="15" width="32.8984375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="26.69921875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="20.09765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="45.19921875" style="7" customWidth="1"/>
+    <col min="19" max="23" width="24.19921875" style="7" customWidth="1"/>
+    <col min="24" max="24" width="36.69921875" style="4" customWidth="1"/>
+    <col min="25" max="25" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="8.796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:25" ht="20.399999999999999" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1970,49 +2090,55 @@
         <v>324</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2040,35 +2166,37 @@
       <c r="I2" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="T2" s="6">
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6">
         <v>2</v>
       </c>
-      <c r="U2" s="6"/>
-      <c r="V2" s="5" t="str">
+      <c r="W2" s="6"/>
+      <c r="X2" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
         <v>/personnel/paz-abad.jpg</v>
       </c>
-      <c r="W2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="Y2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2094,37 +2222,43 @@
         <v>12</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>398</v>
+      </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
+      <c r="S3" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
-      <c r="V3" s="5" t="str">
-        <f t="shared" ref="V3:V66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="5" t="str">
+        <f t="shared" ref="X3:X66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
         <v>/personnel/marissa-abalo.jpg</v>
       </c>
-      <c r="W3" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
+      <c r="Y3" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2150,33 +2284,35 @@
         <v>12</v>
       </c>
       <c r="I4" s="10"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="R4" s="6" t="s">
+        <v>385</v>
+      </c>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
-      <c r="V4" s="5" t="str">
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joseph-allosada.jpg</v>
       </c>
-      <c r="W4" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
+      <c r="Y4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2202,37 +2338,43 @@
         <v>12</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>399</v>
+      </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q5" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
+      <c r="S5" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
-      <c r="V5" s="5" t="str">
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-gay-alsa.jpg</v>
       </c>
-      <c r="W5" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+      <c r="Y5" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2258,37 +2400,39 @@
         <v>12</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
+      <c r="R6" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T6" s="6"/>
       <c r="U6" s="6"/>
-      <c r="V6" s="5" t="str">
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lonier-andrade.jpg</v>
       </c>
-      <c r="W6" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
+      <c r="Y6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2314,37 +2458,43 @@
         <v>16</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>400</v>
+      </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="Q7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="Q7" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
+      <c r="S7" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T7" s="6"/>
       <c r="U7" s="6"/>
-      <c r="V7" s="5" t="str">
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/allan-raul-aparicio.jpg</v>
       </c>
-      <c r="W7" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="Y7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2370,33 +2520,35 @@
         <v>239</v>
       </c>
       <c r="I8" s="10"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="Q8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
+      <c r="R8" s="6" t="s">
+        <v>387</v>
+      </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
       <c r="U8" s="6"/>
-      <c r="V8" s="5" t="str">
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/niña-kristine-ayos.jpg</v>
       </c>
-      <c r="W8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="Y8" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2422,33 +2574,35 @@
         <v>244</v>
       </c>
       <c r="I9" s="10"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="Q9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="R9" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="6"/>
-      <c r="V9" s="5" t="str">
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/glenn-barangan.jpg</v>
       </c>
-      <c r="W9" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="Y9" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2474,37 +2628,43 @@
         <v>12</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>401</v>
+      </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="Q10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="R10" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T10" s="6"/>
       <c r="U10" s="6"/>
-      <c r="V10" s="5" t="str">
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jake-barcenas.jpg</v>
       </c>
-      <c r="W10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="Y10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2530,35 +2690,41 @@
         <v>12</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>402</v>
+      </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="Q11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
+      <c r="S11" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T11" s="6"/>
       <c r="U11" s="6"/>
-      <c r="V11" s="5" t="str">
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/eljoy-barroca.jpg</v>
       </c>
-      <c r="W11" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
+      <c r="Y11" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -2584,37 +2750,39 @@
         <v>12</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
       <c r="M12" s="5"/>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="Q12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
+      <c r="S12" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6"/>
-      <c r="V12" s="5" t="str">
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/angel-batuigas.jpg</v>
       </c>
-      <c r="W12" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
+      <c r="Y12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -2640,33 +2808,35 @@
         <v>12</v>
       </c>
       <c r="I13" s="10"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O13" s="5" t="s">
+      <c r="Q13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="R13" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
-      <c r="V13" s="5" t="str">
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/mary-josephine-bawiga.jpg</v>
       </c>
-      <c r="W13" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
+      <c r="Y13" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -2692,37 +2862,43 @@
         <v>12</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>403</v>
+      </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="Q14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
+      <c r="R14" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6"/>
-      <c r="V14" s="5" t="str">
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/endrie-bohol.jpg</v>
       </c>
-      <c r="W14" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
+      <c r="Y14" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -2750,37 +2926,39 @@
       <c r="I15" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O15" s="5" t="s">
+      <c r="Q15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P15" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q15" s="6" t="s">
+      <c r="R15" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S15" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6">
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6">
         <v>1</v>
       </c>
-      <c r="U15" s="6"/>
-      <c r="V15" s="5" t="str">
+      <c r="W15" s="6"/>
+      <c r="X15" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/maine-bongas.jpg</v>
       </c>
-      <c r="W15" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23">
+      <c r="Y15" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -2804,35 +2982,37 @@
         <v>12</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="Q16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
+      <c r="S16" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6"/>
-      <c r="V16" s="5" t="str">
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ruth-briones.jpg</v>
       </c>
-      <c r="W16" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="Y16" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -2858,31 +3038,33 @@
         <v>12</v>
       </c>
       <c r="I17" s="10"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="Q17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
-      <c r="V17" s="5" t="str">
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-broñola.jpg</v>
       </c>
-      <c r="W17" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="Y17" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -2910,33 +3092,35 @@
       <c r="I18" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="Q18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P18" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
+      <c r="R18" s="6" t="s">
+        <v>387</v>
+      </c>
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
-      <c r="V18" s="5" t="str">
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cabalda.jpg</v>
       </c>
-      <c r="W18" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="Y18" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -2962,37 +3146,39 @@
         <v>249</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+        <v>384</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="6" t="s">
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O19" s="5" t="s">
+      <c r="Q19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="R19" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="S19" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
-      <c r="V19" s="5" t="str">
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/gracelyn-cabunag.jpg</v>
       </c>
-      <c r="W19" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="Y19" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -3020,35 +3206,37 @@
       <c r="I20" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
-      <c r="N20" s="6" t="s">
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O20" s="5" t="s">
+      <c r="Q20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P20" s="6" t="s">
+      <c r="R20" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="6">
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6">
         <v>3</v>
       </c>
-      <c r="U20" s="6"/>
-      <c r="V20" s="5" t="str">
+      <c r="W20" s="6"/>
+      <c r="X20" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/hector-cabanca.jpg</v>
       </c>
-      <c r="W20" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="Y20" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -3074,37 +3262,43 @@
         <v>16</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>404</v>
+      </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="6" t="s">
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O21" s="5" t="s">
+      <c r="Q21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="6" t="s">
+      <c r="R21" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q21" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
+      <c r="S21" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
-      <c r="V21" s="5" t="str">
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeffrey-caberte.jpg</v>
       </c>
-      <c r="W21" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="Y21" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -3130,35 +3324,41 @@
         <v>12</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>405</v>
+      </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O22" s="5" t="s">
+      <c r="Q22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
+      <c r="S22" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
-      <c r="V22" s="5" t="str">
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-cabriana.jpg</v>
       </c>
-      <c r="W22" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="Y22" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -3186,35 +3386,37 @@
       <c r="I23" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="6" t="s">
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="O23" s="5" t="s">
+      <c r="Q23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P23" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q23" s="6" t="s">
+      <c r="R23" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S23" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
-      <c r="V23" s="5" t="str">
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jasmin-cabuenas.jpg</v>
       </c>
-      <c r="W23" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="Y23" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -3240,37 +3442,39 @@
         <v>12</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
+        <v>394</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="6" t="s">
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O24" s="5" t="s">
+      <c r="Q24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P24" s="6" t="s">
+      <c r="R24" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q24" s="6" t="s">
+      <c r="S24" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
-      <c r="V24" s="5" t="str">
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/elsa-calunod.jpg</v>
       </c>
-      <c r="W24" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="Y24" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -3296,37 +3500,43 @@
         <v>12</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>406</v>
+      </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
-      <c r="N25" s="6" t="s">
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="5" t="s">
+      <c r="Q25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P25" s="6" t="s">
+      <c r="R25" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="Q25" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
+      <c r="S25" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
-      <c r="V25" s="5" t="str">
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/leslyn-rose-camero.jpg</v>
       </c>
-      <c r="W25" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="Y25" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -3354,35 +3564,37 @@
       <c r="I26" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
-      <c r="N26" s="6" t="s">
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="O26" s="5" t="s">
+      <c r="Q26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P26" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q26" s="6" t="s">
+      <c r="R26" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S26" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
-      <c r="V26" s="5" t="str">
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/dawn-camille-caparida.jpg</v>
       </c>
-      <c r="W26" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="Y26" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -3406,37 +3618,43 @@
         <v>16</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>407</v>
+      </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="6" t="s">
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O27" s="5" t="s">
+      <c r="Q27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P27" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q27" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
+      <c r="R27" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S27" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
-      <c r="V27" s="5" t="str">
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lourence-capa.jpg</v>
       </c>
-      <c r="W27" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="Y27" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -3462,37 +3680,43 @@
         <v>12</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>408</v>
+      </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="6" t="s">
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O28" s="5" t="s">
+      <c r="Q28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P28" s="6" t="s">
+      <c r="R28" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="Q28" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
+      <c r="S28" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
-      <c r="V28" s="5" t="str">
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cavite.jpg</v>
       </c>
-      <c r="W28" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="Y28" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -3520,37 +3744,39 @@
         <v>270</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="6" t="s">
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O29" s="5" t="s">
+      <c r="Q29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P29" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
+      <c r="R29" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
-      <c r="V29" s="5" t="str">
+      <c r="V29" s="6"/>
+      <c r="W29" s="6"/>
+      <c r="X29" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joseph-dagaraga.jpg</v>
       </c>
-      <c r="W29" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="Y29" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -3578,35 +3804,37 @@
       <c r="I30" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="6" t="s">
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O30" s="5" t="s">
+      <c r="Q30" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P30" s="6" t="s">
+      <c r="R30" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="Q30" s="6" t="s">
+      <c r="S30" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
       <c r="T30" s="6"/>
       <c r="U30" s="6"/>
-      <c r="V30" s="5" t="str">
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
+      <c r="X30" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carolyn-delos-reyes.jpg</v>
       </c>
-      <c r="W30" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="Y30" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -3634,35 +3862,37 @@
       <c r="I31" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
-      <c r="N31" s="6" t="s">
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O31" s="5" t="s">
+      <c r="Q31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P31" s="6" t="s">
+      <c r="R31" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q31" s="6" t="s">
+      <c r="S31" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
-      <c r="V31" s="5" t="str">
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lucille-echavez.jpg</v>
       </c>
-      <c r="W31" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="Y31" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -3690,35 +3920,37 @@
       <c r="I32" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
-      <c r="N32" s="6" t="s">
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O32" s="5" t="s">
+      <c r="Q32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P32" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q32" s="6" t="s">
+      <c r="R32" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="S32" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
-      <c r="V32" s="5" t="str">
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/benerando-erediano.jpg</v>
       </c>
-      <c r="W32" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="Y32" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -3744,39 +3976,41 @@
         <v>244</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
+        <v>393</v>
+      </c>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
-      <c r="N33" s="6" t="s">
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O33" s="5" t="s">
+      <c r="Q33" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P33" s="6" t="s">
+      <c r="R33" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="Q33" s="6" t="s">
+      <c r="S33" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6">
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6">
         <v>4</v>
       </c>
-      <c r="U33" s="6"/>
-      <c r="V33" s="5" t="str">
+      <c r="W33" s="6"/>
+      <c r="X33" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/metchie-gay-gastanes.jpg</v>
       </c>
-      <c r="W33" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="Y33" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -3802,37 +4036,39 @@
         <v>12</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+        <v>383</v>
+      </c>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="6" t="s">
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O34" s="5" t="s">
+      <c r="Q34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P34" s="6" t="s">
+      <c r="R34" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="Q34" s="6" t="s">
+      <c r="S34" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
-      <c r="V34" s="5" t="str">
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jasmin-gerodias.jpg</v>
       </c>
-      <c r="W34" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="Y34" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -3858,37 +4094,43 @@
         <v>12</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>409</v>
+      </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="6" t="s">
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O35" s="5" t="s">
+      <c r="Q35" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P35" s="6" t="s">
+      <c r="R35" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q35" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
+      <c r="S35" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T35" s="6"/>
       <c r="U35" s="6"/>
-      <c r="V35" s="5" t="str">
+      <c r="V35" s="6"/>
+      <c r="W35" s="6"/>
+      <c r="X35" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeralyn-gerra.jpg</v>
       </c>
-      <c r="W35" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="Y35" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -3914,37 +4156,43 @@
         <v>241</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>410</v>
+      </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="6" t="s">
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="Q36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P36" s="6" t="s">
+      <c r="R36" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="Q36" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
+      <c r="S36" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
-      <c r="V36" s="5" t="str">
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/genesa-goc-ong.jpg</v>
       </c>
-      <c r="W36" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="Y36" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -3972,35 +4220,37 @@
       <c r="I37" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="6" t="s">
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O37" s="5" t="s">
+      <c r="Q37" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P37" s="6" t="s">
+      <c r="R37" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="Q37" s="6" t="s">
+      <c r="S37" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
       <c r="T37" s="6"/>
       <c r="U37" s="6"/>
-      <c r="V37" s="5" t="str">
+      <c r="V37" s="6"/>
+      <c r="W37" s="6"/>
+      <c r="X37" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/janelou-gomez.jpg</v>
       </c>
-      <c r="W37" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="Y37" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -4026,37 +4276,43 @@
         <v>12</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>411</v>
+      </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="6" t="s">
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O38" s="5" t="s">
+      <c r="Q38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P38" s="6" t="s">
+      <c r="R38" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q38" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
+      <c r="S38" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
-      <c r="V38" s="5" t="str">
+      <c r="V38" s="6"/>
+      <c r="W38" s="6"/>
+      <c r="X38" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/junnelyn-herbito.jpg</v>
       </c>
-      <c r="W38" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="Y38" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -4082,37 +4338,43 @@
         <v>241</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>412</v>
+      </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="6" t="s">
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O39" s="5" t="s">
+      <c r="Q39" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P39" s="6" t="s">
+      <c r="R39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q39" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
+      <c r="S39" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
-      <c r="V39" s="5" t="str">
+      <c r="V39" s="6"/>
+      <c r="W39" s="6"/>
+      <c r="X39" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/roxan-mae-jao.jpg</v>
       </c>
-      <c r="W39" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="Y39" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -4140,33 +4402,35 @@
       <c r="I40" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="6" t="s">
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O40" s="5" t="s">
+      <c r="Q40" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6" t="s">
+      <c r="R40" s="6"/>
+      <c r="S40" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
-      <c r="V40" s="5" t="str">
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
+      <c r="X40" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/fernando-laspiñas.jpg</v>
       </c>
-      <c r="W40" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="Y40" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -4194,35 +4458,37 @@
       <c r="I41" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="6" t="s">
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O41" s="5" t="s">
+      <c r="Q41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P41" s="6" t="s">
+      <c r="R41" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="Q41" s="6" t="s">
+      <c r="S41" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
       <c r="T41" s="6"/>
       <c r="U41" s="6"/>
-      <c r="V41" s="5" t="str">
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/nerisa-lim.jpg</v>
       </c>
-      <c r="W41" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="Y41" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -4248,33 +4514,35 @@
       <c r="I42" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="6" t="s">
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O42" s="5" t="s">
+      <c r="Q42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6" t="s">
+      <c r="R42" s="6"/>
+      <c r="S42" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
       <c r="T42" s="6"/>
       <c r="U42" s="6"/>
-      <c r="V42" s="5" t="str">
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carl-loreto.jpg</v>
       </c>
-      <c r="W42" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="Y42" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -4300,35 +4568,37 @@
         <v>270</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
+        <v>382</v>
+      </c>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
-      <c r="N43" s="6" t="s">
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O43" s="5" t="s">
+      <c r="Q43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6" t="s">
+      <c r="R43" s="6"/>
+      <c r="S43" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
       <c r="T43" s="6"/>
       <c r="U43" s="6"/>
-      <c r="V43" s="5" t="str">
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lyka-mabanag.jpg</v>
       </c>
-      <c r="W43" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="Y43" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -4356,39 +4626,41 @@
       <c r="I44" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5" t="s">
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="N44" s="6" t="s">
+      <c r="P44" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O44" s="5" t="s">
+      <c r="Q44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P44" s="6" t="s">
+      <c r="R44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q44" s="6" t="s">
+      <c r="S44" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
-      <c r="V44" s="5" t="str">
+      <c r="V44" s="6"/>
+      <c r="W44" s="6"/>
+      <c r="X44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/richie-ryan-mabunay.jpg</v>
       </c>
-      <c r="W44" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="Y44" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -4416,35 +4688,37 @@
       <c r="I45" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
-      <c r="N45" s="6" t="s">
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O45" s="5" t="s">
+      <c r="Q45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P45" s="6" t="s">
+      <c r="R45" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="Q45" s="6" t="s">
+      <c r="S45" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
-      <c r="V45" s="5" t="str">
+      <c r="V45" s="6"/>
+      <c r="W45" s="6"/>
+      <c r="X45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/maria-jeziel-macanin.jpg</v>
       </c>
-      <c r="W45" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="Y45" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -4470,37 +4744,43 @@
         <v>12</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>413</v>
+      </c>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
-      <c r="N46" s="6" t="s">
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O46" s="5" t="s">
+      <c r="Q46" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P46" s="6" t="s">
+      <c r="R46" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="Q46" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
+      <c r="S46" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T46" s="6"/>
       <c r="U46" s="6"/>
-      <c r="V46" s="5" t="str">
+      <c r="V46" s="6"/>
+      <c r="W46" s="6"/>
+      <c r="X46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeralen-maloloy-on.jpg</v>
       </c>
-      <c r="W46" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+      <c r="Y46" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -4526,37 +4806,43 @@
         <v>12</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>414</v>
+      </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
-      <c r="N47" s="6" t="s">
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O47" s="5" t="s">
+      <c r="Q47" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="6" t="s">
+      <c r="R47" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="Q47" s="6" t="s">
+      <c r="S47" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
-      <c r="V47" s="5" t="str">
+      <c r="V47" s="6"/>
+      <c r="W47" s="6"/>
+      <c r="X47" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/elbert-misterio.jpg</v>
       </c>
-      <c r="W47" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+      <c r="Y47" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -4582,35 +4868,41 @@
         <v>241</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>415</v>
+      </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
-      <c r="N48" s="6" t="s">
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O48" s="5" t="s">
+      <c r="Q48" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
+      <c r="S48" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
-      <c r="V48" s="5" t="str">
+      <c r="V48" s="6"/>
+      <c r="W48" s="6"/>
+      <c r="X48" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joy-mortal.jpg</v>
       </c>
-      <c r="W48" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="Y48" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -4638,33 +4930,35 @@
       <c r="I49" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
-      <c r="N49" s="6" t="s">
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O49" s="5" t="s">
+      <c r="Q49" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6" t="s">
+      <c r="R49" s="6"/>
+      <c r="S49" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
       <c r="T49" s="6"/>
       <c r="U49" s="6"/>
-      <c r="V49" s="5" t="str">
+      <c r="V49" s="6"/>
+      <c r="W49" s="6"/>
+      <c r="X49" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/claire-medillo.jpg</v>
       </c>
-      <c r="W49" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23">
+      <c r="Y49" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -4690,37 +4984,43 @@
         <v>12</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>416</v>
+      </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
-      <c r="N50" s="6" t="s">
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O50" s="5" t="s">
+      <c r="Q50" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P50" s="6" t="s">
+      <c r="R50" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="Q50" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
+      <c r="S50" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T50" s="6"/>
       <c r="U50" s="6"/>
-      <c r="V50" s="5" t="str">
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/gwendolyn-olo.jpg</v>
       </c>
-      <c r="W50" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23">
+      <c r="Y50" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -4746,35 +5046,41 @@
         <v>12</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>417</v>
+      </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
-      <c r="N51" s="6" t="s">
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O51" s="5" t="s">
+      <c r="Q51" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
+      <c r="S51" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
-      <c r="V51" s="5" t="str">
+      <c r="V51" s="6"/>
+      <c r="W51" s="6"/>
+      <c r="X51" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jay-neil-oro.jpg</v>
       </c>
-      <c r="W51" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23">
+      <c r="Y51" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -4800,37 +5106,39 @@
         <v>12</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
-      <c r="N52" s="6" t="s">
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O52" s="5" t="s">
+      <c r="Q52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P52" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q52" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
+      <c r="R52" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="S52" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
-      <c r="V52" s="5" t="str">
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/glendale-orocay.jpg</v>
       </c>
-      <c r="W52" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23">
+      <c r="Y52" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -4856,37 +5164,39 @@
         <v>16</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="6" t="s">
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O53" s="5" t="s">
+      <c r="Q53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P53" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
+      <c r="R53" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S53" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
-      <c r="V53" s="5" t="str">
+      <c r="V53" s="6"/>
+      <c r="W53" s="6"/>
+      <c r="X53" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marissa-pintuan.jpg</v>
       </c>
-      <c r="W53" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23">
+      <c r="Y53" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -4914,35 +5224,37 @@
       <c r="I54" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
-      <c r="N54" s="6" t="s">
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O54" s="5" t="s">
+      <c r="Q54" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P54" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q54" s="6" t="s">
+      <c r="R54" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="S54" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
       <c r="T54" s="6"/>
       <c r="U54" s="6"/>
-      <c r="V54" s="5" t="str">
+      <c r="V54" s="6"/>
+      <c r="W54" s="6"/>
+      <c r="X54" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ma.-lourdes-prajes.jpg</v>
       </c>
-      <c r="W54" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23">
+      <c r="Y54" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -4968,35 +5280,41 @@
         <v>12</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>418</v>
+      </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="6" t="s">
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O55" s="5" t="s">
+      <c r="Q55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
+      <c r="S55" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T55" s="6"/>
       <c r="U55" s="6"/>
-      <c r="V55" s="5" t="str">
+      <c r="V55" s="6"/>
+      <c r="W55" s="6"/>
+      <c r="X55" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/bret-kalvin-primacio.jpg</v>
       </c>
-      <c r="W55" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
+      <c r="Y55" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5024,35 +5342,37 @@
       <c r="I56" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="6" t="s">
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O56" s="5" t="s">
+      <c r="Q56" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P56" s="6" t="s">
+      <c r="R56" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q56" s="6" t="s">
+      <c r="S56" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
       <c r="T56" s="6"/>
       <c r="U56" s="6"/>
-      <c r="V56" s="5" t="str">
+      <c r="V56" s="6"/>
+      <c r="W56" s="6"/>
+      <c r="X56" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jhea-quiling.jpg</v>
       </c>
-      <c r="W56" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23">
+      <c r="Y56" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5080,35 +5400,37 @@
       <c r="I57" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="6" t="s">
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O57" s="5" t="s">
+      <c r="Q57" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P57" s="6" t="s">
+      <c r="R57" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="Q57" s="6" t="s">
+      <c r="S57" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R57" s="6"/>
-      <c r="S57" s="6"/>
       <c r="T57" s="6"/>
       <c r="U57" s="6"/>
-      <c r="V57" s="5" t="str">
+      <c r="V57" s="6"/>
+      <c r="W57" s="6"/>
+      <c r="X57" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joyce-racaza.jpg</v>
       </c>
-      <c r="W57" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23">
+      <c r="Y57" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -5136,35 +5458,37 @@
       <c r="I58" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
-      <c r="N58" s="6" t="s">
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O58" s="5" t="s">
+      <c r="Q58" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P58" s="6" t="s">
+      <c r="R58" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="Q58" s="6" t="s">
+      <c r="S58" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
       <c r="T58" s="6"/>
       <c r="U58" s="6"/>
-      <c r="V58" s="5" t="str">
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
+      <c r="X58" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/cromwell-retuya.jpg</v>
       </c>
-      <c r="W58" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23">
+      <c r="Y58" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -5190,39 +5514,41 @@
         <v>12</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
+        <v>392</v>
+      </c>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
-      <c r="N59" s="6" t="s">
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O59" s="5" t="s">
+      <c r="Q59" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P59" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q59" s="6" t="s">
+      <c r="R59" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="S59" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6"/>
-      <c r="T59" s="6">
+      <c r="T59" s="6"/>
+      <c r="U59" s="6"/>
+      <c r="V59" s="6">
         <v>5</v>
       </c>
-      <c r="U59" s="6"/>
-      <c r="V59" s="5" t="str">
+      <c r="W59" s="6"/>
+      <c r="X59" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/nancy-reyes.jpg</v>
       </c>
-      <c r="W59" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23">
+      <c r="Y59" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -5248,35 +5574,41 @@
         <v>12</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>419</v>
+      </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
-      <c r="N60" s="6" t="s">
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O60" s="5" t="s">
+      <c r="Q60" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
+      <c r="S60" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T60" s="6"/>
       <c r="U60" s="6"/>
-      <c r="V60" s="5" t="str">
+      <c r="V60" s="6"/>
+      <c r="W60" s="6"/>
+      <c r="X60" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/angelo-saavedra.jpg</v>
       </c>
-      <c r="W60" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23">
+      <c r="Y60" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -5302,37 +5634,39 @@
         <v>244</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
+        <v>395</v>
+      </c>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
-      <c r="N61" s="6" t="s">
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O61" s="5" t="s">
+      <c r="Q61" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P61" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q61" s="6" t="s">
+      <c r="R61" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="S61" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R61" s="6"/>
-      <c r="S61" s="6"/>
       <c r="T61" s="6"/>
       <c r="U61" s="6"/>
-      <c r="V61" s="5" t="str">
+      <c r="V61" s="6"/>
+      <c r="W61" s="6"/>
+      <c r="X61" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/brendel-sacaris.jpg</v>
       </c>
-      <c r="W61" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23">
+      <c r="Y61" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5358,35 +5692,41 @@
         <v>12</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>420</v>
+      </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
-      <c r="N62" s="6" t="s">
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O62" s="5" t="s">
+      <c r="Q62" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6" t="s">
-        <v>368</v>
-      </c>
       <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
+      <c r="S62" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T62" s="6"/>
       <c r="U62" s="6"/>
-      <c r="V62" s="5" t="str">
+      <c r="V62" s="6"/>
+      <c r="W62" s="6"/>
+      <c r="X62" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C62&amp;" "&amp;B62)," ","-"))&amp;".jpg"</f>
         <v>/personnel/bella-arquine-samontañez.jpg</v>
       </c>
-      <c r="W62" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23">
+      <c r="Y62" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -5412,37 +5752,39 @@
         <v>249</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="6" t="s">
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O63" s="5" t="s">
+      <c r="Q63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P63" s="6" t="s">
+      <c r="R63" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="Q63" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
+      <c r="S63" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
-      <c r="V63" s="5" t="str">
+      <c r="V63" s="6"/>
+      <c r="W63" s="6"/>
+      <c r="X63" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jevy-ann-uy.jpg</v>
       </c>
-      <c r="W63" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23">
+      <c r="Y63" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -5468,37 +5810,39 @@
         <v>12</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
+        <v>381</v>
+      </c>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="6" t="s">
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O64" s="5" t="s">
+      <c r="Q64" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P64" s="6" t="s">
+      <c r="R64" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="Q64" s="6" t="s">
+      <c r="S64" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
       <c r="T64" s="6"/>
       <c r="U64" s="6"/>
-      <c r="V64" s="5" t="str">
+      <c r="V64" s="6"/>
+      <c r="W64" s="6"/>
+      <c r="X64" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/grace-vergara.jpg</v>
       </c>
-      <c r="W64" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23">
+      <c r="Y64" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -5526,35 +5870,37 @@
       <c r="I65" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
-      <c r="N65" s="6" t="s">
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="O65" s="5" t="s">
+      <c r="Q65" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P65" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q65" s="6" t="s">
+      <c r="R65" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S65" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
-      <c r="V65" s="5" t="str">
+      <c r="V65" s="6"/>
+      <c r="W65" s="6"/>
+      <c r="X65" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/guillermo-villavelez.jpg</v>
       </c>
-      <c r="W65" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23">
+      <c r="Y65" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -5582,35 +5928,37 @@
       <c r="I66" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
-      <c r="N66" s="6" t="s">
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O66" s="5" t="s">
+      <c r="Q66" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P66" s="6" t="s">
+      <c r="R66" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="Q66" s="6" t="s">
+      <c r="S66" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
       <c r="T66" s="6"/>
       <c r="U66" s="6"/>
-      <c r="V66" s="5" t="str">
+      <c r="V66" s="6"/>
+      <c r="W66" s="6"/>
+      <c r="X66" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-villaver.jpg</v>
       </c>
-      <c r="W66" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23">
+      <c r="Y66" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -5638,35 +5986,37 @@
       <c r="I67" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
-      <c r="N67" s="6" t="s">
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="O67" s="5" t="s">
+      <c r="Q67" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="P67" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q67" s="6" t="s">
+      <c r="R67" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S67" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="R67" s="6"/>
-      <c r="S67" s="6"/>
       <c r="T67" s="6"/>
       <c r="U67" s="6"/>
-      <c r="V67" s="5" t="str">
-        <f t="shared" ref="V67:V68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="5" t="str">
+        <f t="shared" ref="X67:X68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
         <v>/personnel/markjil-bacaltos.jpg</v>
       </c>
-      <c r="W67" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23">
+      <c r="Y67" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -5694,35 +6044,37 @@
       <c r="I68" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
-      <c r="N68" s="6" t="s">
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="O68" s="5" t="s">
+      <c r="Q68" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="P68" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q68" s="6" t="s">
+      <c r="R68" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S68" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
       <c r="T68" s="6"/>
       <c r="U68" s="6"/>
-      <c r="V68" s="5" t="str">
+      <c r="V68" s="6"/>
+      <c r="W68" s="6"/>
+      <c r="X68" s="5" t="str">
         <f t="shared" si="8"/>
         <v>/personnel/diocel-celocia.jpg</v>
       </c>
-      <c r="W68" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23">
+      <c r="Y68" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -5750,35 +6102,37 @@
       <c r="I69" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
-      <c r="N69" s="6" t="s">
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="O69" s="5" t="s">
+      <c r="Q69" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="P69" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q69" s="6" t="s">
+      <c r="R69" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S69" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="R69" s="6"/>
-      <c r="S69" s="6"/>
       <c r="T69" s="6"/>
       <c r="U69" s="6"/>
-      <c r="V69" s="5" t="str">
-        <f t="shared" ref="V69:V70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
+      <c r="V69" s="6"/>
+      <c r="W69" s="6"/>
+      <c r="X69" s="5" t="str">
+        <f t="shared" ref="X69:X70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
         <v>/personnel/luie-cabs.jpg</v>
       </c>
-      <c r="W69" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23">
+      <c r="Y69" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -5806,35 +6160,37 @@
       <c r="I70" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="10"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
-      <c r="N70" s="6" t="s">
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="O70" s="5" t="s">
+      <c r="Q70" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="P70" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q70" s="6" t="s">
+      <c r="R70" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="S70" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
       <c r="T70" s="6"/>
       <c r="U70" s="6"/>
-      <c r="V70" s="5" t="str">
+      <c r="V70" s="6"/>
+      <c r="W70" s="6"/>
+      <c r="X70" s="5" t="str">
         <f t="shared" si="11"/>
         <v>/personnel/luis-mans.jpg</v>
       </c>
-      <c r="W70" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23">
+      <c r="Y70" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -5849,20 +6205,22 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
+      <c r="N71" s="5"/>
       <c r="O71" s="5"/>
       <c r="P71" s="6"/>
-      <c r="Q71" s="6"/>
+      <c r="Q71" s="5"/>
       <c r="R71" s="6"/>
       <c r="S71" s="6"/>
       <c r="T71" s="6"/>
       <c r="U71" s="6"/>
-      <c r="V71" s="5"/>
+      <c r="V71" s="6"/>
       <c r="W71" s="6"/>
+      <c r="X71" s="5"/>
+      <c r="Y71" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -5877,13 +6235,13 @@
           <x14:formula1>
             <xm:f>Dropdown_Lists!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>N71</xm:sqref>
+          <xm:sqref>P71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{F197BE03-BA33-43F0-8353-14B37878E191}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N70</xm:sqref>
+          <xm:sqref>P2:P70</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{909FCDCA-C40C-4807-A52A-02A68E381F21}">
           <x14:formula1>
@@ -5895,19 +6253,19 @@
           <x14:formula1>
             <xm:f>Dropdown_Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W71</xm:sqref>
+          <xm:sqref>Y2:Y71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70D54F6E-2A67-40F0-92CA-B6E53F44843D}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$D$2:$D$61</xm:f>
           </x14:formula1>
-          <xm:sqref>Q2:Q71</xm:sqref>
+          <xm:sqref>S2:S71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7834D497-9733-4178-89DF-4B7895726F53}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$E$2:$E$60</xm:f>
           </x14:formula1>
-          <xm:sqref>R2:R71</xm:sqref>
+          <xm:sqref>T2:T71</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB6C8804-AD6D-4FAF-9623-3DB465BD80B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5296B38E-E333-4736-B431-660CAEBD597D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="428">
   <si>
     <t>order</t>
   </si>
@@ -1298,6 +1298,27 @@
   </si>
   <si>
     <t>Hazel</t>
+  </si>
+  <si>
+    <t>Daisy</t>
+  </si>
+  <si>
+    <t>Apollo, Demeter, Hades</t>
+  </si>
+  <si>
+    <t>Athena, Erebus, Hera</t>
+  </si>
+  <si>
+    <t>Aphrodite, Hestia, Poseidon</t>
+  </si>
+  <si>
+    <t>Earth, Mars</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Jupiter, Saturn</t>
   </si>
 </sst>
 </file>
@@ -1404,44 +1425,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1673,6 +1656,44 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1865,22 +1886,22 @@
     </tableColumn>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="17"/>
     <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="1"/>
-    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="0"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="6"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2374,7 +2395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" ht="33.6">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2402,8 +2423,12 @@
       <c r="I6" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="J6" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>422</v>
+      </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -2752,8 +2777,12 @@
       <c r="I12" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="J12" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>425</v>
+      </c>
       <c r="L12" s="5" t="s">
         <v>379</v>
       </c>
@@ -2984,8 +3013,12 @@
       <c r="I16" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="J16" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>421</v>
+      </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -3716,7 +3749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" ht="33.6">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -3746,8 +3779,12 @@
       <c r="I29" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
+      <c r="J29" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>424</v>
+      </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -5108,8 +5145,12 @@
       <c r="I52" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
+      <c r="J52" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>426</v>
+      </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
@@ -5138,7 +5179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" ht="33.6">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -5166,8 +5207,12 @@
       <c r="I53" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
+      <c r="J53" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>423</v>
+      </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
@@ -5754,8 +5799,12 @@
       <c r="I63" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
+      <c r="J63" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>427</v>
+      </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5296B38E-E333-4736-B431-660CAEBD597D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFE0AE0-5E41-4065-B58F-FE70AA82722B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="21300" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="475">
   <si>
     <t>order</t>
   </si>
@@ -1174,9 +1174,6 @@
     <t>Junior High School In-Charge</t>
   </si>
   <si>
-    <t>BSP Coordinator</t>
-  </si>
-  <si>
     <t>SDRRM Coordinator</t>
   </si>
   <si>
@@ -1195,9 +1192,6 @@
     <t>Math</t>
   </si>
   <si>
-    <t>ICT/Progamming</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -1319,6 +1313,153 @@
   </si>
   <si>
     <t>Jupiter, Saturn</t>
+  </si>
+  <si>
+    <t>English 10</t>
+  </si>
+  <si>
+    <t>primarySubjectDepartment</t>
+  </si>
+  <si>
+    <t>subject1</t>
+  </si>
+  <si>
+    <t>subject2</t>
+  </si>
+  <si>
+    <t>subject3</t>
+  </si>
+  <si>
+    <t>subject4</t>
+  </si>
+  <si>
+    <t>subject5</t>
+  </si>
+  <si>
+    <t>teachingLevel</t>
+  </si>
+  <si>
+    <t>JHS/SHS</t>
+  </si>
+  <si>
+    <t>MAPEH 8</t>
+  </si>
+  <si>
+    <t>MAPEH 10</t>
+  </si>
+  <si>
+    <t>Life and Career Skills (LCS 11 - SEM1)</t>
+  </si>
+  <si>
+    <t>Values Education 8</t>
+  </si>
+  <si>
+    <t>School Facilities Assistant Coordinator</t>
+  </si>
+  <si>
+    <t>School Sports Assistant Coordinator</t>
+  </si>
+  <si>
+    <t>Drum Lyre and Majorette Corps Coordinator</t>
+  </si>
+  <si>
+    <t>Values Education 9</t>
+  </si>
+  <si>
+    <t>Technical Professional (Tech Pro)</t>
+  </si>
+  <si>
+    <t>Computer Programming (JAVA)</t>
+  </si>
+  <si>
+    <t>Media and Information Literacy</t>
+  </si>
+  <si>
+    <t>Assistant School Testing Coordinator</t>
+  </si>
+  <si>
+    <t>Assistant SHS ICT Coordinator</t>
+  </si>
+  <si>
+    <t>JHS-TLE Coordinator</t>
+  </si>
+  <si>
+    <t>JHS-ICT Coordinator</t>
+  </si>
+  <si>
+    <t>ESP Coordinator</t>
+  </si>
+  <si>
+    <t>School Religious Act Coordinator</t>
+  </si>
+  <si>
+    <t>Edukasyon sa Pagpapakatao 10</t>
+  </si>
+  <si>
+    <t>Wash in School Coordinator</t>
+  </si>
+  <si>
+    <t>Science 8</t>
+  </si>
+  <si>
+    <t>Boys Scout of the Philippines Coordinator</t>
+  </si>
+  <si>
+    <t>Araling Panlipunan Coordinator (SHS)</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>Araling Panlipunan 9</t>
+  </si>
+  <si>
+    <t>Elective 2-Introduction to World Religions and Belief Systems</t>
+  </si>
+  <si>
+    <t>School Health Aide Coordinator (JHS)</t>
+  </si>
+  <si>
+    <t>Technology and Livelihood Education 8 &amp; 9</t>
+  </si>
+  <si>
+    <t>Technology and Livelihood Education 9 &amp; 10</t>
+  </si>
+  <si>
+    <t>Mathematics 9 &amp; 10</t>
+  </si>
+  <si>
+    <t>MAPEH 7 &amp; 10</t>
+  </si>
+  <si>
+    <t>SHS Mathematics Coordinator</t>
+  </si>
+  <si>
+    <t>Mathematics 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>General Mathemathics</t>
+  </si>
+  <si>
+    <t>SHS English Coordinator</t>
+  </si>
+  <si>
+    <t>Learning Action Cell (LAC) Coordinator for SHS</t>
+  </si>
+  <si>
+    <t>Contemporary Philippine Arts from the Regions</t>
+  </si>
+  <si>
+    <t>Research for Daily Life 2</t>
+  </si>
+  <si>
+    <t>SHS Work Immersion Coordinator, Alternate</t>
+  </si>
+  <si>
+    <t>Life and Career Skills</t>
+  </si>
+  <si>
+    <t>English 7 &amp; 8</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1565,140 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1871,37 +2145,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:Y71" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
-  <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:AF71" headerRowDxfId="34" dataDxfId="33" totalsRowDxfId="32">
+  <tableColumns count="32">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="27">
       <calculatedColumnFormula>IF(D2="","",LEFT(TRIM(D2),1)&amp;".")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="18">
+    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="25">
       <calculatedColumnFormula>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="15"/>
-    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="24"/>
+    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="22"/>
+    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="14"/>
+    <tableColumn id="26" xr3:uid="{9234D872-27E9-4981-9849-3B92B3D703D7}" name="primarySubjectDepartment" dataDxfId="6"/>
+    <tableColumn id="27" xr3:uid="{BAF0BAF6-D68C-494F-94BF-9DBEAC627028}" name="subject1" dataDxfId="5"/>
+    <tableColumn id="28" xr3:uid="{8B540991-2968-4F70-8AAC-FCFC355A419A}" name="subject2" dataDxfId="4"/>
+    <tableColumn id="29" xr3:uid="{1D6F7D4B-4E56-4246-A153-8FAB0BEB4811}" name="subject3" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{E295C211-F74A-4E2B-893A-E9FDF18B7EE9}" name="subject4" dataDxfId="2"/>
+    <tableColumn id="31" xr3:uid="{B93E7C74-87A6-4CBE-9E54-1C7E4E717375}" name="subject5" dataDxfId="1"/>
+    <tableColumn id="32" xr3:uid="{AE0F403C-1544-4D9E-929C-27676144B2E2}" name="teachingLevel" dataDxfId="0"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2056,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:AF71"/>
   <sheetFormatPr defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.59765625" style="4" bestFit="1" customWidth="1"/>
@@ -2075,14 +2356,14 @@
     <col min="15" max="15" width="32.8984375" style="4" customWidth="1"/>
     <col min="16" max="16" width="26.69921875" style="4" customWidth="1"/>
     <col min="17" max="17" width="20.09765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="45.19921875" style="7" customWidth="1"/>
-    <col min="19" max="23" width="24.19921875" style="7" customWidth="1"/>
-    <col min="24" max="24" width="36.69921875" style="4" customWidth="1"/>
-    <col min="25" max="25" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.796875" style="4"/>
+    <col min="18" max="25" width="45.19921875" style="7" customWidth="1"/>
+    <col min="26" max="30" width="24.19921875" style="7" customWidth="1"/>
+    <col min="31" max="31" width="36.69921875" style="4" customWidth="1"/>
+    <col min="32" max="32" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="8.796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:32" ht="20.399999999999999" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2111,10 +2392,10 @@
         <v>324</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>325</v>
@@ -2138,28 +2419,49 @@
         <v>4</v>
       </c>
       <c r="S1" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="Z1" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AF1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:32">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2202,22 +2504,37 @@
       <c r="R2" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
+      <c r="S2" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>426</v>
+      </c>
       <c r="U2" s="6"/>
-      <c r="V2" s="6">
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6">
         <v>2</v>
       </c>
-      <c r="W2" s="6"/>
-      <c r="X2" s="5" t="str">
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
         <v>/personnel/paz-abad.jpg</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="AF2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:32">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2249,7 +2566,7 @@
         <v>353</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -2265,21 +2582,38 @@
         <v>343</v>
       </c>
       <c r="S3" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="5" t="str">
-        <f t="shared" ref="X3:X66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="5" t="str">
+        <f t="shared" ref="AE3:AE66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
         <v>/personnel/marissa-abalo.jpg</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="AF3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:32">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2304,7 +2638,9 @@
       <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="I4" s="10" t="s">
+        <v>439</v>
+      </c>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
       <c r="L4" s="5"/>
@@ -2318,22 +2654,37 @@
         <v>17</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
+        <v>384</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>463</v>
+      </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
-      <c r="X4" s="5" t="str">
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joseph-allosada.jpg</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:32" ht="33.6">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2365,10 +2716,14 @@
         <v>355</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+        <v>397</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>441</v>
+      </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="6" t="s">
@@ -2381,21 +2736,36 @@
         <v>343</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
+        <v>343</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>436</v>
+      </c>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
-      <c r="X5" s="5" t="str">
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-gay-alsa.jpg</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="AF5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="33.6">
+    <row r="6" spans="1:32" ht="33.6">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2427,7 +2797,7 @@
         <v>356</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -2440,24 +2810,39 @@
         <v>14</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
+        <v>345</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>445</v>
+      </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
-      <c r="X6" s="5" t="str">
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lonier-andrade.jpg</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="AF6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:32">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2489,10 +2874,14 @@
         <v>354</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>447</v>
+      </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="6" t="s">
@@ -2505,21 +2894,34 @@
         <v>344</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T7" s="6"/>
+        <v>344</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>461</v>
+      </c>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
-      <c r="X7" s="5" t="str">
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/allan-raul-aparicio.jpg</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="AF7" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:32">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2558,22 +2960,31 @@
         <v>7</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
-      <c r="X8" s="5" t="str">
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/niña-kristine-ayos.jpg</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="AF8" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:32">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2598,10 +3009,14 @@
       <c r="H9" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="I9" s="10"/>
+      <c r="I9" s="10" t="s">
+        <v>448</v>
+      </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="5" t="s">
+        <v>449</v>
+      </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -2614,20 +3029,35 @@
       <c r="R9" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
+      <c r="S9" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
-      <c r="X9" s="5" t="str">
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/glenn-barangan.jpg</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="AF9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:32">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2659,10 +3089,14 @@
         <v>355</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>451</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="6" t="s">
@@ -2672,24 +3106,37 @@
         <v>14</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T10" s="6"/>
+        <v>386</v>
+      </c>
+      <c r="T10" s="6" t="s">
+        <v>452</v>
+      </c>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
-      <c r="X10" s="5" t="str">
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jake-barcenas.jpg</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="AF10" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:32">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2721,9 +3168,11 @@
         <v>353</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="L11" s="5"/>
+        <v>400</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>453</v>
+      </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -2733,23 +3182,38 @@
       <c r="Q11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R11" s="6"/>
+      <c r="R11" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="S11" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T11" s="6"/>
+        <v>341</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>454</v>
+      </c>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
-      <c r="X11" s="5" t="str">
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/eljoy-barroca.jpg</v>
       </c>
-      <c r="Y11" s="6" t="s">
+      <c r="AF11" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:32" ht="33.6">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -2781,12 +3245,14 @@
         <v>357</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="M12" s="5"/>
+        <v>455</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>456</v>
+      </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="6" t="s">
@@ -2795,23 +3261,40 @@
       <c r="Q12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R12" s="6"/>
+      <c r="R12" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="S12" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
+        <v>457</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>459</v>
+      </c>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
-      <c r="X12" s="5" t="str">
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/angel-batuigas.jpg</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="AF12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:32">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -2836,7 +3319,9 @@
       <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="10" t="s">
+        <v>460</v>
+      </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="5"/>
@@ -2852,20 +3337,35 @@
       <c r="R13" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
+      <c r="S13" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="T13" s="6" t="s">
+        <v>464</v>
+      </c>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
-      <c r="X13" s="5" t="str">
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/mary-josephine-bawiga.jpg</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="AF13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:32">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -2897,9 +3397,11 @@
         <v>352</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="L14" s="5"/>
+        <v>401</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>465</v>
+      </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -2907,27 +3409,42 @@
         <v>13</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+        <v>384</v>
+      </c>
+      <c r="T14" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>466</v>
+      </c>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
-      <c r="X14" s="5" t="str">
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/endrie-bohol.jpg</v>
       </c>
-      <c r="Y14" s="6" t="s">
+      <c r="AF14" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:32" ht="33.6">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -2957,8 +3474,12 @@
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="L15" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>469</v>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="6" t="s">
@@ -2968,26 +3489,41 @@
         <v>14</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="S15" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z15" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6">
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6">
         <v>1</v>
       </c>
-      <c r="W15" s="6"/>
-      <c r="X15" s="5" t="str">
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/maine-bongas.jpg</v>
       </c>
-      <c r="Y15" s="6" t="s">
+      <c r="AF15" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:32" ht="33.6">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -3017,9 +3553,11 @@
         <v>352</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="L16" s="5"/>
+        <v>419</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>472</v>
+      </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -3029,23 +3567,40 @@
       <c r="Q16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R16" s="6"/>
+      <c r="R16" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="S16" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
+        <v>334</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
-      <c r="X16" s="5" t="str">
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z16" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ruth-briones.jpg</v>
       </c>
-      <c r="Y16" s="6" t="s">
+      <c r="AF16" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:32">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -3089,15 +3644,22 @@
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
-      <c r="X17" s="5" t="str">
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-broñola.jpg</v>
       </c>
-      <c r="Y17" s="6" t="s">
+      <c r="AF17" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:32">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -3138,22 +3700,29 @@
         <v>14</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
-      <c r="X18" s="5" t="str">
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cabalda.jpg</v>
       </c>
-      <c r="Y18" s="6" t="s">
+      <c r="AF18" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:32">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -3179,7 +3748,7 @@
         <v>249</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
@@ -3196,22 +3765,29 @@
       <c r="R19" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S19" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="S19" s="6"/>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
-      <c r="X19" s="5" t="str">
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/gracelyn-cabunag.jpg</v>
       </c>
-      <c r="Y19" s="6" t="s">
+      <c r="AF19" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:32">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -3257,19 +3833,26 @@
       <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
-      <c r="V20" s="6">
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6">
         <v>3</v>
       </c>
-      <c r="W20" s="6"/>
-      <c r="X20" s="5" t="str">
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/hector-cabanca.jpg</v>
       </c>
-      <c r="Y20" s="6" t="s">
+      <c r="AF20" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:32">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -3301,7 +3884,7 @@
         <v>354</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -3316,22 +3899,29 @@
       <c r="R21" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S21" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S21" s="6"/>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
-      <c r="X21" s="5" t="str">
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeffrey-caberte.jpg</v>
       </c>
-      <c r="Y21" s="6" t="s">
+      <c r="AF21" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:32">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -3363,7 +3953,7 @@
         <v>355</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -3376,22 +3966,29 @@
         <v>17</v>
       </c>
       <c r="R22" s="6"/>
-      <c r="S22" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
-      <c r="X22" s="5" t="str">
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-cabriana.jpg</v>
       </c>
-      <c r="Y22" s="6" t="s">
+      <c r="AF22" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:32">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -3432,24 +4029,31 @@
         <v>7</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S23" s="6" t="s">
-        <v>364</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S23" s="6"/>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
-      <c r="X23" s="5" t="str">
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jasmin-cabuenas.jpg</v>
       </c>
-      <c r="Y23" s="6" t="s">
+      <c r="AF23" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:32">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -3475,7 +4079,7 @@
         <v>12</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -3492,22 +4096,29 @@
       <c r="R24" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S24" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
-      <c r="X24" s="5" t="str">
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/elsa-calunod.jpg</v>
       </c>
-      <c r="Y24" s="6" t="s">
+      <c r="AF24" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:32">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -3539,7 +4150,7 @@
         <v>352</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -3554,22 +4165,29 @@
       <c r="R25" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S25" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S25" s="6"/>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
-      <c r="X25" s="5" t="str">
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/leslyn-rose-camero.jpg</v>
       </c>
-      <c r="Y25" s="6" t="s">
+      <c r="AF25" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:32">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -3610,24 +4228,31 @@
         <v>17</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>364</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S26" s="6"/>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
-      <c r="X26" s="5" t="str">
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/dawn-camille-caparida.jpg</v>
       </c>
-      <c r="Y26" s="6" t="s">
+      <c r="AF26" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:32">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -3657,7 +4282,7 @@
         <v>354</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -3670,24 +4295,31 @@
         <v>17</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="S27" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="S27" s="6"/>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
-      <c r="X27" s="5" t="str">
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lourence-capa.jpg</v>
       </c>
-      <c r="Y27" s="6" t="s">
+      <c r="AF27" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:32">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -3719,7 +4351,7 @@
         <v>355</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -3734,22 +4366,29 @@
       <c r="R28" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S28" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S28" s="6"/>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
-      <c r="X28" s="5" t="str">
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cavite.jpg</v>
       </c>
-      <c r="Y28" s="6" t="s">
+      <c r="AF28" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="33.6">
+    <row r="29" spans="1:32" ht="33.6">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -3783,7 +4422,7 @@
         <v>356</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -3796,24 +4435,31 @@
         <v>14</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="S29" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="S29" s="6"/>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
-      <c r="X29" s="5" t="str">
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joseph-dagaraga.jpg</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="AF29" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:32">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -3856,22 +4502,29 @@
       <c r="R30" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S30" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S30" s="6"/>
       <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
-      <c r="X30" s="5" t="str">
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carolyn-delos-reyes.jpg</v>
       </c>
-      <c r="Y30" s="6" t="s">
+      <c r="AF30" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:32">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -3914,22 +4567,29 @@
       <c r="R31" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S31" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S31" s="6"/>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
-      <c r="X31" s="5" t="str">
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lucille-echavez.jpg</v>
       </c>
-      <c r="Y31" s="6" t="s">
+      <c r="AF31" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:32">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -3970,24 +4630,31 @@
         <v>14</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="S32" s="6" t="s">
-        <v>365</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="S32" s="6"/>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
       <c r="W32" s="6"/>
-      <c r="X32" s="5" t="str">
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/benerando-erediano.jpg</v>
       </c>
-      <c r="Y32" s="6" t="s">
+      <c r="AF32" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:32">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -4013,7 +4680,7 @@
         <v>244</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
@@ -4030,24 +4697,31 @@
       <c r="R33" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S33" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="S33" s="6"/>
       <c r="T33" s="6"/>
       <c r="U33" s="6"/>
-      <c r="V33" s="6">
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="6">
         <v>4</v>
       </c>
-      <c r="W33" s="6"/>
-      <c r="X33" s="5" t="str">
+      <c r="AD33" s="6"/>
+      <c r="AE33" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/metchie-gay-gastanes.jpg</v>
       </c>
-      <c r="Y33" s="6" t="s">
+      <c r="AF33" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:32">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -4073,7 +4747,7 @@
         <v>12</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
@@ -4090,22 +4764,29 @@
       <c r="R34" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="S34" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="S34" s="6"/>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
       <c r="W34" s="6"/>
-      <c r="X34" s="5" t="str">
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jasmin-gerodias.jpg</v>
       </c>
-      <c r="Y34" s="6" t="s">
+      <c r="AF34" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:32">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4137,7 +4818,7 @@
         <v>353</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
@@ -4152,22 +4833,29 @@
       <c r="R35" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S35" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S35" s="6"/>
       <c r="T35" s="6"/>
       <c r="U35" s="6"/>
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
-      <c r="X35" s="5" t="str">
+      <c r="X35" s="6"/>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA35" s="6"/>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="6"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeralyn-gerra.jpg</v>
       </c>
-      <c r="Y35" s="6" t="s">
+      <c r="AF35" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:32">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -4199,7 +4887,7 @@
         <v>353</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
@@ -4214,22 +4902,29 @@
       <c r="R36" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S36" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S36" s="6"/>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
       <c r="V36" s="6"/>
       <c r="W36" s="6"/>
-      <c r="X36" s="5" t="str">
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/genesa-goc-ong.jpg</v>
       </c>
-      <c r="Y36" s="6" t="s">
+      <c r="AF36" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:32">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -4272,22 +4967,29 @@
       <c r="R37" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S37" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S37" s="6"/>
       <c r="T37" s="6"/>
       <c r="U37" s="6"/>
       <c r="V37" s="6"/>
       <c r="W37" s="6"/>
-      <c r="X37" s="5" t="str">
+      <c r="X37" s="6"/>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="6"/>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/janelou-gomez.jpg</v>
       </c>
-      <c r="Y37" s="6" t="s">
+      <c r="AF37" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:32">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -4319,7 +5021,7 @@
         <v>352</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
@@ -4334,22 +5036,29 @@
       <c r="R38" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S38" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S38" s="6"/>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
-      <c r="X38" s="5" t="str">
+      <c r="X38" s="6"/>
+      <c r="Y38" s="6"/>
+      <c r="Z38" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA38" s="6"/>
+      <c r="AB38" s="6"/>
+      <c r="AC38" s="6"/>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/junnelyn-herbito.jpg</v>
       </c>
-      <c r="Y38" s="6" t="s">
+      <c r="AF38" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:32">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -4381,7 +5090,7 @@
         <v>355</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
@@ -4396,22 +5105,29 @@
       <c r="R39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S39" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S39" s="6"/>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
-      <c r="X39" s="5" t="str">
+      <c r="X39" s="6"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA39" s="6"/>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/roxan-mae-jao.jpg</v>
       </c>
-      <c r="Y39" s="6" t="s">
+      <c r="AF39" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:32">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -4452,22 +5168,29 @@
         <v>17</v>
       </c>
       <c r="R40" s="6"/>
-      <c r="S40" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S40" s="6"/>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
       <c r="V40" s="6"/>
       <c r="W40" s="6"/>
-      <c r="X40" s="5" t="str">
+      <c r="X40" s="6"/>
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA40" s="6"/>
+      <c r="AB40" s="6"/>
+      <c r="AC40" s="6"/>
+      <c r="AD40" s="6"/>
+      <c r="AE40" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/fernando-laspiñas.jpg</v>
       </c>
-      <c r="Y40" s="6" t="s">
+      <c r="AF40" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:32">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -4510,22 +5233,29 @@
       <c r="R41" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S41" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S41" s="6"/>
       <c r="T41" s="6"/>
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
-      <c r="X41" s="5" t="str">
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA41" s="6"/>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="6"/>
+      <c r="AD41" s="6"/>
+      <c r="AE41" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/nerisa-lim.jpg</v>
       </c>
-      <c r="Y41" s="6" t="s">
+      <c r="AF41" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:32">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -4564,22 +5294,29 @@
         <v>17</v>
       </c>
       <c r="R42" s="6"/>
-      <c r="S42" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S42" s="6"/>
       <c r="T42" s="6"/>
       <c r="U42" s="6"/>
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
-      <c r="X42" s="5" t="str">
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carl-loreto.jpg</v>
       </c>
-      <c r="Y42" s="6" t="s">
+      <c r="AF42" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:32">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -4605,7 +5342,7 @@
         <v>270</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
@@ -4620,22 +5357,29 @@
         <v>14</v>
       </c>
       <c r="R43" s="6"/>
-      <c r="S43" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="S43" s="6"/>
       <c r="T43" s="6"/>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
-      <c r="X43" s="5" t="str">
+      <c r="X43" s="6"/>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lyka-mabanag.jpg</v>
       </c>
-      <c r="Y43" s="6" t="s">
+      <c r="AF43" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:32">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -4661,7 +5405,7 @@
         <v>250</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
@@ -4682,22 +5426,29 @@
       <c r="R44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S44" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="S44" s="6"/>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
-      <c r="X44" s="5" t="str">
+      <c r="X44" s="6"/>
+      <c r="Y44" s="6"/>
+      <c r="Z44" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/richie-ryan-mabunay.jpg</v>
       </c>
-      <c r="Y44" s="6" t="s">
+      <c r="AF44" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:32">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -4740,22 +5491,29 @@
       <c r="R45" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S45" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S45" s="6"/>
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
       <c r="V45" s="6"/>
       <c r="W45" s="6"/>
-      <c r="X45" s="5" t="str">
+      <c r="X45" s="6"/>
+      <c r="Y45" s="6"/>
+      <c r="Z45" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA45" s="6"/>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/maria-jeziel-macanin.jpg</v>
       </c>
-      <c r="Y45" s="6" t="s">
+      <c r="AF45" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:32">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -4787,7 +5545,7 @@
         <v>354</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
@@ -4802,22 +5560,29 @@
       <c r="R46" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S46" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="6"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
-      <c r="X46" s="5" t="str">
+      <c r="X46" s="6"/>
+      <c r="Y46" s="6"/>
+      <c r="Z46" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA46" s="6"/>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="6"/>
+      <c r="AD46" s="6"/>
+      <c r="AE46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeralen-maloloy-on.jpg</v>
       </c>
-      <c r="Y46" s="6" t="s">
+      <c r="AF46" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:32">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -4849,7 +5614,7 @@
         <v>352</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
@@ -4864,22 +5629,29 @@
       <c r="R47" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S47" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S47" s="6"/>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
-      <c r="X47" s="5" t="str">
+      <c r="X47" s="6"/>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/elbert-misterio.jpg</v>
       </c>
-      <c r="Y47" s="6" t="s">
+      <c r="AF47" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:32">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -4911,7 +5683,7 @@
         <v>353</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
@@ -4924,22 +5696,29 @@
         <v>17</v>
       </c>
       <c r="R48" s="6"/>
-      <c r="S48" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S48" s="6"/>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
       <c r="V48" s="6"/>
       <c r="W48" s="6"/>
-      <c r="X48" s="5" t="str">
+      <c r="X48" s="6"/>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA48" s="6"/>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="6"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joy-mortal.jpg</v>
       </c>
-      <c r="Y48" s="6" t="s">
+      <c r="AF48" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:32">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -4980,22 +5759,29 @@
         <v>17</v>
       </c>
       <c r="R49" s="6"/>
-      <c r="S49" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S49" s="6"/>
       <c r="T49" s="6"/>
       <c r="U49" s="6"/>
       <c r="V49" s="6"/>
       <c r="W49" s="6"/>
-      <c r="X49" s="5" t="str">
+      <c r="X49" s="6"/>
+      <c r="Y49" s="6"/>
+      <c r="Z49" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA49" s="6"/>
+      <c r="AB49" s="6"/>
+      <c r="AC49" s="6"/>
+      <c r="AD49" s="6"/>
+      <c r="AE49" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/claire-medillo.jpg</v>
       </c>
-      <c r="Y49" s="6" t="s">
+      <c r="AF49" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:32">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -5027,7 +5813,7 @@
         <v>352</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
@@ -5042,22 +5828,29 @@
       <c r="R50" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S50" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S50" s="6"/>
       <c r="T50" s="6"/>
       <c r="U50" s="6"/>
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
-      <c r="X50" s="5" t="str">
+      <c r="X50" s="6"/>
+      <c r="Y50" s="6"/>
+      <c r="Z50" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA50" s="6"/>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="6"/>
+      <c r="AD50" s="6"/>
+      <c r="AE50" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/gwendolyn-olo.jpg</v>
       </c>
-      <c r="Y50" s="6" t="s">
+      <c r="AF50" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:32">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5089,7 +5882,7 @@
         <v>355</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
@@ -5102,22 +5895,29 @@
         <v>17</v>
       </c>
       <c r="R51" s="6"/>
-      <c r="S51" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S51" s="6"/>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6"/>
-      <c r="X51" s="5" t="str">
+      <c r="X51" s="6"/>
+      <c r="Y51" s="6"/>
+      <c r="Z51" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jay-neil-oro.jpg</v>
       </c>
-      <c r="Y51" s="6" t="s">
+      <c r="AF51" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:32">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5149,7 +5949,7 @@
         <v>357</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
@@ -5162,24 +5962,31 @@
         <v>14</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="S52" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="S52" s="6"/>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
-      <c r="X52" s="5" t="str">
+      <c r="X52" s="6"/>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/glendale-orocay.jpg</v>
       </c>
-      <c r="Y52" s="6" t="s">
+      <c r="AF52" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="33.6">
+    <row r="53" spans="1:32" ht="33.6">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -5211,7 +6018,7 @@
         <v>356</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
@@ -5224,24 +6031,31 @@
         <v>17</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="S53" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="S53" s="6"/>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
       <c r="V53" s="6"/>
       <c r="W53" s="6"/>
-      <c r="X53" s="5" t="str">
+      <c r="X53" s="6"/>
+      <c r="Y53" s="6"/>
+      <c r="Z53" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA53" s="6"/>
+      <c r="AB53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AD53" s="6"/>
+      <c r="AE53" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marissa-pintuan.jpg</v>
       </c>
-      <c r="Y53" s="6" t="s">
+      <c r="AF53" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:32">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -5282,24 +6096,31 @@
         <v>17</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="S54" s="6" t="s">
-        <v>369</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="S54" s="6"/>
       <c r="T54" s="6"/>
       <c r="U54" s="6"/>
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
-      <c r="X54" s="5" t="str">
+      <c r="X54" s="6"/>
+      <c r="Y54" s="6"/>
+      <c r="Z54" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA54" s="6"/>
+      <c r="AB54" s="6"/>
+      <c r="AC54" s="6"/>
+      <c r="AD54" s="6"/>
+      <c r="AE54" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ma.-lourdes-prajes.jpg</v>
       </c>
-      <c r="Y54" s="6" t="s">
+      <c r="AF54" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:32">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -5331,7 +6152,7 @@
         <v>353</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
@@ -5344,22 +6165,29 @@
         <v>17</v>
       </c>
       <c r="R55" s="6"/>
-      <c r="S55" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S55" s="6"/>
       <c r="T55" s="6"/>
       <c r="U55" s="6"/>
       <c r="V55" s="6"/>
       <c r="W55" s="6"/>
-      <c r="X55" s="5" t="str">
+      <c r="X55" s="6"/>
+      <c r="Y55" s="6"/>
+      <c r="Z55" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA55" s="6"/>
+      <c r="AB55" s="6"/>
+      <c r="AC55" s="6"/>
+      <c r="AD55" s="6"/>
+      <c r="AE55" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/bret-kalvin-primacio.jpg</v>
       </c>
-      <c r="Y55" s="6" t="s">
+      <c r="AF55" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:32">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5402,22 +6230,29 @@
       <c r="R56" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S56" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S56" s="6"/>
       <c r="T56" s="6"/>
       <c r="U56" s="6"/>
       <c r="V56" s="6"/>
       <c r="W56" s="6"/>
-      <c r="X56" s="5" t="str">
+      <c r="X56" s="6"/>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA56" s="6"/>
+      <c r="AB56" s="6"/>
+      <c r="AC56" s="6"/>
+      <c r="AD56" s="6"/>
+      <c r="AE56" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jhea-quiling.jpg</v>
       </c>
-      <c r="Y56" s="6" t="s">
+      <c r="AF56" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:32">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5460,22 +6295,29 @@
       <c r="R57" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S57" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S57" s="6"/>
       <c r="T57" s="6"/>
       <c r="U57" s="6"/>
       <c r="V57" s="6"/>
       <c r="W57" s="6"/>
-      <c r="X57" s="5" t="str">
+      <c r="X57" s="6"/>
+      <c r="Y57" s="6"/>
+      <c r="Z57" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA57" s="6"/>
+      <c r="AB57" s="6"/>
+      <c r="AC57" s="6"/>
+      <c r="AD57" s="6"/>
+      <c r="AE57" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joyce-racaza.jpg</v>
       </c>
-      <c r="Y57" s="6" t="s">
+      <c r="AF57" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:32">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -5518,22 +6360,29 @@
       <c r="R58" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="S58" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S58" s="6"/>
       <c r="T58" s="6"/>
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
-      <c r="X58" s="5" t="str">
+      <c r="X58" s="6"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA58" s="6"/>
+      <c r="AB58" s="6"/>
+      <c r="AC58" s="6"/>
+      <c r="AD58" s="6"/>
+      <c r="AE58" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/cromwell-retuya.jpg</v>
       </c>
-      <c r="Y58" s="6" t="s">
+      <c r="AF58" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:32">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -5559,7 +6408,7 @@
         <v>12</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
@@ -5574,26 +6423,33 @@
         <v>17</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="S59" s="6" t="s">
-        <v>367</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="S59" s="6"/>
       <c r="T59" s="6"/>
       <c r="U59" s="6"/>
-      <c r="V59" s="6">
+      <c r="V59" s="6"/>
+      <c r="W59" s="6"/>
+      <c r="X59" s="6"/>
+      <c r="Y59" s="6"/>
+      <c r="Z59" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="AA59" s="6"/>
+      <c r="AB59" s="6"/>
+      <c r="AC59" s="6">
         <v>5</v>
       </c>
-      <c r="W59" s="6"/>
-      <c r="X59" s="5" t="str">
+      <c r="AD59" s="6"/>
+      <c r="AE59" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/nancy-reyes.jpg</v>
       </c>
-      <c r="Y59" s="6" t="s">
+      <c r="AF59" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:32">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -5625,7 +6481,7 @@
         <v>354</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
@@ -5638,22 +6494,29 @@
         <v>17</v>
       </c>
       <c r="R60" s="6"/>
-      <c r="S60" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S60" s="6"/>
       <c r="T60" s="6"/>
       <c r="U60" s="6"/>
       <c r="V60" s="6"/>
       <c r="W60" s="6"/>
-      <c r="X60" s="5" t="str">
+      <c r="X60" s="6"/>
+      <c r="Y60" s="6"/>
+      <c r="Z60" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA60" s="6"/>
+      <c r="AB60" s="6"/>
+      <c r="AC60" s="6"/>
+      <c r="AD60" s="6"/>
+      <c r="AE60" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/angelo-saavedra.jpg</v>
       </c>
-      <c r="Y60" s="6" t="s">
+      <c r="AF60" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:32">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -5679,7 +6542,7 @@
         <v>244</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
@@ -5694,24 +6557,31 @@
         <v>17</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="S61" s="6" t="s">
-        <v>365</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="S61" s="6"/>
       <c r="T61" s="6"/>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
       <c r="W61" s="6"/>
-      <c r="X61" s="5" t="str">
+      <c r="X61" s="6"/>
+      <c r="Y61" s="6"/>
+      <c r="Z61" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA61" s="6"/>
+      <c r="AB61" s="6"/>
+      <c r="AC61" s="6"/>
+      <c r="AD61" s="6"/>
+      <c r="AE61" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/brendel-sacaris.jpg</v>
       </c>
-      <c r="Y61" s="6" t="s">
+      <c r="AF61" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:32">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5743,7 +6613,7 @@
         <v>354</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
@@ -5756,22 +6626,29 @@
         <v>17</v>
       </c>
       <c r="R62" s="6"/>
-      <c r="S62" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S62" s="6"/>
       <c r="T62" s="6"/>
       <c r="U62" s="6"/>
       <c r="V62" s="6"/>
       <c r="W62" s="6"/>
-      <c r="X62" s="5" t="str">
+      <c r="X62" s="6"/>
+      <c r="Y62" s="6"/>
+      <c r="Z62" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA62" s="6"/>
+      <c r="AB62" s="6"/>
+      <c r="AC62" s="6"/>
+      <c r="AD62" s="6"/>
+      <c r="AE62" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C62&amp;" "&amp;B62)," ","-"))&amp;".jpg"</f>
         <v>/personnel/bella-arquine-samontañez.jpg</v>
       </c>
-      <c r="Y62" s="6" t="s">
+      <c r="AF62" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:32">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -5803,7 +6680,7 @@
         <v>357</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
@@ -5818,22 +6695,29 @@
       <c r="R63" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S63" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="S63" s="6"/>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
-      <c r="X63" s="5" t="str">
+      <c r="X63" s="6"/>
+      <c r="Y63" s="6"/>
+      <c r="Z63" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA63" s="6"/>
+      <c r="AB63" s="6"/>
+      <c r="AC63" s="6"/>
+      <c r="AD63" s="6"/>
+      <c r="AE63" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jevy-ann-uy.jpg</v>
       </c>
-      <c r="Y63" s="6" t="s">
+      <c r="AF63" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:32">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -5859,7 +6743,7 @@
         <v>12</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
@@ -5876,22 +6760,29 @@
       <c r="R64" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S64" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="S64" s="6"/>
       <c r="T64" s="6"/>
       <c r="U64" s="6"/>
       <c r="V64" s="6"/>
       <c r="W64" s="6"/>
-      <c r="X64" s="5" t="str">
+      <c r="X64" s="6"/>
+      <c r="Y64" s="6"/>
+      <c r="Z64" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA64" s="6"/>
+      <c r="AB64" s="6"/>
+      <c r="AC64" s="6"/>
+      <c r="AD64" s="6"/>
+      <c r="AE64" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/grace-vergara.jpg</v>
       </c>
-      <c r="Y64" s="6" t="s">
+      <c r="AF64" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:32">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -5932,24 +6823,31 @@
         <v>7</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S65" s="6" t="s">
-        <v>271</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S65" s="6"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
       <c r="V65" s="6"/>
       <c r="W65" s="6"/>
-      <c r="X65" s="5" t="str">
+      <c r="X65" s="6"/>
+      <c r="Y65" s="6"/>
+      <c r="Z65" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA65" s="6"/>
+      <c r="AB65" s="6"/>
+      <c r="AC65" s="6"/>
+      <c r="AD65" s="6"/>
+      <c r="AE65" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/guillermo-villavelez.jpg</v>
       </c>
-      <c r="Y65" s="6" t="s">
+      <c r="AF65" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:32">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -5992,22 +6890,29 @@
       <c r="R66" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S66" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="S66" s="6"/>
       <c r="T66" s="6"/>
       <c r="U66" s="6"/>
       <c r="V66" s="6"/>
       <c r="W66" s="6"/>
-      <c r="X66" s="5" t="str">
+      <c r="X66" s="6"/>
+      <c r="Y66" s="6"/>
+      <c r="Z66" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AA66" s="6"/>
+      <c r="AB66" s="6"/>
+      <c r="AC66" s="6"/>
+      <c r="AD66" s="6"/>
+      <c r="AE66" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-villaver.jpg</v>
       </c>
-      <c r="Y66" s="6" t="s">
+      <c r="AF66" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:32">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -6048,24 +6953,31 @@
         <v>371</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S67" s="6" t="s">
-        <v>370</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S67" s="6"/>
       <c r="T67" s="6"/>
       <c r="U67" s="6"/>
       <c r="V67" s="6"/>
       <c r="W67" s="6"/>
-      <c r="X67" s="5" t="str">
-        <f t="shared" ref="X67:X68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
+      <c r="X67" s="6"/>
+      <c r="Y67" s="6"/>
+      <c r="Z67" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA67" s="6"/>
+      <c r="AB67" s="6"/>
+      <c r="AC67" s="6"/>
+      <c r="AD67" s="6"/>
+      <c r="AE67" s="5" t="str">
+        <f t="shared" ref="AE67:AE68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
         <v>/personnel/markjil-bacaltos.jpg</v>
       </c>
-      <c r="Y67" s="6" t="s">
+      <c r="AF67" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:32">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -6106,24 +7018,31 @@
         <v>371</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S68" s="6" t="s">
-        <v>370</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S68" s="6"/>
       <c r="T68" s="6"/>
       <c r="U68" s="6"/>
       <c r="V68" s="6"/>
       <c r="W68" s="6"/>
-      <c r="X68" s="5" t="str">
+      <c r="X68" s="6"/>
+      <c r="Y68" s="6"/>
+      <c r="Z68" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA68" s="6"/>
+      <c r="AB68" s="6"/>
+      <c r="AC68" s="6"/>
+      <c r="AD68" s="6"/>
+      <c r="AE68" s="5" t="str">
         <f t="shared" si="8"/>
         <v>/personnel/diocel-celocia.jpg</v>
       </c>
-      <c r="Y68" s="6" t="s">
+      <c r="AF68" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:32">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -6164,24 +7083,31 @@
         <v>371</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S69" s="6" t="s">
-        <v>370</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S69" s="6"/>
       <c r="T69" s="6"/>
       <c r="U69" s="6"/>
       <c r="V69" s="6"/>
       <c r="W69" s="6"/>
-      <c r="X69" s="5" t="str">
-        <f t="shared" ref="X69:X70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
+      <c r="X69" s="6"/>
+      <c r="Y69" s="6"/>
+      <c r="Z69" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA69" s="6"/>
+      <c r="AB69" s="6"/>
+      <c r="AC69" s="6"/>
+      <c r="AD69" s="6"/>
+      <c r="AE69" s="5" t="str">
+        <f t="shared" ref="AE69:AE70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
         <v>/personnel/luie-cabs.jpg</v>
       </c>
-      <c r="Y69" s="6" t="s">
+      <c r="AF69" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:32">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -6222,24 +7148,31 @@
         <v>371</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S70" s="6" t="s">
-        <v>370</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="S70" s="6"/>
       <c r="T70" s="6"/>
       <c r="U70" s="6"/>
       <c r="V70" s="6"/>
       <c r="W70" s="6"/>
-      <c r="X70" s="5" t="str">
+      <c r="X70" s="6"/>
+      <c r="Y70" s="6"/>
+      <c r="Z70" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA70" s="6"/>
+      <c r="AB70" s="6"/>
+      <c r="AC70" s="6"/>
+      <c r="AD70" s="6"/>
+      <c r="AE70" s="5" t="str">
         <f t="shared" si="11"/>
         <v>/personnel/luis-mans.jpg</v>
       </c>
-      <c r="Y70" s="6" t="s">
+      <c r="AF70" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:32">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -6268,8 +7201,15 @@
       <c r="U71" s="6"/>
       <c r="V71" s="6"/>
       <c r="W71" s="6"/>
-      <c r="X71" s="5"/>
+      <c r="X71" s="6"/>
       <c r="Y71" s="6"/>
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6"/>
+      <c r="AB71" s="6"/>
+      <c r="AC71" s="6"/>
+      <c r="AD71" s="6"/>
+      <c r="AE71" s="5"/>
+      <c r="AF71" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -6302,19 +7242,19 @@
           <x14:formula1>
             <xm:f>Dropdown_Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y71</xm:sqref>
+          <xm:sqref>AF2:AF71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70D54F6E-2A67-40F0-92CA-B6E53F44843D}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$D$2:$D$61</xm:f>
           </x14:formula1>
-          <xm:sqref>S2:S71</xm:sqref>
+          <xm:sqref>Z2:Z71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7834D497-9733-4178-89DF-4B7895726F53}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$E$2:$E$60</xm:f>
           </x14:formula1>
-          <xm:sqref>T2:T71</xm:sqref>
+          <xm:sqref>AA2:AA71</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFE0AE0-5E41-4065-B58F-FE70AA82722B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C289C-C94D-47D0-869F-434C983C10DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="21300" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="21315" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="482">
   <si>
     <t>order</t>
   </si>
@@ -1198,9 +1198,6 @@
     <t>EPP</t>
   </si>
   <si>
-    <t>Electronic Product Assembly and Servicing</t>
-  </si>
-  <si>
     <t>Hairdressing/Beauty Care</t>
   </si>
   <si>
@@ -1460,6 +1457,30 @@
   </si>
   <si>
     <t>English 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>Guidance and Student Support</t>
+  </si>
+  <si>
+    <t>Electronic Products Assembly and Servicing</t>
+  </si>
+  <si>
+    <t>Technical-Vocational-Livelihood (TVL)</t>
+  </si>
+  <si>
+    <t>Technology and Livelihood Education (TLE)</t>
+  </si>
+  <si>
+    <t>SubjectDepartment2</t>
+  </si>
+  <si>
+    <t>SubjectDepartment3</t>
+  </si>
+  <si>
+    <t>SubjectDepartment4</t>
+  </si>
+  <si>
+    <t>SubjectDepartment5</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1586,110 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1698,33 +1822,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2145,44 +2242,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:AF71" headerRowDxfId="34" dataDxfId="33" totalsRowDxfId="32">
-  <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:AJ71" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="36">
+  <tableColumns count="36">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{AF2D5150-6C8E-4586-A045-6EA7C80A524C}" name="firstName" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{DEB63105-4C35-428E-B5D1-A14E3164B3DA}" name="middleName" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{CFE5C25B-9704-4E8F-ACBC-C9336567385E}" name="middleInitial" dataDxfId="31">
       <calculatedColumnFormula>IF(D2="","",LEFT(TRIM(D2),1)&amp;".")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="25">
+    <tableColumn id="9" xr3:uid="{C15E3D36-7D44-4129-AD8E-8A7781CC6A93}" name="suffix" dataDxfId="30"/>
+    <tableColumn id="13" xr3:uid="{1E3C14F7-2268-499C-B881-A1FE0A7127D7}" name="displayName" dataDxfId="29">
       <calculatedColumnFormula>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="24"/>
-    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="22"/>
-    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="14"/>
-    <tableColumn id="26" xr3:uid="{9234D872-27E9-4981-9849-3B92B3D703D7}" name="primarySubjectDepartment" dataDxfId="6"/>
-    <tableColumn id="27" xr3:uid="{BAF0BAF6-D68C-494F-94BF-9DBEAC627028}" name="subject1" dataDxfId="5"/>
-    <tableColumn id="28" xr3:uid="{8B540991-2968-4F70-8AAC-FCFC355A419A}" name="subject2" dataDxfId="4"/>
-    <tableColumn id="29" xr3:uid="{1D6F7D4B-4E56-4246-A153-8FAB0BEB4811}" name="subject3" dataDxfId="3"/>
-    <tableColumn id="30" xr3:uid="{E295C211-F74A-4E2B-893A-E9FDF18B7EE9}" name="subject4" dataDxfId="2"/>
-    <tableColumn id="31" xr3:uid="{B93E7C74-87A6-4CBE-9E54-1C7E4E717375}" name="subject5" dataDxfId="1"/>
-    <tableColumn id="32" xr3:uid="{AE0F403C-1544-4D9E-929C-27676144B2E2}" name="teachingLevel" dataDxfId="0"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="position" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{871D5899-2C99-449D-AE1E-5492B1075D69}" name="designation1" dataDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{9E70E31F-1B17-4E67-A99E-4037A94153C1}" name="advisoryGradeLevel" dataDxfId="26"/>
+    <tableColumn id="25" xr3:uid="{82F63A8C-E0AF-4172-B1EB-CC758DA39858}" name="advisorySection" dataDxfId="25"/>
+    <tableColumn id="15" xr3:uid="{F4F0A446-7DFB-4099-8C3C-39E5D7D48BD0}" name="designation2" dataDxfId="24"/>
+    <tableColumn id="16" xr3:uid="{9D4F6523-1087-480E-82D3-17DF6BB11D95}" name="designation3" dataDxfId="23"/>
+    <tableColumn id="18" xr3:uid="{30162747-79C9-4043-9391-B8B420E4C626}" name="designation4" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{820C0CC6-055B-4F59-A5A5-608142530FDE}" name="otherDesignations" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="category" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="18"/>
+    <tableColumn id="26" xr3:uid="{9234D872-27E9-4981-9849-3B92B3D703D7}" name="primarySubjectDepartment" dataDxfId="17"/>
+    <tableColumn id="34" xr3:uid="{168EB6BE-8B21-4305-ABC1-174562CD0A0B}" name="SubjectDepartment2" dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{5C2FF8F3-D884-43D6-84E1-D482E29A632A}" name="SubjectDepartment3" dataDxfId="2"/>
+    <tableColumn id="36" xr3:uid="{9BC6D117-EABD-4BEC-9C2D-4F49F4E8F4AF}" name="SubjectDepartment4" dataDxfId="1"/>
+    <tableColumn id="37" xr3:uid="{C21080E4-B7D1-416D-9C89-C64670FF6EAA}" name="SubjectDepartment5" dataDxfId="0"/>
+    <tableColumn id="27" xr3:uid="{BAF0BAF6-D68C-494F-94BF-9DBEAC627028}" name="subject1" dataDxfId="16"/>
+    <tableColumn id="28" xr3:uid="{8B540991-2968-4F70-8AAC-FCFC355A419A}" name="subject2" dataDxfId="15"/>
+    <tableColumn id="29" xr3:uid="{1D6F7D4B-4E56-4246-A153-8FAB0BEB4811}" name="subject3" dataDxfId="14"/>
+    <tableColumn id="30" xr3:uid="{E295C211-F74A-4E2B-893A-E9FDF18B7EE9}" name="subject4" dataDxfId="13"/>
+    <tableColumn id="31" xr3:uid="{B93E7C74-87A6-4CBE-9E54-1C7E4E717375}" name="subject5" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{AE0F403C-1544-4D9E-929C-27676144B2E2}" name="teachingLevel" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2337,17 +2438,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF71"/>
+  <dimension ref="A1:AJ71"/>
   <sheetFormatPr defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.09765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.8984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.3984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.296875" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.3984375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="23.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.69921875" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40.796875" style="11" customWidth="1"/>
     <col min="10" max="10" width="19.296875" style="11" customWidth="1"/>
     <col min="11" max="11" width="17.296875" style="11" customWidth="1"/>
@@ -2356,14 +2457,14 @@
     <col min="15" max="15" width="32.8984375" style="4" customWidth="1"/>
     <col min="16" max="16" width="26.69921875" style="4" customWidth="1"/>
     <col min="17" max="17" width="20.09765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="25" width="45.19921875" style="7" customWidth="1"/>
-    <col min="26" max="30" width="24.19921875" style="7" customWidth="1"/>
-    <col min="31" max="31" width="36.69921875" style="4" customWidth="1"/>
-    <col min="32" max="32" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="8.796875" style="4"/>
+    <col min="18" max="29" width="45.19921875" style="7" customWidth="1"/>
+    <col min="30" max="34" width="24.19921875" style="7" customWidth="1"/>
+    <col min="35" max="35" width="36.69921875" style="4" customWidth="1"/>
+    <col min="36" max="36" width="6.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="8.796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:36" ht="39" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2392,10 +2493,10 @@
         <v>324</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>394</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>395</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>325</v>
@@ -2419,49 +2520,61 @@
         <v>4</v>
       </c>
       <c r="S1" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="X1" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="Y1" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AF1" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AG1" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AH1" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AI1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:36">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2507,34 +2620,38 @@
       <c r="S2" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="T2" s="6" t="s">
-        <v>426</v>
-      </c>
+      <c r="T2" s="6"/>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>366</v>
-      </c>
+      <c r="X2" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
-      <c r="AC2" s="6">
+      <c r="AC2" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6">
         <v>2</v>
       </c>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="5" t="str">
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
         <v>/personnel/paz-abad.jpg</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:36">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2566,7 +2683,7 @@
         <v>353</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -2584,36 +2701,40 @@
       <c r="S3" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="T3" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="U3" s="6" t="s">
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="Z3" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="AA3" s="6"/>
       <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="5" t="str">
-        <f t="shared" ref="AE3:AE66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
+      <c r="AC3" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="5" t="str">
+        <f t="shared" ref="AI3:AI66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
         <v>/personnel/marissa-abalo.jpg</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AJ3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:36">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2639,7 +2760,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
@@ -2659,32 +2780,36 @@
       <c r="S4" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="T4" s="6" t="s">
-        <v>463</v>
-      </c>
+      <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="X4" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
       <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="5" t="str">
+      <c r="AC4" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD4" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joseph-allosada.jpg</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AJ4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="33.6">
+    <row r="5" spans="1:36" ht="33.6">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2716,13 +2841,13 @@
         <v>355</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L5" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>440</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>441</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -2738,34 +2863,38 @@
       <c r="S5" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="T5" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>436</v>
-      </c>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
+      <c r="X5" s="6" t="s">
+        <v>441</v>
+      </c>
       <c r="Y5" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="Z5" s="6"/>
       <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="5" t="str">
+      <c r="AC5" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD5" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6"/>
+      <c r="AI5" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-gay-alsa.jpg</v>
       </c>
-      <c r="AF5" s="6" t="s">
+      <c r="AJ5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="33.6">
+    <row r="6" spans="1:36" ht="33.6">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2797,7 +2926,7 @@
         <v>356</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -2810,39 +2939,43 @@
         <v>14</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="T6" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="U6" s="6" t="s">
-        <v>445</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
+      <c r="X6" s="6" t="s">
+        <v>443</v>
+      </c>
       <c r="Y6" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="Z6" s="6"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="5" t="str">
+      <c r="AC6" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD6" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lonier-andrade.jpg</v>
       </c>
-      <c r="AF6" s="6" t="s">
+      <c r="AJ6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:36">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2874,13 +3007,13 @@
         <v>354</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L7" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="M7" s="5" t="s">
         <v>446</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>447</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -2894,34 +3027,38 @@
         <v>344</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>461</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="T7" s="6"/>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="X7" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
       <c r="AA7" s="6"/>
       <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="5" t="str">
+      <c r="AC7" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD7" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/allan-raul-aparicio.jpg</v>
       </c>
-      <c r="AF7" s="6" t="s">
+      <c r="AJ7" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:36">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2969,22 +3106,26 @@
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
-      <c r="Z8" s="6" t="s">
-        <v>364</v>
-      </c>
+      <c r="Z8" s="6"/>
       <c r="AA8" s="6"/>
       <c r="AB8" s="6"/>
       <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="5" t="str">
+      <c r="AD8" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/niña-kristine-ayos.jpg</v>
       </c>
-      <c r="AF8" s="6" t="s">
+      <c r="AJ8" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:36">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -3010,12 +3151,12 @@
         <v>244</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -3030,34 +3171,38 @@
         <v>344</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>462</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="T9" s="6"/>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>368</v>
-      </c>
+      <c r="X9" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="5" t="str">
+      <c r="AC9" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD9" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="6"/>
+      <c r="AI9" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/glenn-barangan.jpg</v>
       </c>
-      <c r="AF9" s="6" t="s">
+      <c r="AJ9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:36">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -3089,13 +3234,13 @@
         <v>355</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L10" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>450</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>451</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
@@ -3111,32 +3256,36 @@
       <c r="S10" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="T10" s="6" t="s">
-        <v>452</v>
-      </c>
+      <c r="T10" s="6"/>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="X10" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
       <c r="AA10" s="6"/>
       <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="5" t="str">
+      <c r="AC10" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jake-barcenas.jpg</v>
       </c>
-      <c r="AF10" s="6" t="s">
+      <c r="AJ10" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:36">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -3168,10 +3317,10 @@
         <v>353</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -3188,32 +3337,36 @@
       <c r="S11" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="T11" s="6" t="s">
-        <v>454</v>
-      </c>
+      <c r="T11" s="6"/>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z11" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="X11" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
       <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="5" t="str">
+      <c r="AC11" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD11" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/eljoy-barroca.jpg</v>
       </c>
-      <c r="AF11" s="6" t="s">
+      <c r="AJ11" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="33.6">
+    <row r="12" spans="1:36" ht="33.6">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -3245,13 +3398,13 @@
         <v>357</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L12" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>456</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -3265,36 +3418,40 @@
         <v>342</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="T12" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="U12" s="6" t="s">
-        <v>459</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
+      <c r="X12" s="6" t="s">
+        <v>457</v>
+      </c>
       <c r="Y12" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="Z12" s="6"/>
       <c r="AA12" s="6"/>
       <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="5" t="str">
+      <c r="AC12" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD12" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/angel-batuigas.jpg</v>
       </c>
-      <c r="AF12" s="6" t="s">
+      <c r="AJ12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:36">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -3320,7 +3477,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -3340,32 +3497,36 @@
       <c r="S13" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="T13" s="6" t="s">
-        <v>464</v>
-      </c>
+      <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z13" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="X13" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
       <c r="AB13" s="6"/>
-      <c r="AC13" s="6"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="5" t="str">
+      <c r="AC13" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD13" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/mary-josephine-bawiga.jpg</v>
       </c>
-      <c r="AF13" s="6" t="s">
+      <c r="AJ13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:36">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -3397,10 +3558,10 @@
         <v>352</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -3417,34 +3578,38 @@
       <c r="S14" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="T14" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="U14" s="6" t="s">
-        <v>466</v>
-      </c>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
+      <c r="X14" s="6" t="s">
+        <v>466</v>
+      </c>
       <c r="Y14" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
-      <c r="AE14" s="5" t="str">
+      <c r="AC14" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD14" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/endrie-bohol.jpg</v>
       </c>
-      <c r="AF14" s="6" t="s">
+      <c r="AJ14" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="33.6">
+    <row r="15" spans="1:36" ht="33.6">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -3475,10 +3640,10 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>468</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>469</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -3494,36 +3659,40 @@
       <c r="S15" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="T15" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="U15" s="6" t="s">
-        <v>471</v>
-      </c>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
+      <c r="X15" s="6" t="s">
+        <v>469</v>
+      </c>
       <c r="Y15" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z15" s="6" t="s">
-        <v>365</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="Z15" s="6"/>
       <c r="AA15" s="6"/>
       <c r="AB15" s="6"/>
-      <c r="AC15" s="6">
+      <c r="AC15" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD15" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
+      <c r="AG15" s="6">
         <v>1</v>
       </c>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="5" t="str">
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/maine-bongas.jpg</v>
       </c>
-      <c r="AF15" s="6" t="s">
+      <c r="AJ15" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="33.6">
+    <row r="16" spans="1:36" ht="33.6">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -3553,10 +3722,10 @@
         <v>352</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -3573,34 +3742,38 @@
       <c r="S16" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="T16" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="U16" s="6" t="s">
-        <v>474</v>
-      </c>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
+      <c r="X16" s="6" t="s">
+        <v>472</v>
+      </c>
       <c r="Y16" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="Z16" s="6" t="s">
-        <v>277</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
       <c r="AB16" s="6"/>
-      <c r="AC16" s="6"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="5" t="str">
+      <c r="AC16" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD16" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
+      <c r="AG16" s="6"/>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ruth-briones.jpg</v>
       </c>
-      <c r="AF16" s="6" t="s">
+      <c r="AJ16" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:36">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -3651,15 +3824,19 @@
       <c r="AB17" s="6"/>
       <c r="AC17" s="6"/>
       <c r="AD17" s="6"/>
-      <c r="AE17" s="5" t="str">
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-broñola.jpg</v>
       </c>
-      <c r="AF17" s="6" t="s">
+      <c r="AJ17" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:36">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -3702,7 +3879,9 @@
       <c r="R18" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S18" s="6"/>
+      <c r="S18" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
@@ -3714,15 +3893,19 @@
       <c r="AB18" s="6"/>
       <c r="AC18" s="6"/>
       <c r="AD18" s="6"/>
-      <c r="AE18" s="5" t="str">
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cabalda.jpg</v>
       </c>
-      <c r="AF18" s="6" t="s">
+      <c r="AJ18" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:36">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -3765,29 +3948,35 @@
       <c r="R19" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S19" s="6"/>
+      <c r="S19" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
-      <c r="Z19" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="5" t="str">
+      <c r="AD19" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
+      <c r="AG19" s="6"/>
+      <c r="AH19" s="6"/>
+      <c r="AI19" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/gracelyn-cabunag.jpg</v>
       </c>
-      <c r="AF19" s="6" t="s">
+      <c r="AJ19" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:36">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -3830,7 +4019,9 @@
       <c r="R20" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S20" s="6"/>
+      <c r="S20" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
@@ -3840,19 +4031,23 @@
       <c r="Z20" s="6"/>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="6">
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="6">
         <v>3</v>
       </c>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="5" t="str">
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/hector-cabanca.jpg</v>
       </c>
-      <c r="AF20" s="6" t="s">
+      <c r="AJ20" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:36">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -3884,7 +4079,7 @@
         <v>354</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -3899,29 +4094,35 @@
       <c r="R21" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S21" s="6"/>
+      <c r="S21" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
-      <c r="Z21" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z21" s="6"/>
       <c r="AA21" s="6"/>
       <c r="AB21" s="6"/>
       <c r="AC21" s="6"/>
-      <c r="AD21" s="6"/>
-      <c r="AE21" s="5" t="str">
+      <c r="AD21" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="6"/>
+      <c r="AI21" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeffrey-caberte.jpg</v>
       </c>
-      <c r="AF21" s="6" t="s">
+      <c r="AJ21" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:36">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -3953,7 +4154,7 @@
         <v>355</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -3973,22 +4174,26 @@
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
-      <c r="Z22" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z22" s="6"/>
       <c r="AA22" s="6"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="5" t="str">
+      <c r="AD22" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6"/>
+      <c r="AI22" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-cabriana.jpg</v>
       </c>
-      <c r="AF22" s="6" t="s">
+      <c r="AJ22" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:36">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -4031,29 +4236,35 @@
       <c r="R23" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S23" s="6"/>
+      <c r="S23" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
-      <c r="Z23" s="6" t="s">
-        <v>364</v>
-      </c>
+      <c r="Z23" s="6"/>
       <c r="AA23" s="6"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
-      <c r="AD23" s="6"/>
-      <c r="AE23" s="5" t="str">
+      <c r="AD23" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jasmin-cabuenas.jpg</v>
       </c>
-      <c r="AF23" s="6" t="s">
+      <c r="AJ23" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:36">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -4079,7 +4290,7 @@
         <v>12</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -4096,29 +4307,35 @@
       <c r="R24" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S24" s="6"/>
+      <c r="S24" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
       <c r="Y24" s="6"/>
-      <c r="Z24" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z24" s="6"/>
       <c r="AA24" s="6"/>
       <c r="AB24" s="6"/>
       <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="5" t="str">
+      <c r="AD24" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/elsa-calunod.jpg</v>
       </c>
-      <c r="AF24" s="6" t="s">
+      <c r="AJ24" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:36">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -4150,7 +4367,7 @@
         <v>352</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -4165,29 +4382,35 @@
       <c r="R25" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S25" s="6"/>
+      <c r="S25" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
       <c r="Y25" s="6"/>
-      <c r="Z25" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z25" s="6"/>
       <c r="AA25" s="6"/>
       <c r="AB25" s="6"/>
       <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="5" t="str">
+      <c r="AD25" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6"/>
+      <c r="AI25" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/leslyn-rose-camero.jpg</v>
       </c>
-      <c r="AF25" s="6" t="s">
+      <c r="AJ25" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:36">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -4230,29 +4453,35 @@
       <c r="R26" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S26" s="6"/>
+      <c r="S26" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
       <c r="X26" s="6"/>
       <c r="Y26" s="6"/>
-      <c r="Z26" s="6" t="s">
-        <v>364</v>
-      </c>
+      <c r="Z26" s="6"/>
       <c r="AA26" s="6"/>
       <c r="AB26" s="6"/>
       <c r="AC26" s="6"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="5" t="str">
+      <c r="AD26" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/dawn-camille-caparida.jpg</v>
       </c>
-      <c r="AF26" s="6" t="s">
+      <c r="AJ26" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:36">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -4282,7 +4511,7 @@
         <v>354</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -4297,29 +4526,35 @@
       <c r="R27" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="S27" s="6"/>
+      <c r="S27" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="6"/>
-      <c r="Z27" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z27" s="6"/>
       <c r="AA27" s="6"/>
       <c r="AB27" s="6"/>
       <c r="AC27" s="6"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="5" t="str">
+      <c r="AD27" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="6"/>
+      <c r="AI27" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lourence-capa.jpg</v>
       </c>
-      <c r="AF27" s="6" t="s">
+      <c r="AJ27" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:36">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -4351,7 +4586,7 @@
         <v>355</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -4366,29 +4601,35 @@
       <c r="R28" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S28" s="6"/>
+      <c r="S28" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
-      <c r="Z28" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z28" s="6"/>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="5" t="str">
+      <c r="AD28" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cavite.jpg</v>
       </c>
-      <c r="AF28" s="6" t="s">
+      <c r="AJ28" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:32" ht="33.6">
+    <row r="29" spans="1:36" ht="33.6">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -4422,7 +4663,7 @@
         <v>356</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -4444,22 +4685,26 @@
       <c r="W29" s="6"/>
       <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
-      <c r="Z29" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z29" s="6"/>
       <c r="AA29" s="6"/>
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
-      <c r="AD29" s="6"/>
-      <c r="AE29" s="5" t="str">
+      <c r="AD29" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="6"/>
+      <c r="AI29" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joseph-dagaraga.jpg</v>
       </c>
-      <c r="AF29" s="6" t="s">
+      <c r="AJ29" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:36">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -4503,28 +4748,34 @@
         <v>342</v>
       </c>
       <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
+      <c r="T30" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
       <c r="X30" s="6"/>
       <c r="Y30" s="6"/>
-      <c r="Z30" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z30" s="6"/>
       <c r="AA30" s="6"/>
       <c r="AB30" s="6"/>
       <c r="AC30" s="6"/>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="5" t="str">
+      <c r="AD30" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6"/>
+      <c r="AI30" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carolyn-delos-reyes.jpg</v>
       </c>
-      <c r="AF30" s="6" t="s">
+      <c r="AJ30" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:36">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -4567,29 +4818,37 @@
       <c r="R31" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S31" s="6"/>
+      <c r="S31" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
       <c r="X31" s="6"/>
       <c r="Y31" s="6"/>
-      <c r="Z31" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z31" s="6"/>
       <c r="AA31" s="6"/>
       <c r="AB31" s="6"/>
-      <c r="AC31" s="6"/>
-      <c r="AD31" s="6"/>
-      <c r="AE31" s="5" t="str">
+      <c r="AC31" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD31" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="6"/>
+      <c r="AI31" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lucille-echavez.jpg</v>
       </c>
-      <c r="AF31" s="6" t="s">
+      <c r="AJ31" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:36">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -4630,31 +4889,41 @@
         <v>14</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="S32" s="6"/>
+        <v>345</v>
+      </c>
+      <c r="S32" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
       <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
+      <c r="X32" s="6" t="s">
+        <v>475</v>
+      </c>
       <c r="Y32" s="6"/>
-      <c r="Z32" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z32" s="6"/>
       <c r="AA32" s="6"/>
       <c r="AB32" s="6"/>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="5" t="str">
+      <c r="AC32" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD32" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/benerando-erediano.jpg</v>
       </c>
-      <c r="AF32" s="6" t="s">
+      <c r="AJ32" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:36">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -4680,7 +4949,7 @@
         <v>244</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
@@ -4697,31 +4966,37 @@
       <c r="R33" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S33" s="6"/>
+      <c r="S33" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T33" s="6"/>
       <c r="U33" s="6"/>
       <c r="V33" s="6"/>
       <c r="W33" s="6"/>
       <c r="X33" s="6"/>
       <c r="Y33" s="6"/>
-      <c r="Z33" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
       <c r="AB33" s="6"/>
-      <c r="AC33" s="6">
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE33" s="6"/>
+      <c r="AF33" s="6"/>
+      <c r="AG33" s="6">
         <v>4</v>
       </c>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="5" t="str">
+      <c r="AH33" s="6"/>
+      <c r="AI33" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/metchie-gay-gastanes.jpg</v>
       </c>
-      <c r="AF33" s="6" t="s">
+      <c r="AJ33" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:36">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -4764,29 +5039,35 @@
       <c r="R34" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="S34" s="6"/>
+      <c r="S34" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
       <c r="Y34" s="6"/>
-      <c r="Z34" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z34" s="6"/>
       <c r="AA34" s="6"/>
       <c r="AB34" s="6"/>
       <c r="AC34" s="6"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="5" t="str">
+      <c r="AD34" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jasmin-gerodias.jpg</v>
       </c>
-      <c r="AF34" s="6" t="s">
+      <c r="AJ34" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:36">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4818,7 +5099,7 @@
         <v>353</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
@@ -4840,22 +5121,26 @@
       <c r="W35" s="6"/>
       <c r="X35" s="6"/>
       <c r="Y35" s="6"/>
-      <c r="Z35" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z35" s="6"/>
       <c r="AA35" s="6"/>
       <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="5" t="str">
+      <c r="AD35" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE35" s="6"/>
+      <c r="AF35" s="6"/>
+      <c r="AG35" s="6"/>
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeralyn-gerra.jpg</v>
       </c>
-      <c r="AF35" s="6" t="s">
+      <c r="AJ35" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:36">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -4887,7 +5172,7 @@
         <v>353</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
@@ -4909,22 +5194,26 @@
       <c r="W36" s="6"/>
       <c r="X36" s="6"/>
       <c r="Y36" s="6"/>
-      <c r="Z36" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z36" s="6"/>
       <c r="AA36" s="6"/>
       <c r="AB36" s="6"/>
       <c r="AC36" s="6"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="5" t="str">
+      <c r="AD36" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+      <c r="AG36" s="6"/>
+      <c r="AH36" s="6"/>
+      <c r="AI36" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/genesa-goc-ong.jpg</v>
       </c>
-      <c r="AF36" s="6" t="s">
+      <c r="AJ36" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:36">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -4974,22 +5263,26 @@
       <c r="W37" s="6"/>
       <c r="X37" s="6"/>
       <c r="Y37" s="6"/>
-      <c r="Z37" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
       <c r="AC37" s="6"/>
-      <c r="AD37" s="6"/>
-      <c r="AE37" s="5" t="str">
+      <c r="AD37" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE37" s="6"/>
+      <c r="AF37" s="6"/>
+      <c r="AG37" s="6"/>
+      <c r="AH37" s="6"/>
+      <c r="AI37" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/janelou-gomez.jpg</v>
       </c>
-      <c r="AF37" s="6" t="s">
+      <c r="AJ37" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:36">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -5021,7 +5314,7 @@
         <v>352</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
@@ -5036,29 +5329,35 @@
       <c r="R38" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S38" s="6"/>
+      <c r="S38" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
       <c r="X38" s="6"/>
       <c r="Y38" s="6"/>
-      <c r="Z38" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z38" s="6"/>
       <c r="AA38" s="6"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="6"/>
-      <c r="AD38" s="6"/>
-      <c r="AE38" s="5" t="str">
+      <c r="AD38" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE38" s="6"/>
+      <c r="AF38" s="6"/>
+      <c r="AG38" s="6"/>
+      <c r="AH38" s="6"/>
+      <c r="AI38" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/junnelyn-herbito.jpg</v>
       </c>
-      <c r="AF38" s="6" t="s">
+      <c r="AJ38" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" spans="1:36">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -5090,7 +5389,7 @@
         <v>355</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
@@ -5105,29 +5404,35 @@
       <c r="R39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S39" s="6"/>
+      <c r="S39" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
       <c r="W39" s="6"/>
       <c r="X39" s="6"/>
       <c r="Y39" s="6"/>
-      <c r="Z39" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="5" t="str">
+      <c r="AD39" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE39" s="6"/>
+      <c r="AF39" s="6"/>
+      <c r="AG39" s="6"/>
+      <c r="AH39" s="6"/>
+      <c r="AI39" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/roxan-mae-jao.jpg</v>
       </c>
-      <c r="AF39" s="6" t="s">
+      <c r="AJ39" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:36">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -5175,22 +5480,26 @@
       <c r="W40" s="6"/>
       <c r="X40" s="6"/>
       <c r="Y40" s="6"/>
-      <c r="Z40" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z40" s="6"/>
       <c r="AA40" s="6"/>
       <c r="AB40" s="6"/>
       <c r="AC40" s="6"/>
-      <c r="AD40" s="6"/>
-      <c r="AE40" s="5" t="str">
+      <c r="AD40" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE40" s="6"/>
+      <c r="AF40" s="6"/>
+      <c r="AG40" s="6"/>
+      <c r="AH40" s="6"/>
+      <c r="AI40" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/fernando-laspiñas.jpg</v>
       </c>
-      <c r="AF40" s="6" t="s">
+      <c r="AJ40" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:36">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -5233,29 +5542,35 @@
       <c r="R41" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S41" s="6"/>
+      <c r="S41" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="T41" s="6"/>
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
       <c r="W41" s="6"/>
       <c r="X41" s="6"/>
       <c r="Y41" s="6"/>
-      <c r="Z41" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z41" s="6"/>
       <c r="AA41" s="6"/>
       <c r="AB41" s="6"/>
       <c r="AC41" s="6"/>
-      <c r="AD41" s="6"/>
-      <c r="AE41" s="5" t="str">
+      <c r="AD41" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE41" s="6"/>
+      <c r="AF41" s="6"/>
+      <c r="AG41" s="6"/>
+      <c r="AH41" s="6"/>
+      <c r="AI41" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/nerisa-lim.jpg</v>
       </c>
-      <c r="AF41" s="6" t="s">
+      <c r="AJ41" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:36">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -5301,22 +5616,26 @@
       <c r="W42" s="6"/>
       <c r="X42" s="6"/>
       <c r="Y42" s="6"/>
-      <c r="Z42" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z42" s="6"/>
       <c r="AA42" s="6"/>
       <c r="AB42" s="6"/>
       <c r="AC42" s="6"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="5" t="str">
+      <c r="AD42" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6"/>
+      <c r="AI42" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carl-loreto.jpg</v>
       </c>
-      <c r="AF42" s="6" t="s">
+      <c r="AJ42" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:36">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -5364,22 +5683,26 @@
       <c r="W43" s="6"/>
       <c r="X43" s="6"/>
       <c r="Y43" s="6"/>
-      <c r="Z43" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z43" s="6"/>
       <c r="AA43" s="6"/>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="5" t="str">
+      <c r="AD43" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE43" s="6"/>
+      <c r="AF43" s="6"/>
+      <c r="AG43" s="6"/>
+      <c r="AH43" s="6"/>
+      <c r="AI43" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/lyka-mabanag.jpg</v>
       </c>
-      <c r="AF43" s="6" t="s">
+      <c r="AJ43" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:36">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -5426,29 +5749,35 @@
       <c r="R44" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S44" s="6"/>
+      <c r="S44" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
       <c r="X44" s="6"/>
       <c r="Y44" s="6"/>
-      <c r="Z44" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
       <c r="AB44" s="6"/>
       <c r="AC44" s="6"/>
-      <c r="AD44" s="6"/>
-      <c r="AE44" s="5" t="str">
+      <c r="AD44" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE44" s="6"/>
+      <c r="AF44" s="6"/>
+      <c r="AG44" s="6"/>
+      <c r="AH44" s="6"/>
+      <c r="AI44" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/richie-ryan-mabunay.jpg</v>
       </c>
-      <c r="AF44" s="6" t="s">
+      <c r="AJ44" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:36">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -5498,22 +5827,26 @@
       <c r="W45" s="6"/>
       <c r="X45" s="6"/>
       <c r="Y45" s="6"/>
-      <c r="Z45" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z45" s="6"/>
       <c r="AA45" s="6"/>
       <c r="AB45" s="6"/>
       <c r="AC45" s="6"/>
-      <c r="AD45" s="6"/>
-      <c r="AE45" s="5" t="str">
+      <c r="AD45" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="6"/>
+      <c r="AG45" s="6"/>
+      <c r="AH45" s="6"/>
+      <c r="AI45" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/maria-jeziel-macanin.jpg</v>
       </c>
-      <c r="AF45" s="6" t="s">
+      <c r="AJ45" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" spans="1:36">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -5545,7 +5878,7 @@
         <v>354</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
@@ -5560,29 +5893,35 @@
       <c r="R46" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S46" s="6"/>
+      <c r="S46" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T46" s="6"/>
       <c r="U46" s="6"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
       <c r="X46" s="6"/>
       <c r="Y46" s="6"/>
-      <c r="Z46" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z46" s="6"/>
       <c r="AA46" s="6"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="6"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="5" t="str">
+      <c r="AD46" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE46" s="6"/>
+      <c r="AF46" s="6"/>
+      <c r="AG46" s="6"/>
+      <c r="AH46" s="6"/>
+      <c r="AI46" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jeralen-maloloy-on.jpg</v>
       </c>
-      <c r="AF46" s="6" t="s">
+      <c r="AJ46" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:36">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -5614,7 +5953,7 @@
         <v>352</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
@@ -5629,29 +5968,35 @@
       <c r="R47" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="S47" s="6"/>
+      <c r="S47" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
       <c r="X47" s="6"/>
       <c r="Y47" s="6"/>
-      <c r="Z47" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z47" s="6"/>
       <c r="AA47" s="6"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="5" t="str">
+      <c r="AD47" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE47" s="6"/>
+      <c r="AF47" s="6"/>
+      <c r="AG47" s="6"/>
+      <c r="AH47" s="6"/>
+      <c r="AI47" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/elbert-misterio.jpg</v>
       </c>
-      <c r="AF47" s="6" t="s">
+      <c r="AJ47" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:36">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -5683,7 +6028,7 @@
         <v>353</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
@@ -5703,22 +6048,26 @@
       <c r="W48" s="6"/>
       <c r="X48" s="6"/>
       <c r="Y48" s="6"/>
-      <c r="Z48" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z48" s="6"/>
       <c r="AA48" s="6"/>
       <c r="AB48" s="6"/>
       <c r="AC48" s="6"/>
-      <c r="AD48" s="6"/>
-      <c r="AE48" s="5" t="str">
+      <c r="AD48" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE48" s="6"/>
+      <c r="AF48" s="6"/>
+      <c r="AG48" s="6"/>
+      <c r="AH48" s="6"/>
+      <c r="AI48" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joy-mortal.jpg</v>
       </c>
-      <c r="AF48" s="6" t="s">
+      <c r="AJ48" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:36">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -5766,22 +6115,26 @@
       <c r="W49" s="6"/>
       <c r="X49" s="6"/>
       <c r="Y49" s="6"/>
-      <c r="Z49" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z49" s="6"/>
       <c r="AA49" s="6"/>
       <c r="AB49" s="6"/>
       <c r="AC49" s="6"/>
-      <c r="AD49" s="6"/>
-      <c r="AE49" s="5" t="str">
+      <c r="AD49" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE49" s="6"/>
+      <c r="AF49" s="6"/>
+      <c r="AG49" s="6"/>
+      <c r="AH49" s="6"/>
+      <c r="AI49" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/claire-medillo.jpg</v>
       </c>
-      <c r="AF49" s="6" t="s">
+      <c r="AJ49" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:36">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -5813,7 +6166,7 @@
         <v>352</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
@@ -5828,29 +6181,35 @@
       <c r="R50" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="S50" s="6"/>
+      <c r="S50" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T50" s="6"/>
       <c r="U50" s="6"/>
       <c r="V50" s="6"/>
       <c r="W50" s="6"/>
       <c r="X50" s="6"/>
       <c r="Y50" s="6"/>
-      <c r="Z50" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z50" s="6"/>
       <c r="AA50" s="6"/>
       <c r="AB50" s="6"/>
       <c r="AC50" s="6"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="5" t="str">
+      <c r="AD50" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE50" s="6"/>
+      <c r="AF50" s="6"/>
+      <c r="AG50" s="6"/>
+      <c r="AH50" s="6"/>
+      <c r="AI50" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/gwendolyn-olo.jpg</v>
       </c>
-      <c r="AF50" s="6" t="s">
+      <c r="AJ50" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:36">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5882,7 +6241,7 @@
         <v>355</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
@@ -5902,22 +6261,26 @@
       <c r="W51" s="6"/>
       <c r="X51" s="6"/>
       <c r="Y51" s="6"/>
-      <c r="Z51" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z51" s="6"/>
       <c r="AA51" s="6"/>
       <c r="AB51" s="6"/>
       <c r="AC51" s="6"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="5" t="str">
+      <c r="AD51" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE51" s="6"/>
+      <c r="AF51" s="6"/>
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="6"/>
+      <c r="AI51" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jay-neil-oro.jpg</v>
       </c>
-      <c r="AF51" s="6" t="s">
+      <c r="AJ51" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:36">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5949,7 +6312,7 @@
         <v>357</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
@@ -5962,31 +6325,37 @@
         <v>14</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="S52" s="6"/>
+        <v>387</v>
+      </c>
+      <c r="S52" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6"/>
       <c r="X52" s="6"/>
       <c r="Y52" s="6"/>
-      <c r="Z52" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z52" s="6"/>
       <c r="AA52" s="6"/>
       <c r="AB52" s="6"/>
       <c r="AC52" s="6"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="5" t="str">
+      <c r="AD52" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE52" s="6"/>
+      <c r="AF52" s="6"/>
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6"/>
+      <c r="AI52" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/glendale-orocay.jpg</v>
       </c>
-      <c r="AF52" s="6" t="s">
+      <c r="AJ52" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:32" ht="33.6">
+    <row r="53" spans="1:36" ht="33.6">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -6018,7 +6387,7 @@
         <v>356</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
@@ -6033,29 +6402,35 @@
       <c r="R53" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="S53" s="6"/>
+      <c r="S53" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
       <c r="V53" s="6"/>
       <c r="W53" s="6"/>
       <c r="X53" s="6"/>
       <c r="Y53" s="6"/>
-      <c r="Z53" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z53" s="6"/>
       <c r="AA53" s="6"/>
       <c r="AB53" s="6"/>
       <c r="AC53" s="6"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="5" t="str">
+      <c r="AD53" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE53" s="6"/>
+      <c r="AF53" s="6"/>
+      <c r="AG53" s="6"/>
+      <c r="AH53" s="6"/>
+      <c r="AI53" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marissa-pintuan.jpg</v>
       </c>
-      <c r="AF53" s="6" t="s">
+      <c r="AJ53" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:36">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -6105,22 +6480,26 @@
       <c r="W54" s="6"/>
       <c r="X54" s="6"/>
       <c r="Y54" s="6"/>
-      <c r="Z54" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z54" s="6"/>
       <c r="AA54" s="6"/>
       <c r="AB54" s="6"/>
       <c r="AC54" s="6"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="5" t="str">
+      <c r="AD54" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE54" s="6"/>
+      <c r="AF54" s="6"/>
+      <c r="AG54" s="6"/>
+      <c r="AH54" s="6"/>
+      <c r="AI54" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ma.-lourdes-prajes.jpg</v>
       </c>
-      <c r="AF54" s="6" t="s">
+      <c r="AJ54" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:36">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -6152,7 +6531,7 @@
         <v>353</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
@@ -6172,22 +6551,26 @@
       <c r="W55" s="6"/>
       <c r="X55" s="6"/>
       <c r="Y55" s="6"/>
-      <c r="Z55" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z55" s="6"/>
       <c r="AA55" s="6"/>
       <c r="AB55" s="6"/>
       <c r="AC55" s="6"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="5" t="str">
+      <c r="AD55" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE55" s="6"/>
+      <c r="AF55" s="6"/>
+      <c r="AG55" s="6"/>
+      <c r="AH55" s="6"/>
+      <c r="AI55" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/bret-kalvin-primacio.jpg</v>
       </c>
-      <c r="AF55" s="6" t="s">
+      <c r="AJ55" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:36">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -6230,29 +6613,35 @@
       <c r="R56" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S56" s="6"/>
+      <c r="S56" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T56" s="6"/>
       <c r="U56" s="6"/>
       <c r="V56" s="6"/>
       <c r="W56" s="6"/>
       <c r="X56" s="6"/>
       <c r="Y56" s="6"/>
-      <c r="Z56" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z56" s="6"/>
       <c r="AA56" s="6"/>
       <c r="AB56" s="6"/>
       <c r="AC56" s="6"/>
-      <c r="AD56" s="6"/>
-      <c r="AE56" s="5" t="str">
+      <c r="AD56" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE56" s="6"/>
+      <c r="AF56" s="6"/>
+      <c r="AG56" s="6"/>
+      <c r="AH56" s="6"/>
+      <c r="AI56" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jhea-quiling.jpg</v>
       </c>
-      <c r="AF56" s="6" t="s">
+      <c r="AJ56" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:36">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -6295,29 +6684,35 @@
       <c r="R57" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S57" s="6"/>
+      <c r="S57" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="T57" s="6"/>
       <c r="U57" s="6"/>
       <c r="V57" s="6"/>
       <c r="W57" s="6"/>
       <c r="X57" s="6"/>
       <c r="Y57" s="6"/>
-      <c r="Z57" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z57" s="6"/>
       <c r="AA57" s="6"/>
       <c r="AB57" s="6"/>
       <c r="AC57" s="6"/>
-      <c r="AD57" s="6"/>
-      <c r="AE57" s="5" t="str">
+      <c r="AD57" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE57" s="6"/>
+      <c r="AF57" s="6"/>
+      <c r="AG57" s="6"/>
+      <c r="AH57" s="6"/>
+      <c r="AI57" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joyce-racaza.jpg</v>
       </c>
-      <c r="AF57" s="6" t="s">
+      <c r="AJ57" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:36">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -6360,29 +6755,35 @@
       <c r="R58" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="S58" s="6"/>
+      <c r="S58" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="T58" s="6"/>
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
       <c r="W58" s="6"/>
       <c r="X58" s="6"/>
       <c r="Y58" s="6"/>
-      <c r="Z58" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z58" s="6"/>
       <c r="AA58" s="6"/>
       <c r="AB58" s="6"/>
       <c r="AC58" s="6"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="5" t="str">
+      <c r="AD58" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE58" s="6"/>
+      <c r="AF58" s="6"/>
+      <c r="AG58" s="6"/>
+      <c r="AH58" s="6"/>
+      <c r="AI58" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/cromwell-retuya.jpg</v>
       </c>
-      <c r="AF58" s="6" t="s">
+      <c r="AJ58" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:36">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -6408,7 +6809,7 @@
         <v>12</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
@@ -6425,31 +6826,37 @@
       <c r="R59" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="S59" s="6"/>
+      <c r="S59" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="T59" s="6"/>
       <c r="U59" s="6"/>
       <c r="V59" s="6"/>
       <c r="W59" s="6"/>
       <c r="X59" s="6"/>
       <c r="Y59" s="6"/>
-      <c r="Z59" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="Z59" s="6"/>
       <c r="AA59" s="6"/>
       <c r="AB59" s="6"/>
-      <c r="AC59" s="6">
+      <c r="AC59" s="6"/>
+      <c r="AD59" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE59" s="6"/>
+      <c r="AF59" s="6"/>
+      <c r="AG59" s="6">
         <v>5</v>
       </c>
-      <c r="AD59" s="6"/>
-      <c r="AE59" s="5" t="str">
+      <c r="AH59" s="6"/>
+      <c r="AI59" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/nancy-reyes.jpg</v>
       </c>
-      <c r="AF59" s="6" t="s">
+      <c r="AJ59" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:36">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -6481,7 +6888,7 @@
         <v>354</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
@@ -6501,22 +6908,26 @@
       <c r="W60" s="6"/>
       <c r="X60" s="6"/>
       <c r="Y60" s="6"/>
-      <c r="Z60" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z60" s="6"/>
       <c r="AA60" s="6"/>
       <c r="AB60" s="6"/>
       <c r="AC60" s="6"/>
-      <c r="AD60" s="6"/>
-      <c r="AE60" s="5" t="str">
+      <c r="AD60" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE60" s="6"/>
+      <c r="AF60" s="6"/>
+      <c r="AG60" s="6"/>
+      <c r="AH60" s="6"/>
+      <c r="AI60" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/angelo-saavedra.jpg</v>
       </c>
-      <c r="AF60" s="6" t="s">
+      <c r="AJ60" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:36">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -6542,7 +6953,7 @@
         <v>244</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
@@ -6557,31 +6968,37 @@
         <v>17</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="S61" s="6"/>
+        <v>388</v>
+      </c>
+      <c r="S61" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="T61" s="6"/>
       <c r="U61" s="6"/>
       <c r="V61" s="6"/>
       <c r="W61" s="6"/>
       <c r="X61" s="6"/>
       <c r="Y61" s="6"/>
-      <c r="Z61" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z61" s="6"/>
       <c r="AA61" s="6"/>
       <c r="AB61" s="6"/>
       <c r="AC61" s="6"/>
-      <c r="AD61" s="6"/>
-      <c r="AE61" s="5" t="str">
+      <c r="AD61" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE61" s="6"/>
+      <c r="AF61" s="6"/>
+      <c r="AG61" s="6"/>
+      <c r="AH61" s="6"/>
+      <c r="AI61" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/brendel-sacaris.jpg</v>
       </c>
-      <c r="AF61" s="6" t="s">
+      <c r="AJ61" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:36">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -6613,7 +7030,7 @@
         <v>354</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
@@ -6626,29 +7043,35 @@
         <v>17</v>
       </c>
       <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
+      <c r="S62" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="T62" s="6"/>
       <c r="U62" s="6"/>
       <c r="V62" s="6"/>
       <c r="W62" s="6"/>
       <c r="X62" s="6"/>
       <c r="Y62" s="6"/>
-      <c r="Z62" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z62" s="6"/>
       <c r="AA62" s="6"/>
       <c r="AB62" s="6"/>
       <c r="AC62" s="6"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="5" t="str">
+      <c r="AD62" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE62" s="6"/>
+      <c r="AF62" s="6"/>
+      <c r="AG62" s="6"/>
+      <c r="AH62" s="6"/>
+      <c r="AI62" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C62&amp;" "&amp;B62)," ","-"))&amp;".jpg"</f>
         <v>/personnel/bella-arquine-samontañez.jpg</v>
       </c>
-      <c r="AF62" s="6" t="s">
+      <c r="AJ62" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:36">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -6680,7 +7103,7 @@
         <v>357</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
@@ -6695,29 +7118,35 @@
       <c r="R63" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S63" s="6"/>
+      <c r="S63" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
       <c r="W63" s="6"/>
       <c r="X63" s="6"/>
       <c r="Y63" s="6"/>
-      <c r="Z63" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="Z63" s="6"/>
       <c r="AA63" s="6"/>
       <c r="AB63" s="6"/>
       <c r="AC63" s="6"/>
-      <c r="AD63" s="6"/>
-      <c r="AE63" s="5" t="str">
+      <c r="AD63" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE63" s="6"/>
+      <c r="AF63" s="6"/>
+      <c r="AG63" s="6"/>
+      <c r="AH63" s="6"/>
+      <c r="AI63" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jevy-ann-uy.jpg</v>
       </c>
-      <c r="AF63" s="6" t="s">
+      <c r="AJ63" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:36">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -6760,29 +7189,35 @@
       <c r="R64" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="S64" s="6"/>
+      <c r="S64" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="T64" s="6"/>
       <c r="U64" s="6"/>
       <c r="V64" s="6"/>
       <c r="W64" s="6"/>
       <c r="X64" s="6"/>
       <c r="Y64" s="6"/>
-      <c r="Z64" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="Z64" s="6"/>
       <c r="AA64" s="6"/>
       <c r="AB64" s="6"/>
       <c r="AC64" s="6"/>
-      <c r="AD64" s="6"/>
-      <c r="AE64" s="5" t="str">
+      <c r="AD64" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AE64" s="6"/>
+      <c r="AF64" s="6"/>
+      <c r="AG64" s="6"/>
+      <c r="AH64" s="6"/>
+      <c r="AI64" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/grace-vergara.jpg</v>
       </c>
-      <c r="AF64" s="6" t="s">
+      <c r="AJ64" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:36">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -6825,29 +7260,35 @@
       <c r="R65" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S65" s="6"/>
+      <c r="S65" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
       <c r="V65" s="6"/>
       <c r="W65" s="6"/>
       <c r="X65" s="6"/>
       <c r="Y65" s="6"/>
-      <c r="Z65" s="6" t="s">
-        <v>271</v>
-      </c>
+      <c r="Z65" s="6"/>
       <c r="AA65" s="6"/>
       <c r="AB65" s="6"/>
       <c r="AC65" s="6"/>
-      <c r="AD65" s="6"/>
-      <c r="AE65" s="5" t="str">
+      <c r="AD65" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="AE65" s="6"/>
+      <c r="AF65" s="6"/>
+      <c r="AG65" s="6"/>
+      <c r="AH65" s="6"/>
+      <c r="AI65" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/guillermo-villavelez.jpg</v>
       </c>
-      <c r="AF65" s="6" t="s">
+      <c r="AJ65" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:36">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -6890,29 +7331,35 @@
       <c r="R66" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="S66" s="6"/>
+      <c r="S66" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="T66" s="6"/>
       <c r="U66" s="6"/>
       <c r="V66" s="6"/>
       <c r="W66" s="6"/>
       <c r="X66" s="6"/>
       <c r="Y66" s="6"/>
-      <c r="Z66" s="6" t="s">
-        <v>369</v>
-      </c>
+      <c r="Z66" s="6"/>
       <c r="AA66" s="6"/>
       <c r="AB66" s="6"/>
       <c r="AC66" s="6"/>
-      <c r="AD66" s="6"/>
-      <c r="AE66" s="5" t="str">
+      <c r="AD66" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE66" s="6"/>
+      <c r="AF66" s="6"/>
+      <c r="AG66" s="6"/>
+      <c r="AH66" s="6"/>
+      <c r="AI66" s="5" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-villaver.jpg</v>
       </c>
-      <c r="AF66" s="6" t="s">
+      <c r="AJ66" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:36">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -6955,29 +7402,35 @@
       <c r="R67" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S67" s="6"/>
+      <c r="S67" s="6" t="s">
+        <v>385</v>
+      </c>
       <c r="T67" s="6"/>
       <c r="U67" s="6"/>
       <c r="V67" s="6"/>
       <c r="W67" s="6"/>
       <c r="X67" s="6"/>
       <c r="Y67" s="6"/>
-      <c r="Z67" s="6" t="s">
-        <v>370</v>
-      </c>
+      <c r="Z67" s="6"/>
       <c r="AA67" s="6"/>
       <c r="AB67" s="6"/>
       <c r="AC67" s="6"/>
-      <c r="AD67" s="6"/>
-      <c r="AE67" s="5" t="str">
-        <f t="shared" ref="AE67:AE68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
+      <c r="AD67" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AE67" s="6"/>
+      <c r="AF67" s="6"/>
+      <c r="AG67" s="6"/>
+      <c r="AH67" s="6"/>
+      <c r="AI67" s="5" t="str">
+        <f t="shared" ref="AI67:AI68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
         <v>/personnel/markjil-bacaltos.jpg</v>
       </c>
-      <c r="AF67" s="6" t="s">
+      <c r="AJ67" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:36">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -7020,29 +7473,35 @@
       <c r="R68" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S68" s="6"/>
+      <c r="S68" s="6" t="s">
+        <v>385</v>
+      </c>
       <c r="T68" s="6"/>
       <c r="U68" s="6"/>
       <c r="V68" s="6"/>
       <c r="W68" s="6"/>
       <c r="X68" s="6"/>
       <c r="Y68" s="6"/>
-      <c r="Z68" s="6" t="s">
-        <v>370</v>
-      </c>
+      <c r="Z68" s="6"/>
       <c r="AA68" s="6"/>
       <c r="AB68" s="6"/>
       <c r="AC68" s="6"/>
-      <c r="AD68" s="6"/>
-      <c r="AE68" s="5" t="str">
+      <c r="AD68" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AE68" s="6"/>
+      <c r="AF68" s="6"/>
+      <c r="AG68" s="6"/>
+      <c r="AH68" s="6"/>
+      <c r="AI68" s="5" t="str">
         <f t="shared" si="8"/>
         <v>/personnel/diocel-celocia.jpg</v>
       </c>
-      <c r="AF68" s="6" t="s">
+      <c r="AJ68" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:36">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -7085,29 +7544,35 @@
       <c r="R69" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S69" s="6"/>
+      <c r="S69" s="6" t="s">
+        <v>385</v>
+      </c>
       <c r="T69" s="6"/>
       <c r="U69" s="6"/>
       <c r="V69" s="6"/>
       <c r="W69" s="6"/>
       <c r="X69" s="6"/>
       <c r="Y69" s="6"/>
-      <c r="Z69" s="6" t="s">
-        <v>370</v>
-      </c>
+      <c r="Z69" s="6"/>
       <c r="AA69" s="6"/>
       <c r="AB69" s="6"/>
       <c r="AC69" s="6"/>
-      <c r="AD69" s="6"/>
-      <c r="AE69" s="5" t="str">
-        <f t="shared" ref="AE69:AE70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
+      <c r="AD69" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AE69" s="6"/>
+      <c r="AF69" s="6"/>
+      <c r="AG69" s="6"/>
+      <c r="AH69" s="6"/>
+      <c r="AI69" s="5" t="str">
+        <f t="shared" ref="AI69:AI70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
         <v>/personnel/luie-cabs.jpg</v>
       </c>
-      <c r="AF69" s="6" t="s">
+      <c r="AJ69" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:36">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -7150,29 +7615,35 @@
       <c r="R70" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="S70" s="6"/>
+      <c r="S70" s="6" t="s">
+        <v>385</v>
+      </c>
       <c r="T70" s="6"/>
       <c r="U70" s="6"/>
       <c r="V70" s="6"/>
       <c r="W70" s="6"/>
       <c r="X70" s="6"/>
       <c r="Y70" s="6"/>
-      <c r="Z70" s="6" t="s">
-        <v>370</v>
-      </c>
+      <c r="Z70" s="6"/>
       <c r="AA70" s="6"/>
       <c r="AB70" s="6"/>
       <c r="AC70" s="6"/>
-      <c r="AD70" s="6"/>
-      <c r="AE70" s="5" t="str">
+      <c r="AD70" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AE70" s="6"/>
+      <c r="AF70" s="6"/>
+      <c r="AG70" s="6"/>
+      <c r="AH70" s="6"/>
+      <c r="AI70" s="5" t="str">
         <f t="shared" si="11"/>
         <v>/personnel/luis-mans.jpg</v>
       </c>
-      <c r="AF70" s="6" t="s">
+      <c r="AJ70" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:36">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -7208,8 +7679,12 @@
       <c r="AB71" s="6"/>
       <c r="AC71" s="6"/>
       <c r="AD71" s="6"/>
-      <c r="AE71" s="5"/>
+      <c r="AE71" s="6"/>
       <c r="AF71" s="6"/>
+      <c r="AG71" s="6"/>
+      <c r="AH71" s="6"/>
+      <c r="AI71" s="5"/>
+      <c r="AJ71" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -7242,19 +7717,19 @@
           <x14:formula1>
             <xm:f>Dropdown_Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>AF2:AF71</xm:sqref>
+          <xm:sqref>AJ2:AJ71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70D54F6E-2A67-40F0-92CA-B6E53F44843D}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$D$2:$D$61</xm:f>
           </x14:formula1>
-          <xm:sqref>Z2:Z71</xm:sqref>
+          <xm:sqref>AD2:AD71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7834D497-9733-4178-89DF-4B7895726F53}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$E$2:$E$60</xm:f>
           </x14:formula1>
-          <xm:sqref>AA2:AA71</xm:sqref>
+          <xm:sqref>AE2:AE71</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C289C-C94D-47D0-869F-434C983C10DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0BA6E3-EA50-40AC-857B-DD692E14D218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="21315" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="484">
   <si>
     <t>order</t>
   </si>
@@ -1481,6 +1481,12 @@
   </si>
   <si>
     <t>SubjectDepartment5</t>
+  </si>
+  <si>
+    <t>Utility Support</t>
+  </si>
+  <si>
+    <t>Security Personnel</t>
   </si>
 </sst>
 </file>
@@ -1589,6 +1595,33 @@
   <dxfs count="39">
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1662,33 +1695,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2243,6 +2249,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:AJ71" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="36">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AJ71">
+    <sortCondition ref="B2:B71"/>
+  </sortState>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="order" dataDxfId="35"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="lastName" dataDxfId="34"/>
@@ -2267,23 +2276,23 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="department" dataDxfId="19"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="subjectArea" dataDxfId="18"/>
     <tableColumn id="26" xr3:uid="{9234D872-27E9-4981-9849-3B92B3D703D7}" name="primarySubjectDepartment" dataDxfId="17"/>
-    <tableColumn id="34" xr3:uid="{168EB6BE-8B21-4305-ABC1-174562CD0A0B}" name="SubjectDepartment2" dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{5C2FF8F3-D884-43D6-84E1-D482E29A632A}" name="SubjectDepartment3" dataDxfId="2"/>
-    <tableColumn id="36" xr3:uid="{9BC6D117-EABD-4BEC-9C2D-4F49F4E8F4AF}" name="SubjectDepartment4" dataDxfId="1"/>
-    <tableColumn id="37" xr3:uid="{C21080E4-B7D1-416D-9C89-C64670FF6EAA}" name="SubjectDepartment5" dataDxfId="0"/>
-    <tableColumn id="27" xr3:uid="{BAF0BAF6-D68C-494F-94BF-9DBEAC627028}" name="subject1" dataDxfId="16"/>
-    <tableColumn id="28" xr3:uid="{8B540991-2968-4F70-8AAC-FCFC355A419A}" name="subject2" dataDxfId="15"/>
-    <tableColumn id="29" xr3:uid="{1D6F7D4B-4E56-4246-A153-8FAB0BEB4811}" name="subject3" dataDxfId="14"/>
-    <tableColumn id="30" xr3:uid="{E295C211-F74A-4E2B-893A-E9FDF18B7EE9}" name="subject4" dataDxfId="13"/>
-    <tableColumn id="31" xr3:uid="{B93E7C74-87A6-4CBE-9E54-1C7E4E717375}" name="subject5" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{AE0F403C-1544-4D9E-929C-27676144B2E2}" name="teachingLevel" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="4"/>
+    <tableColumn id="34" xr3:uid="{168EB6BE-8B21-4305-ABC1-174562CD0A0B}" name="SubjectDepartment2" dataDxfId="16"/>
+    <tableColumn id="35" xr3:uid="{5C2FF8F3-D884-43D6-84E1-D482E29A632A}" name="SubjectDepartment3" dataDxfId="15"/>
+    <tableColumn id="36" xr3:uid="{9BC6D117-EABD-4BEC-9C2D-4F49F4E8F4AF}" name="SubjectDepartment4" dataDxfId="14"/>
+    <tableColumn id="37" xr3:uid="{C21080E4-B7D1-416D-9C89-C64670FF6EAA}" name="SubjectDepartment5" dataDxfId="13"/>
+    <tableColumn id="27" xr3:uid="{BAF0BAF6-D68C-494F-94BF-9DBEAC627028}" name="subject1" dataDxfId="12"/>
+    <tableColumn id="28" xr3:uid="{8B540991-2968-4F70-8AAC-FCFC355A419A}" name="subject2" dataDxfId="11"/>
+    <tableColumn id="29" xr3:uid="{1D6F7D4B-4E56-4246-A153-8FAB0BEB4811}" name="subject3" dataDxfId="10"/>
+    <tableColumn id="30" xr3:uid="{E295C211-F74A-4E2B-893A-E9FDF18B7EE9}" name="subject4" dataDxfId="9"/>
+    <tableColumn id="31" xr3:uid="{B93E7C74-87A6-4CBE-9E54-1C7E4E717375}" name="subject5" dataDxfId="8"/>
+    <tableColumn id="32" xr3:uid="{AE0F403C-1544-4D9E-929C-27676144B2E2}" name="teachingLevel" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{07B5CB0A-FE18-46C6-B1E6-1B1D900FB654}" name="displayGroup" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{65EBFB40-77EE-48B3-8561-311242B8D6D2}" name="subGroup" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{AE424BEB-0E42-47BC-8BF7-A0E6C15B9F30}" name="groupOrder" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{8ED835C9-250F-4A69-B1C0-89AD725EFF0F}" name="subGroupOrder" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{894550D0-2DF4-4E17-A2FB-C537176088F7}" name="personOrder" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="photoUrl" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2451,7 +2460,7 @@
     <col min="8" max="8" width="21.69921875" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40.796875" style="11" customWidth="1"/>
     <col min="10" max="10" width="19.296875" style="11" customWidth="1"/>
-    <col min="11" max="11" width="17.296875" style="11" customWidth="1"/>
+    <col min="11" max="11" width="30.69921875" style="11" customWidth="1"/>
     <col min="12" max="12" width="31" style="4" customWidth="1"/>
     <col min="13" max="14" width="28" style="4" customWidth="1"/>
     <col min="15" max="15" width="32.8984375" style="4" customWidth="1"/>
@@ -2588,12 +2597,12 @@
         <v>54</v>
       </c>
       <c r="E2" s="5" t="str">
-        <f t="shared" ref="E2:E37" si="0">IF(D2="","",LEFT(TRIM(D2),1)&amp;".")</f>
+        <f>IF(D2="","",LEFT(TRIM(D2),1)&amp;".")</f>
         <v>V.</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="str">
-        <f t="shared" ref="G2:G4" si="1">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</f>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C2,IF(E2&lt;&gt;"",IF(RIGHT(E2,1)=".",E2,E2&amp;"."),D2),B2,F2))</f>
         <v>Paz V. Abad</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -2665,12 +2674,12 @@
         <v>58</v>
       </c>
       <c r="E3" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D3="","",LEFT(TRIM(D3),1)&amp;".")</f>
         <v>G.</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C3,IF(E3&lt;&gt;"",IF(RIGHT(E3,1)=".",E3,E3&amp;"."),D3),B3,F3))</f>
         <v>Marissa G. Abalo</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2727,7 +2736,7 @@
       <c r="AG3" s="6"/>
       <c r="AH3" s="6"/>
       <c r="AI3" s="5" t="str">
-        <f t="shared" ref="AI3:AI66" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C3&amp;" "&amp;B3)," ","-"))&amp;".jpg"</f>
         <v>/personnel/marissa-abalo.jpg</v>
       </c>
       <c r="AJ3" s="6" t="s">
@@ -2748,12 +2757,12 @@
         <v>61</v>
       </c>
       <c r="E4" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D4="","",LEFT(TRIM(D4),1)&amp;".")</f>
         <v>C.</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C4,IF(E4&lt;&gt;"",IF(RIGHT(E4,1)=".",E4,E4&amp;"."),D4),B4,F4))</f>
         <v>Joseph C. Allosada</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -2802,7 +2811,7 @@
       <c r="AG4" s="6"/>
       <c r="AH4" s="6"/>
       <c r="AI4" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C4&amp;" "&amp;B4)," ","-"))&amp;".jpg"</f>
         <v>/personnel/joseph-allosada.jpg</v>
       </c>
       <c r="AJ4" s="6" t="s">
@@ -2823,12 +2832,12 @@
         <v>64</v>
       </c>
       <c r="E5" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D5="","",LEFT(TRIM(D5),1)&amp;".")</f>
         <v>B.</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="str">
-        <f t="shared" ref="G5:G37" si="3">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C5,IF(E5&lt;&gt;"",IF(RIGHT(E5,1)=".",E5,E5&amp;"."),D5),B5,F5))</f>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C5,IF(E5&lt;&gt;"",IF(RIGHT(E5,1)=".",E5,E5&amp;"."),D5),B5,F5))</f>
         <v>Sharon Gay B. Alsa</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -2887,7 +2896,7 @@
       <c r="AG5" s="6"/>
       <c r="AH5" s="6"/>
       <c r="AI5" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C5&amp;" "&amp;B5)," ","-"))&amp;".jpg"</f>
         <v>/personnel/sharon-gay-alsa.jpg</v>
       </c>
       <c r="AJ5" s="6" t="s">
@@ -2908,12 +2917,12 @@
         <v>67</v>
       </c>
       <c r="E6" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D6="","",LEFT(TRIM(D6),1)&amp;".")</f>
         <v>C.</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C6,IF(E6&lt;&gt;"",IF(RIGHT(E6,1)=".",E6,E6&amp;"."),D6),B6,F6))</f>
         <v>Lonier C. Andrade</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -2968,7 +2977,7 @@
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
       <c r="AI6" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C6&amp;" "&amp;B6)," ","-"))&amp;".jpg"</f>
         <v>/personnel/lonier-andrade.jpg</v>
       </c>
       <c r="AJ6" s="6" t="s">
@@ -2989,12 +2998,12 @@
         <v>70</v>
       </c>
       <c r="E7" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D7="","",LEFT(TRIM(D7),1)&amp;".")</f>
         <v>R.</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C7,IF(E7&lt;&gt;"",IF(RIGHT(E7,1)=".",E7,E7&amp;"."),D7),B7,F7))</f>
         <v>Allan Raul R. Aparicio</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -3051,7 +3060,7 @@
       <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
       <c r="AI7" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C7&amp;" "&amp;B7)," ","-"))&amp;".jpg"</f>
         <v>/personnel/allan-raul-aparicio.jpg</v>
       </c>
       <c r="AJ7" s="6" t="s">
@@ -3072,12 +3081,12 @@
         <v>71</v>
       </c>
       <c r="E8" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D8="","",LEFT(TRIM(D8),1)&amp;".")</f>
         <v>A.</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C8,IF(E8&lt;&gt;"",IF(RIGHT(E8,1)=".",E8,E8&amp;"."),D8),B8,F8))</f>
         <v>Niña Kristine A. Ayos</v>
       </c>
       <c r="H8" s="5" t="s">
@@ -3118,7 +3127,7 @@
       <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
       <c r="AI8" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C8&amp;" "&amp;B8)," ","-"))&amp;".jpg"</f>
         <v>/personnel/niña-kristine-ayos.jpg</v>
       </c>
       <c r="AJ8" s="6" t="s">
@@ -3127,76 +3136,70 @@
     </row>
     <row r="9" spans="1:36">
       <c r="A9" s="5">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>107</v>
+        <v>235</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>72</v>
+        <v>236</v>
       </c>
       <c r="E9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>T.</v>
+        <f>IF(D9="","",LEFT(TRIM(D9),1)&amp;".")</f>
+        <v>Z.</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Glenn T. Barangan</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C9,IF(E9&lt;&gt;"",IF(RIGHT(E9,1)=".",E9,E9&amp;"."),D9),B9,F9))</f>
+        <v>Markjil Z. Bacaltos</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5" t="s">
-        <v>448</v>
-      </c>
+      <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="6" t="s">
-        <v>13</v>
+        <v>372</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>17</v>
+        <v>371</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>477</v>
+        <v>385</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
-      <c r="X9" s="6" t="s">
-        <v>461</v>
-      </c>
+      <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
-      <c r="AC9" s="6" t="s">
-        <v>337</v>
-      </c>
+      <c r="AC9" s="6"/>
       <c r="AD9" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE9" s="6"/>
       <c r="AF9" s="6"/>
       <c r="AG9" s="6"/>
       <c r="AH9" s="6"/>
       <c r="AI9" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/glenn-barangan.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C9&amp;" "&amp;B9)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/markjil-bacaltos.jpg</v>
       </c>
       <c r="AJ9" s="6" t="s">
         <v>9</v>
@@ -3204,64 +3207,58 @@
     </row>
     <row r="10" spans="1:36">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D10="","",LEFT(TRIM(D10),1)&amp;".")</f>
         <v>T.</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Jake T. Barcenas</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C10,IF(E10&lt;&gt;"",IF(RIGHT(E10,1)=".",E10,E10&amp;"."),D10),B10,F10))</f>
+        <v>Glenn T. Barangan</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>12</v>
+        <v>244</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>398</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
       <c r="L10" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>450</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>386</v>
+        <v>344</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
       <c r="X10" s="6" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
@@ -3271,15 +3268,15 @@
         <v>337</v>
       </c>
       <c r="AD10" s="6" t="s">
-        <v>277</v>
+        <v>368</v>
       </c>
       <c r="AE10" s="6"/>
       <c r="AF10" s="6"/>
       <c r="AG10" s="6"/>
       <c r="AH10" s="6"/>
       <c r="AI10" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jake-barcenas.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C10&amp;" "&amp;B10)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/glenn-barangan.jpg</v>
       </c>
       <c r="AJ10" s="6" t="s">
         <v>9</v>
@@ -3287,25 +3284,25 @@
     </row>
     <row r="11" spans="1:36">
       <c r="A11" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>P.</v>
+        <f>IF(D11="","",LEFT(TRIM(D11),1)&amp;".")</f>
+        <v>T.</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Eljoy P. Barroca</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C11,IF(E11&lt;&gt;"",IF(RIGHT(E11,1)=".",E11,E11&amp;"."),D11),B11,F11))</f>
+        <v>Jake T. Barcenas</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>12</v>
@@ -3314,35 +3311,37 @@
         <v>277</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="M11" s="5"/>
+        <v>449</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>450</v>
+      </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="T11" s="6"/>
       <c r="U11" s="6"/>
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
       <c r="X11" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
@@ -3359,34 +3358,34 @@
       <c r="AG11" s="6"/>
       <c r="AH11" s="6"/>
       <c r="AI11" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/eljoy-barroca.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C11&amp;" "&amp;B11)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jake-barcenas.jpg</v>
       </c>
       <c r="AJ11" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="33.6">
+    <row r="12" spans="1:36">
       <c r="A12" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>C.</v>
+        <f>IF(D12="","",LEFT(TRIM(D12),1)&amp;".")</f>
+        <v>P.</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Angel C. Batuigas</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C12,IF(E12&lt;&gt;"",IF(RIGHT(E12,1)=".",E12,E12&amp;"."),D12),B12,F12))</f>
+        <v>Eljoy P. Barroca</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>12</v>
@@ -3395,17 +3394,15 @@
         <v>277</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>455</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="6" t="s">
@@ -3415,26 +3412,24 @@
         <v>17</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>456</v>
+        <v>341</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
       <c r="X12" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="Y12" s="6" t="s">
-        <v>458</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
       <c r="AA12" s="6"/>
       <c r="AB12" s="6"/>
       <c r="AC12" s="6" t="s">
-        <v>433</v>
+        <v>337</v>
       </c>
       <c r="AD12" s="6" t="s">
         <v>277</v>
@@ -3444,45 +3439,53 @@
       <c r="AG12" s="6"/>
       <c r="AH12" s="6"/>
       <c r="AI12" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/angel-batuigas.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C12&amp;" "&amp;B12)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/eljoy-barroca.jpg</v>
       </c>
       <c r="AJ12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:36" ht="33.6">
       <c r="A13" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>L.</v>
+        <f>IF(D13="","",LEFT(TRIM(D13),1)&amp;".")</f>
+        <v>C.</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Mary Josephine L. Bawiga</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C13,IF(E13&lt;&gt;"",IF(RIGHT(E13,1)=".",E13,E13&amp;"."),D13),B13,F13))</f>
+        <v>Angel C. Batuigas</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+        <v>277</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>455</v>
+      </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="6" t="s">
@@ -3492,77 +3495,73 @@
         <v>17</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>343</v>
+        <v>456</v>
       </c>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
       <c r="X13" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="Y13" s="6"/>
+        <v>457</v>
+      </c>
+      <c r="Y13" s="6" t="s">
+        <v>458</v>
+      </c>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
       <c r="AB13" s="6"/>
       <c r="AC13" s="6" t="s">
-        <v>337</v>
+        <v>433</v>
       </c>
       <c r="AD13" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE13" s="6"/>
       <c r="AF13" s="6"/>
       <c r="AG13" s="6"/>
       <c r="AH13" s="6"/>
       <c r="AI13" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/mary-josephine-bawiga.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C13&amp;" "&amp;B13)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/angel-batuigas.jpg</v>
       </c>
       <c r="AJ13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:36" ht="33.6">
       <c r="A14" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>P.</v>
+        <f>IF(D14="","",LEFT(TRIM(D14),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Endrie P. Bohol</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C14,IF(E14&lt;&gt;"",IF(RIGHT(E14,1)=".",E14,E14&amp;"."),D14),B14,F14))</f>
+        <v>Mary Josephine L. Bawiga</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>464</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -3570,81 +3569,81 @@
         <v>13</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
       <c r="X14" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="Y14" s="6" t="s">
-        <v>465</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
       <c r="AB14" s="6"/>
       <c r="AC14" s="6" t="s">
-        <v>433</v>
+        <v>337</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="AE14" s="6"/>
       <c r="AF14" s="6"/>
       <c r="AG14" s="6"/>
       <c r="AH14" s="6"/>
       <c r="AI14" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/endrie-bohol.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C14&amp;" "&amp;B14)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/mary-josephine-bawiga.jpg</v>
       </c>
       <c r="AJ14" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="33.6">
+    <row r="15" spans="1:36">
       <c r="A15" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>L.</v>
+        <f>IF(D15="","",LEFT(TRIM(D15),1)&amp;".")</f>
+        <v>P.</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Maine L. Bongas</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C15,IF(E15&lt;&gt;"",IF(RIGHT(E15,1)=".",E15,E15&amp;"."),D15),B15,F15))</f>
+        <v>Endrie P. Bohol</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>252</v>
+        <v>12</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>400</v>
+      </c>
       <c r="L15" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>468</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="6" t="s">
@@ -3654,39 +3653,37 @@
         <v>14</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
       <c r="X15" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="Z15" s="6"/>
       <c r="AA15" s="6"/>
       <c r="AB15" s="6"/>
       <c r="AC15" s="6" t="s">
-        <v>338</v>
+        <v>433</v>
       </c>
       <c r="AD15" s="6" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="AE15" s="6"/>
       <c r="AF15" s="6"/>
-      <c r="AG15" s="6">
-        <v>1</v>
-      </c>
+      <c r="AG15" s="6"/>
       <c r="AH15" s="6"/>
       <c r="AI15" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/maine-bongas.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C15&amp;" "&amp;B15)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/endrie-bohol.jpg</v>
       </c>
       <c r="AJ15" s="6" t="s">
         <v>9</v>
@@ -3694,47 +3691,47 @@
     </row>
     <row r="16" spans="1:36" ht="33.6">
       <c r="A16" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="E16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(D16="","",LEFT(TRIM(D16),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Ruth Briones</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C16,IF(E16&lt;&gt;"",IF(RIGHT(E16,1)=".",E16,E16&amp;"."),D16),B16,F16))</f>
+        <v>Maine L. Bongas</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>418</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="M16" s="5"/>
+        <v>467</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>334</v>
@@ -3747,61 +3744,69 @@
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
       <c r="AB16" s="6"/>
       <c r="AC16" s="6" t="s">
-        <v>433</v>
+        <v>338</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="AE16" s="6"/>
       <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
+      <c r="AG16" s="6">
+        <v>1</v>
+      </c>
       <c r="AH16" s="6"/>
       <c r="AI16" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/ruth-briones.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C16&amp;" "&amp;B16)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/maine-bongas.jpg</v>
       </c>
       <c r="AJ16" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:36">
+    <row r="17" spans="1:36" ht="33.6">
       <c r="A17" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>79</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>G.</v>
+        <f>IF(D17="","",LEFT(TRIM(D17),1)&amp;".")</f>
+        <v/>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Sharon G. Broñola</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C17,IF(E17&lt;&gt;"",IF(RIGHT(E17,1)=".",E17,E17&amp;"."),D17),B17,F17))</f>
+        <v>Ruth Briones</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
+      <c r="I17" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>471</v>
+      </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -3811,26 +3816,38 @@
       <c r="Q17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
+      <c r="R17" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
+      <c r="X17" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="Y17" s="6" t="s">
+        <v>473</v>
+      </c>
       <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
       <c r="AB17" s="6"/>
-      <c r="AC17" s="6"/>
-      <c r="AD17" s="6"/>
+      <c r="AC17" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD17" s="6" t="s">
+        <v>277</v>
+      </c>
       <c r="AE17" s="6"/>
       <c r="AF17" s="6"/>
       <c r="AG17" s="6"/>
       <c r="AH17" s="6"/>
       <c r="AI17" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/sharon-broñola.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C17&amp;" "&amp;B17)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/ruth-briones.jpg</v>
       </c>
       <c r="AJ17" s="6" t="s">
         <v>9</v>
@@ -3838,32 +3855,30 @@
     </row>
     <row r="18" spans="1:36">
       <c r="A18" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>A.</v>
+        <f>IF(D18="","",LEFT(TRIM(D18),1)&amp;".")</f>
+        <v>G.</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Joan A. Cabalda</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C18,IF(E18&lt;&gt;"",IF(RIGHT(E18,1)=".",E18,E18&amp;"."),D18),B18,F18))</f>
+        <v>Sharon G. Broñola</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>377</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="5"/>
@@ -3871,17 +3886,13 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>7</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
@@ -3898,40 +3909,40 @@
       <c r="AG18" s="6"/>
       <c r="AH18" s="6"/>
       <c r="AI18" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/joan-cabalda.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C18&amp;" "&amp;B18)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/sharon-broñola.jpg</v>
       </c>
       <c r="AJ18" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:36">
+    <row r="19" spans="1:36" ht="33.6">
       <c r="A19" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>M.</v>
+        <f>IF(D19="","",LEFT(TRIM(D19),1)&amp;".")</f>
+        <v>A.</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Gracelyn M. Cabunag</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C19,IF(E19&lt;&gt;"",IF(RIGHT(E19,1)=".",E19,E19&amp;"."),D19),B19,F19))</f>
+        <v>Joan A. Cabalda</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
@@ -3940,16 +3951,16 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>14</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>339</v>
+        <v>385</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>339</v>
+        <v>7</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
@@ -3961,16 +3972,14 @@
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
-      <c r="AD19" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="6"/>
       <c r="AH19" s="6"/>
       <c r="AI19" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/gracelyn-cabunag.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C19&amp;" "&amp;B19)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/joan-cabalda.jpg</v>
       </c>
       <c r="AJ19" s="6" t="s">
         <v>9</v>
@@ -3990,12 +3999,12 @@
         <v>82</v>
       </c>
       <c r="E20" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D20="","",LEFT(TRIM(D20),1)&amp;".")</f>
         <v>R.</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C20,IF(E20&lt;&gt;"",IF(RIGHT(E20,1)=".",E20,E20&amp;"."),D20),B20,F20))</f>
         <v>Hector R. Cabanca</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -4040,7 +4049,7 @@
       </c>
       <c r="AH20" s="6"/>
       <c r="AI20" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C20&amp;" "&amp;B20)," ","-"))&amp;".jpg"</f>
         <v>/personnel/hector-cabanca.jpg</v>
       </c>
       <c r="AJ20" s="6" t="s">
@@ -4061,12 +4070,12 @@
         <v>83</v>
       </c>
       <c r="E21" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D21="","",LEFT(TRIM(D21),1)&amp;".")</f>
         <v>A.</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C21,IF(E21&lt;&gt;"",IF(RIGHT(E21,1)=".",E21,E21&amp;"."),D21),B21,F21))</f>
         <v>Jeffrey A. Caberte</v>
       </c>
       <c r="H21" s="5" t="s">
@@ -4115,7 +4124,7 @@
       <c r="AG21" s="6"/>
       <c r="AH21" s="6"/>
       <c r="AI21" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C21&amp;" "&amp;B21)," ","-"))&amp;".jpg"</f>
         <v>/personnel/jeffrey-caberte.jpg</v>
       </c>
       <c r="AJ21" s="6" t="s">
@@ -4136,12 +4145,12 @@
         <v>84</v>
       </c>
       <c r="E22" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D22="","",LEFT(TRIM(D22),1)&amp;".")</f>
         <v>L.</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C22,IF(E22&lt;&gt;"",IF(RIGHT(E22,1)=".",E22,E22&amp;"."),D22),B22,F22))</f>
         <v>Marilou L. Cabriana</v>
       </c>
       <c r="H22" s="5" t="s">
@@ -4186,7 +4195,7 @@
       <c r="AG22" s="6"/>
       <c r="AH22" s="6"/>
       <c r="AI22" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C22&amp;" "&amp;B22)," ","-"))&amp;".jpg"</f>
         <v>/personnel/marilou-cabriana.jpg</v>
       </c>
       <c r="AJ22" s="6" t="s">
@@ -4195,31 +4204,31 @@
     </row>
     <row r="23" spans="1:36">
       <c r="A23" s="5">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>120</v>
+        <v>373</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>146</v>
+        <v>376</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="E23" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D23="","",LEFT(TRIM(D23),1)&amp;".")</f>
         <v>B.</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="str">
         <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C23,IF(E23&lt;&gt;"",IF(RIGHT(E23,1)=".",E23,E23&amp;"."),D23),B23,F23))</f>
-        <v>Jasmin B. Cabuenas</v>
+        <v>Luie B. Cabs</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>364</v>
+        <v>483</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -4228,16 +4237,16 @@
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="6" t="s">
-        <v>7</v>
+        <v>240</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>7</v>
+        <v>371</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>385</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>474</v>
+        <v>385</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
@@ -4250,15 +4259,15 @@
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
       <c r="AD23" s="6" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AE23" s="6"/>
       <c r="AF23" s="6"/>
       <c r="AG23" s="6"/>
       <c r="AH23" s="6"/>
       <c r="AI23" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jasmin-cabuenas.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C23&amp;" "&amp;B23)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/luie-cabs.jpg</v>
       </c>
       <c r="AJ23" s="6" t="s">
         <v>9</v>
@@ -4266,31 +4275,31 @@
     </row>
     <row r="24" spans="1:36">
       <c r="A24" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>C.</v>
+        <f>IF(D24="","",LEFT(TRIM(D24),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Elsa C. Calunod</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C24,IF(E24&lt;&gt;"",IF(RIGHT(E24,1)=".",E24,E24&amp;"."),D24),B24,F24))</f>
+        <v>Jasmin B. Cabuenas</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -4299,16 +4308,16 @@
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>334</v>
+        <v>385</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>334</v>
+        <v>474</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
@@ -4321,15 +4330,15 @@
       <c r="AB24" s="6"/>
       <c r="AC24" s="6"/>
       <c r="AD24" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AE24" s="6"/>
       <c r="AF24" s="6"/>
       <c r="AG24" s="6"/>
       <c r="AH24" s="6"/>
       <c r="AI24" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/elsa-calunod.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C24&amp;" "&amp;B24)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jasmin-cabuenas.jpg</v>
       </c>
       <c r="AJ24" s="6" t="s">
         <v>9</v>
@@ -4337,38 +4346,34 @@
     </row>
     <row r="25" spans="1:36">
       <c r="A25" s="5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E25" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>L.</v>
+        <f>IF(D25="","",LEFT(TRIM(D25),1)&amp;".")</f>
+        <v>M.</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Leslyn Rose L. Camero</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C25,IF(E25&lt;&gt;"",IF(RIGHT(E25,1)=".",E25,E25&amp;"."),D25),B25,F25))</f>
+        <v>Gracelyn M. Cabunag</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>12</v>
+        <v>249</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>403</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -4377,7 +4382,7 @@
         <v>13</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>339</v>
@@ -4396,15 +4401,15 @@
       <c r="AB25" s="6"/>
       <c r="AC25" s="6"/>
       <c r="AD25" s="6" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="AE25" s="6"/>
       <c r="AF25" s="6"/>
       <c r="AG25" s="6"/>
       <c r="AH25" s="6"/>
       <c r="AI25" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/leslyn-rose-camero.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C25&amp;" "&amp;B25)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/gracelyn-cabunag.jpg</v>
       </c>
       <c r="AJ25" s="6" t="s">
         <v>9</v>
@@ -4412,31 +4417,31 @@
     </row>
     <row r="26" spans="1:36">
       <c r="A26" s="5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E26" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>L.</v>
+        <f>IF(D26="","",LEFT(TRIM(D26),1)&amp;".")</f>
+        <v>C.</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Dawn Camille L. Caparida</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C26,IF(E26&lt;&gt;"",IF(RIGHT(E26,1)=".",E26,E26&amp;"."),D26),B26,F26))</f>
+        <v>Elsa C. Calunod</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>260</v>
+        <v>12</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
@@ -4445,16 +4450,16 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>17</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>7</v>
+        <v>334</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -4467,15 +4472,15 @@
       <c r="AB26" s="6"/>
       <c r="AC26" s="6"/>
       <c r="AD26" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AE26" s="6"/>
       <c r="AF26" s="6"/>
       <c r="AG26" s="6"/>
       <c r="AH26" s="6"/>
       <c r="AI26" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/dawn-camille-caparida.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C26&amp;" "&amp;B26)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/elsa-calunod.jpg</v>
       </c>
       <c r="AJ26" s="6" t="s">
         <v>9</v>
@@ -4483,35 +4488,37 @@
     </row>
     <row r="27" spans="1:36">
       <c r="A27" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>87</v>
+      </c>
       <c r="E27" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(D27="","",LEFT(TRIM(D27),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Lourence Capa</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C27,IF(E27&lt;&gt;"",IF(RIGHT(E27,1)=".",E27,E27&amp;"."),D27),B27,F27))</f>
+        <v>Leslyn Rose L. Camero</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>277</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -4524,10 +4531,10 @@
         <v>17</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
@@ -4547,8 +4554,8 @@
       <c r="AG27" s="6"/>
       <c r="AH27" s="6"/>
       <c r="AI27" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/lourence-capa.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C27&amp;" "&amp;B27)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/leslyn-rose-camero.jpg</v>
       </c>
       <c r="AJ27" s="6" t="s">
         <v>9</v>
@@ -4556,37 +4563,35 @@
     </row>
     <row r="28" spans="1:36">
       <c r="A28" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>88</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D28" s="5"/>
       <c r="E28" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>G.</v>
+        <f>IF(D28="","",LEFT(TRIM(D28),1)&amp;".")</f>
+        <v/>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Joan G. Cavite</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C28,IF(E28&lt;&gt;"",IF(RIGHT(E28,1)=".",E28,E28&amp;"."),D28),B28,F28))</f>
+        <v>Lourence Capa</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>277</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -4599,10 +4604,10 @@
         <v>17</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -4622,8 +4627,8 @@
       <c r="AG28" s="6"/>
       <c r="AH28" s="6"/>
       <c r="AI28" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/joan-cavite.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C28&amp;" "&amp;B28)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/lourence-capa.jpg</v>
       </c>
       <c r="AJ28" s="6" t="s">
         <v>9</v>
@@ -4631,54 +4636,50 @@
     </row>
     <row r="29" spans="1:36" ht="33.6">
       <c r="A29" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E29" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>C.</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>55</v>
-      </c>
+        <f>IF(D29="","",LEFT(TRIM(D29),1)&amp;".")</f>
+        <v>L.</v>
+      </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Joseph C. Dagaraga Jr.</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C29,IF(E29&lt;&gt;"",IF(RIGHT(E29,1)=".",E29,E29&amp;"."),D29),B29,F29))</f>
+        <v>Dawn Camille L. Caparida</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>421</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
       <c r="P29" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="S29" s="6"/>
+        <v>385</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
@@ -4690,15 +4691,15 @@
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
       <c r="AD29" s="6" t="s">
-        <v>277</v>
+        <v>364</v>
       </c>
       <c r="AE29" s="6"/>
       <c r="AF29" s="6"/>
       <c r="AG29" s="6"/>
       <c r="AH29" s="6"/>
       <c r="AI29" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/joseph-dagaraga.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C29&amp;" "&amp;B29)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/dawn-camille-caparida.jpg</v>
       </c>
       <c r="AJ29" s="6" t="s">
         <v>9</v>
@@ -4706,34 +4707,38 @@
     </row>
     <row r="30" spans="1:36">
       <c r="A30" s="5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E30" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>L.</v>
+        <f>IF(D30="","",LEFT(TRIM(D30),1)&amp;".")</f>
+        <v>G.</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Carolyn L. Delos Reyes</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C30,IF(E30&lt;&gt;"",IF(RIGHT(E30,1)=".",E30,E30&amp;"."),D30),B30,F30))</f>
+        <v>Joan G. Cavite</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>405</v>
+      </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -4745,12 +4750,12 @@
         <v>17</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6" t="s">
-        <v>474</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
@@ -4761,15 +4766,15 @@
       <c r="AB30" s="6"/>
       <c r="AC30" s="6"/>
       <c r="AD30" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE30" s="6"/>
       <c r="AF30" s="6"/>
       <c r="AG30" s="6"/>
       <c r="AH30" s="6"/>
       <c r="AI30" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/carolyn-delos-reyes.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C30&amp;" "&amp;B30)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/joan-cavite.jpg</v>
       </c>
       <c r="AJ30" s="6" t="s">
         <v>9</v>
@@ -4777,31 +4782,31 @@
     </row>
     <row r="31" spans="1:36">
       <c r="A31" s="5">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>126</v>
+        <v>237</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="E31" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>R.</v>
+        <f>IF(D31="","",LEFT(TRIM(D31),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Lucille R. Echavez</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C31,IF(E31&lt;&gt;"",IF(RIGHT(E31,1)=".",E31,E31&amp;"."),D31),B31,F31))</f>
+        <v>Diocel B. Celocia</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>16</v>
+        <v>269</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>369</v>
+        <v>482</v>
       </c>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
@@ -4810,16 +4815,16 @@
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="6" t="s">
-        <v>13</v>
+        <v>372</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>17</v>
+        <v>371</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="S31" s="6" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
@@ -4830,54 +4835,58 @@
       <c r="Z31" s="6"/>
       <c r="AA31" s="6"/>
       <c r="AB31" s="6"/>
-      <c r="AC31" s="6" t="s">
-        <v>337</v>
-      </c>
+      <c r="AC31" s="6"/>
       <c r="AD31" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AE31" s="6"/>
       <c r="AF31" s="6"/>
       <c r="AG31" s="6"/>
       <c r="AH31" s="6"/>
       <c r="AI31" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/lucille-echavez.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C31&amp;" "&amp;B31)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/diocel-celocia.jpg</v>
       </c>
       <c r="AJ31" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:36">
+    <row r="32" spans="1:36" ht="33.6">
       <c r="A32" s="5">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E32" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(D32="","",LEFT(TRIM(D32),1)&amp;".")</f>
         <v>C.</v>
       </c>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="G32" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Benerando C. Erediano</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C32,IF(E32&lt;&gt;"",IF(RIGHT(E32,1)=".",E32,E32&amp;"."),D32),B32,F32))</f>
+        <v>Joseph C. Dagaraga Jr.</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>270</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>421</v>
+      </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -4889,35 +4898,29 @@
         <v>14</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="S32" s="6" t="s">
-        <v>476</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="S32" s="6"/>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
       <c r="W32" s="6"/>
-      <c r="X32" s="6" t="s">
-        <v>475</v>
-      </c>
+      <c r="X32" s="6"/>
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
       <c r="AA32" s="6"/>
       <c r="AB32" s="6"/>
-      <c r="AC32" s="6" t="s">
-        <v>345</v>
-      </c>
+      <c r="AC32" s="6"/>
       <c r="AD32" s="6" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
       <c r="AG32" s="6"/>
       <c r="AH32" s="6"/>
       <c r="AI32" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/benerando-erediano.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C32&amp;" "&amp;B32)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/joseph-dagaraga.jpg</v>
       </c>
       <c r="AJ32" s="6" t="s">
         <v>9</v>
@@ -4925,31 +4928,31 @@
     </row>
     <row r="33" spans="1:36">
       <c r="A33" s="5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E33" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>A.</v>
+        <f>IF(D33="","",LEFT(TRIM(D33),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Metchie Gay A. Gastanes</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C33,IF(E33&lt;&gt;"",IF(RIGHT(E33,1)=".",E33,E33&amp;"."),D33),B33,F33))</f>
+        <v>Carolyn L. Delos Reyes</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>244</v>
+        <v>12</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
@@ -4964,12 +4967,12 @@
         <v>17</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="S33" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="T33" s="6"/>
+        <v>342</v>
+      </c>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="U33" s="6"/>
       <c r="V33" s="6"/>
       <c r="W33" s="6"/>
@@ -4980,17 +4983,15 @@
       <c r="AB33" s="6"/>
       <c r="AC33" s="6"/>
       <c r="AD33" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE33" s="6"/>
       <c r="AF33" s="6"/>
-      <c r="AG33" s="6">
-        <v>4</v>
-      </c>
+      <c r="AG33" s="6"/>
       <c r="AH33" s="6"/>
       <c r="AI33" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/metchie-gay-gastanes.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C33&amp;" "&amp;B33)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/carolyn-delos-reyes.jpg</v>
       </c>
       <c r="AJ33" s="6" t="s">
         <v>9</v>
@@ -4998,31 +4999,31 @@
     </row>
     <row r="34" spans="1:36">
       <c r="A34" s="5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E34" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>B.</v>
+        <f>IF(D34="","",LEFT(TRIM(D34),1)&amp;".")</f>
+        <v>R.</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Jasmin B. Gerodias</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C34,IF(E34&lt;&gt;"",IF(RIGHT(E34,1)=".",E34,E34&amp;"."),D34),B34,F34))</f>
+        <v>Lucille R. Echavez</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
@@ -5037,10 +5038,10 @@
         <v>17</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S34" s="6" t="s">
-        <v>477</v>
+        <v>343</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
@@ -5051,17 +5052,19 @@
       <c r="Z34" s="6"/>
       <c r="AA34" s="6"/>
       <c r="AB34" s="6"/>
-      <c r="AC34" s="6"/>
+      <c r="AC34" s="6" t="s">
+        <v>337</v>
+      </c>
       <c r="AD34" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AE34" s="6"/>
       <c r="AF34" s="6"/>
       <c r="AG34" s="6"/>
       <c r="AH34" s="6"/>
       <c r="AI34" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jasmin-gerodias.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C34&amp;" "&amp;B34)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/lucille-echavez.jpg</v>
       </c>
       <c r="AJ34" s="6" t="s">
         <v>9</v>
@@ -5069,38 +5072,34 @@
     </row>
     <row r="35" spans="1:36">
       <c r="A35" s="5">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E35" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>D.</v>
+        <f>IF(D35="","",LEFT(TRIM(D35),1)&amp;".")</f>
+        <v>C.</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Jeralyn D. Gerra</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C35,IF(E35&lt;&gt;"",IF(RIGHT(E35,1)=".",E35,E35&amp;"."),D35),B35,F35))</f>
+        <v>Benerando C. Erediano</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>12</v>
+        <v>270</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>406</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -5109,32 +5108,38 @@
         <v>13</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="S35" s="6"/>
+        <v>345</v>
+      </c>
+      <c r="S35" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="T35" s="6"/>
       <c r="U35" s="6"/>
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
+      <c r="X35" s="6" t="s">
+        <v>475</v>
+      </c>
       <c r="Y35" s="6"/>
       <c r="Z35" s="6"/>
       <c r="AA35" s="6"/>
       <c r="AB35" s="6"/>
-      <c r="AC35" s="6"/>
+      <c r="AC35" s="6" t="s">
+        <v>345</v>
+      </c>
       <c r="AD35" s="6" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="AE35" s="6"/>
       <c r="AF35" s="6"/>
       <c r="AG35" s="6"/>
       <c r="AH35" s="6"/>
       <c r="AI35" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jeralyn-gerra.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C35&amp;" "&amp;B35)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/benerando-erediano.jpg</v>
       </c>
       <c r="AJ35" s="6" t="s">
         <v>9</v>
@@ -5142,38 +5147,34 @@
     </row>
     <row r="36" spans="1:36">
       <c r="A36" s="5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E36" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>D.</v>
+        <f>IF(D36="","",LEFT(TRIM(D36),1)&amp;".")</f>
+        <v>A.</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Genesa D. Goc-ong</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C36,IF(E36&lt;&gt;"",IF(RIGHT(E36,1)=".",E36,E36&amp;"."),D36),B36,F36))</f>
+        <v>Metchie Gay A. Gastanes</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>407</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
@@ -5185,9 +5186,11 @@
         <v>17</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="S36" s="6"/>
+        <v>341</v>
+      </c>
+      <c r="S36" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
       <c r="V36" s="6"/>
@@ -5199,15 +5202,17 @@
       <c r="AB36" s="6"/>
       <c r="AC36" s="6"/>
       <c r="AD36" s="6" t="s">
-        <v>277</v>
+        <v>367</v>
       </c>
       <c r="AE36" s="6"/>
       <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
+      <c r="AG36" s="6">
+        <v>4</v>
+      </c>
       <c r="AH36" s="6"/>
       <c r="AI36" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/genesa-goc-ong.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C36&amp;" "&amp;B36)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/metchie-gay-gastanes.jpg</v>
       </c>
       <c r="AJ36" s="6" t="s">
         <v>9</v>
@@ -5215,31 +5220,31 @@
     </row>
     <row r="37" spans="1:36">
       <c r="A37" s="5">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E37" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>D.</v>
+        <f>IF(D37="","",LEFT(TRIM(D37),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>Janelou D. Gomez</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C37,IF(E37&lt;&gt;"",IF(RIGHT(E37,1)=".",E37,E37&amp;"."),D37),B37,F37))</f>
+        <v>Jasmin B. Gerodias</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>241</v>
+        <v>12</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
@@ -5254,9 +5259,11 @@
         <v>17</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="S37" s="6"/>
+        <v>344</v>
+      </c>
+      <c r="S37" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="T37" s="6"/>
       <c r="U37" s="6"/>
       <c r="V37" s="6"/>
@@ -5268,15 +5275,15 @@
       <c r="AB37" s="6"/>
       <c r="AC37" s="6"/>
       <c r="AD37" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AE37" s="6"/>
       <c r="AF37" s="6"/>
       <c r="AG37" s="6"/>
       <c r="AH37" s="6"/>
       <c r="AI37" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/janelou-gomez.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C37&amp;" "&amp;B37)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jasmin-gerodias.jpg</v>
       </c>
       <c r="AJ37" s="6" t="s">
         <v>9</v>
@@ -5284,25 +5291,25 @@
     </row>
     <row r="38" spans="1:36">
       <c r="A38" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E38" s="5" t="str">
-        <f t="shared" ref="E38:E65" si="4">IF(D38="","",LEFT(TRIM(D38),1)&amp;".")</f>
-        <v>R.</v>
+        <f>IF(D38="","",LEFT(TRIM(D38),1)&amp;".")</f>
+        <v>D.</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5" t="str">
-        <f t="shared" ref="G38:G65" si="5">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C38,IF(E38&lt;&gt;"",IF(RIGHT(E38,1)=".",E38,E38&amp;"."),D38),B38,F38))</f>
-        <v>Junnelyn R. Herbito</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C38,IF(E38&lt;&gt;"",IF(RIGHT(E38,1)=".",E38,E38&amp;"."),D38),B38,F38))</f>
+        <v>Jeralyn D. Gerra</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>12</v>
@@ -5311,10 +5318,10 @@
         <v>277</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
@@ -5329,9 +5336,7 @@
       <c r="R38" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="S38" s="6" t="s">
-        <v>334</v>
-      </c>
+      <c r="S38" s="6"/>
       <c r="T38" s="6"/>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
@@ -5350,8 +5355,8 @@
       <c r="AG38" s="6"/>
       <c r="AH38" s="6"/>
       <c r="AI38" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/junnelyn-herbito.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C38&amp;" "&amp;B38)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jeralyn-gerra.jpg</v>
       </c>
       <c r="AJ38" s="6" t="s">
         <v>9</v>
@@ -5359,25 +5364,25 @@
     </row>
     <row r="39" spans="1:36">
       <c r="A39" s="5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E39" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>T.</v>
+        <f>IF(D39="","",LEFT(TRIM(D39),1)&amp;".")</f>
+        <v>D.</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Roxan Mae T. Jao</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C39,IF(E39&lt;&gt;"",IF(RIGHT(E39,1)=".",E39,E39&amp;"."),D39),B39,F39))</f>
+        <v>Genesa D. Goc-ong</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>241</v>
@@ -5386,10 +5391,10 @@
         <v>277</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
@@ -5402,11 +5407,9 @@
         <v>17</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="S39" s="6" t="s">
-        <v>334</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="S39" s="6"/>
       <c r="T39" s="6"/>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
@@ -5425,8 +5428,8 @@
       <c r="AG39" s="6"/>
       <c r="AH39" s="6"/>
       <c r="AI39" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/roxan-mae-jao.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C39&amp;" "&amp;B39)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/genesa-goc-ong.jpg</v>
       </c>
       <c r="AJ39" s="6" t="s">
         <v>9</v>
@@ -5434,28 +5437,28 @@
     </row>
     <row r="40" spans="1:36">
       <c r="A40" s="5">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E40" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>H.</v>
+        <f>IF(D40="","",LEFT(TRIM(D40),1)&amp;".")</f>
+        <v>D.</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Fernando H. Laspiñas</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C40,IF(E40&lt;&gt;"",IF(RIGHT(E40,1)=".",E40,E40&amp;"."),D40),B40,F40))</f>
+        <v>Janelou D. Gomez</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>369</v>
@@ -5472,7 +5475,9 @@
       <c r="Q40" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R40" s="6"/>
+      <c r="R40" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="S40" s="6"/>
       <c r="T40" s="6"/>
       <c r="U40" s="6"/>
@@ -5492,8 +5497,8 @@
       <c r="AG40" s="6"/>
       <c r="AH40" s="6"/>
       <c r="AI40" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/fernando-laspiñas.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C40&amp;" "&amp;B40)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/janelou-gomez.jpg</v>
       </c>
       <c r="AJ40" s="6" t="s">
         <v>9</v>
@@ -5501,34 +5506,38 @@
     </row>
     <row r="41" spans="1:36">
       <c r="A41" s="5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E41" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>B.</v>
+        <f>IF(D41="","",LEFT(TRIM(D41),1)&amp;".")</f>
+        <v>R.</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Nerisa B. Lim</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C41,IF(E41&lt;&gt;"",IF(RIGHT(E41,1)=".",E41,E41&amp;"."),D41),B41,F41))</f>
+        <v>Junnelyn R. Herbito</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>408</v>
+      </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
@@ -5540,10 +5549,10 @@
         <v>17</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="S41" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="T41" s="6"/>
       <c r="U41" s="6"/>
@@ -5556,15 +5565,15 @@
       <c r="AB41" s="6"/>
       <c r="AC41" s="6"/>
       <c r="AD41" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE41" s="6"/>
       <c r="AF41" s="6"/>
       <c r="AG41" s="6"/>
       <c r="AH41" s="6"/>
       <c r="AI41" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/nerisa-lim.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C41&amp;" "&amp;B41)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/junnelyn-herbito.jpg</v>
       </c>
       <c r="AJ41" s="6" t="s">
         <v>9</v>
@@ -5572,32 +5581,38 @@
     </row>
     <row r="42" spans="1:36">
       <c r="A42" s="5">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>97</v>
+      </c>
       <c r="E42" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(D42="","",LEFT(TRIM(D42),1)&amp;".")</f>
+        <v>T.</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Carl Loreto</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C42,IF(E42&lt;&gt;"",IF(RIGHT(E42,1)=".",E42,E42&amp;"."),D42),B42,F42))</f>
+        <v>Roxan Mae T. Jao</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>409</v>
+      </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
@@ -5608,8 +5623,12 @@
       <c r="Q42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
+      <c r="R42" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="S42" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T42" s="6"/>
       <c r="U42" s="6"/>
       <c r="V42" s="6"/>
@@ -5621,15 +5640,15 @@
       <c r="AB42" s="6"/>
       <c r="AC42" s="6"/>
       <c r="AD42" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE42" s="6"/>
       <c r="AF42" s="6"/>
       <c r="AG42" s="6"/>
       <c r="AH42" s="6"/>
       <c r="AI42" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/carl-loreto.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C42&amp;" "&amp;B42)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/roxan-mae-jao.jpg</v>
       </c>
       <c r="AJ42" s="6" t="s">
         <v>9</v>
@@ -5637,31 +5656,31 @@
     </row>
     <row r="43" spans="1:36">
       <c r="A43" s="5">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E43" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>M.</v>
+        <f>IF(D43="","",LEFT(TRIM(D43),1)&amp;".")</f>
+        <v>H.</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Lyka M. Mabanag</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C43,IF(E43&lt;&gt;"",IF(RIGHT(E43,1)=".",E43,E43&amp;"."),D43),B43,F43))</f>
+        <v>Fernando H. Laspiñas</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>270</v>
+        <v>12</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
@@ -5673,7 +5692,7 @@
         <v>13</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R43" s="6"/>
       <c r="S43" s="6"/>
@@ -5688,15 +5707,15 @@
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
       <c r="AD43" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AE43" s="6"/>
       <c r="AF43" s="6"/>
       <c r="AG43" s="6"/>
       <c r="AH43" s="6"/>
       <c r="AI43" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/lyka-mabanag.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C43&amp;" "&amp;B43)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/fernando-laspiñas.jpg</v>
       </c>
       <c r="AJ43" s="6" t="s">
         <v>9</v>
@@ -5704,53 +5723,49 @@
     </row>
     <row r="44" spans="1:36">
       <c r="A44" s="5">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E44" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>C.</v>
+        <f>IF(D44="","",LEFT(TRIM(D44),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Richie Ryan C. Mabunay</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C44,IF(E44&lt;&gt;"",IF(RIGHT(E44,1)=".",E44,E44&amp;"."),D44),B44,F44))</f>
+        <v>Nerisa B. Lim</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
-      <c r="L44" s="5" t="s">
-        <v>333</v>
-      </c>
+      <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="5" t="s">
-        <v>332</v>
-      </c>
+      <c r="O44" s="5"/>
       <c r="P44" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q44" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>15</v>
+        <v>339</v>
       </c>
       <c r="S44" s="6" t="s">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
@@ -5763,15 +5778,15 @@
       <c r="AB44" s="6"/>
       <c r="AC44" s="6"/>
       <c r="AD44" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AE44" s="6"/>
       <c r="AF44" s="6"/>
       <c r="AG44" s="6"/>
       <c r="AH44" s="6"/>
       <c r="AI44" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/richie-ryan-mabunay.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C44&amp;" "&amp;B44)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/nerisa-lim.jpg</v>
       </c>
       <c r="AJ44" s="6" t="s">
         <v>9</v>
@@ -5779,28 +5794,26 @@
     </row>
     <row r="45" spans="1:36">
       <c r="A45" s="5">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>189</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D45" s="5"/>
       <c r="E45" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>H.</v>
+        <f>IF(D45="","",LEFT(TRIM(D45),1)&amp;".")</f>
+        <v/>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Maria Jeziel H. Macanin</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C45,IF(E45&lt;&gt;"",IF(RIGHT(E45,1)=".",E45,E45&amp;"."),D45),B45,F45))</f>
+        <v>Carl Loreto</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>369</v>
@@ -5817,9 +5830,7 @@
       <c r="Q45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R45" s="6" t="s">
-        <v>342</v>
-      </c>
+      <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
@@ -5839,8 +5850,8 @@
       <c r="AG45" s="6"/>
       <c r="AH45" s="6"/>
       <c r="AI45" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/maria-jeziel-macanin.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C45&amp;" "&amp;B45)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/carl-loreto.jpg</v>
       </c>
       <c r="AJ45" s="6" t="s">
         <v>9</v>
@@ -5848,38 +5859,34 @@
     </row>
     <row r="46" spans="1:36">
       <c r="A46" s="5">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="E46" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>L.</v>
+        <f>IF(D46="","",LEFT(TRIM(D46),1)&amp;".")</f>
+        <v>M.</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Jeralen L. Maloloy-on</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C46,IF(E46&lt;&gt;"",IF(RIGHT(E46,1)=".",E46,E46&amp;"."),D46),B46,F46))</f>
+        <v>Lyka M. Mabanag</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>12</v>
+        <v>270</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>410</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
@@ -5888,14 +5895,10 @@
         <v>13</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="R46" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="S46" s="6" t="s">
-        <v>341</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="6"/>
       <c r="V46" s="6"/>
@@ -5907,15 +5910,15 @@
       <c r="AB46" s="6"/>
       <c r="AC46" s="6"/>
       <c r="AD46" s="6" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="AE46" s="6"/>
       <c r="AF46" s="6"/>
       <c r="AG46" s="6"/>
       <c r="AH46" s="6"/>
       <c r="AI46" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jeralen-maloloy-on.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C46&amp;" "&amp;B46)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/lyka-mabanag.jpg</v>
       </c>
       <c r="AJ46" s="6" t="s">
         <v>9</v>
@@ -5923,53 +5926,53 @@
     </row>
     <row r="47" spans="1:36">
       <c r="A47" s="5">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="E47" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>L.</v>
+        <f>IF(D47="","",LEFT(TRIM(D47),1)&amp;".")</f>
+        <v>C.</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Elbert L. Misterio</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C47,IF(E47&lt;&gt;"",IF(RIGHT(E47,1)=".",E47,E47&amp;"."),D47),B47,F47))</f>
+        <v>Richie Ryan C. Mabunay</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="L47" s="5"/>
+        <v>379</v>
+      </c>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="5" t="s">
+        <v>333</v>
+      </c>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
+      <c r="O47" s="5" t="s">
+        <v>332</v>
+      </c>
       <c r="P47" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>343</v>
+        <v>15</v>
       </c>
       <c r="S47" s="6" t="s">
-        <v>343</v>
+        <v>476</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -5982,15 +5985,15 @@
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
       <c r="AD47" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AE47" s="6"/>
       <c r="AF47" s="6"/>
       <c r="AG47" s="6"/>
       <c r="AH47" s="6"/>
       <c r="AI47" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/elbert-misterio.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C47&amp;" "&amp;B47)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/richie-ryan-mabunay.jpg</v>
       </c>
       <c r="AJ47" s="6" t="s">
         <v>9</v>
@@ -5998,38 +6001,34 @@
     </row>
     <row r="48" spans="1:36">
       <c r="A48" s="5">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E48" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>E.</v>
+        <f>IF(D48="","",LEFT(TRIM(D48),1)&amp;".")</f>
+        <v>H.</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Joy E. Mortal</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C48,IF(E48&lt;&gt;"",IF(RIGHT(E48,1)=".",E48,E48&amp;"."),D48),B48,F48))</f>
+        <v>Maria Jeziel H. Macanin</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="K48" s="10" t="s">
-        <v>412</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
@@ -6040,7 +6039,9 @@
       <c r="Q48" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R48" s="6"/>
+      <c r="R48" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
@@ -6053,15 +6054,15 @@
       <c r="AB48" s="6"/>
       <c r="AC48" s="6"/>
       <c r="AD48" s="6" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="AE48" s="6"/>
       <c r="AF48" s="6"/>
       <c r="AG48" s="6"/>
       <c r="AH48" s="6"/>
       <c r="AI48" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/joy-mortal.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C48&amp;" "&amp;B48)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/maria-jeziel-macanin.jpg</v>
       </c>
       <c r="AJ48" s="6" t="s">
         <v>9</v>
@@ -6069,34 +6070,38 @@
     </row>
     <row r="49" spans="1:36">
       <c r="A49" s="5">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E49" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>B.</v>
+        <f>IF(D49="","",LEFT(TRIM(D49),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Claire B. Medillo</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C49,IF(E49&lt;&gt;"",IF(RIGHT(E49,1)=".",E49,E49&amp;"."),D49),B49,F49))</f>
+        <v>Jeralen L. Maloloy-on</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>410</v>
+      </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
@@ -6107,8 +6112,12 @@
       <c r="Q49" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
+      <c r="R49" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="S49" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T49" s="6"/>
       <c r="U49" s="6"/>
       <c r="V49" s="6"/>
@@ -6120,15 +6129,15 @@
       <c r="AB49" s="6"/>
       <c r="AC49" s="6"/>
       <c r="AD49" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE49" s="6"/>
       <c r="AF49" s="6"/>
       <c r="AG49" s="6"/>
       <c r="AH49" s="6"/>
       <c r="AI49" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/claire-medillo.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C49&amp;" "&amp;B49)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jeralen-maloloy-on.jpg</v>
       </c>
       <c r="AJ49" s="6" t="s">
         <v>9</v>
@@ -6136,53 +6145,49 @@
     </row>
     <row r="50" spans="1:36">
       <c r="A50" s="5">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>199</v>
+        <v>375</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E50" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>F.</v>
+        <f>IF(D50="","",LEFT(TRIM(D50),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Gwendolyn F. Olo</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C50,IF(E50&lt;&gt;"",IF(RIGHT(E50,1)=".",E50,E50&amp;"."),D50),B50,F50))</f>
+        <v>Luis B. Mans</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>12</v>
+        <v>267</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="K50" s="10" t="s">
-        <v>413</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
       <c r="P50" s="6" t="s">
-        <v>13</v>
+        <v>240</v>
       </c>
       <c r="Q50" s="5" t="s">
-        <v>17</v>
+        <v>371</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="S50" s="6" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="T50" s="6"/>
       <c r="U50" s="6"/>
@@ -6195,15 +6200,15 @@
       <c r="AB50" s="6"/>
       <c r="AC50" s="6"/>
       <c r="AD50" s="6" t="s">
-        <v>277</v>
+        <v>370</v>
       </c>
       <c r="AE50" s="6"/>
       <c r="AF50" s="6"/>
       <c r="AG50" s="6"/>
       <c r="AH50" s="6"/>
       <c r="AI50" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/gwendolyn-olo.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C50&amp;" "&amp;B50)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/luis-mans.jpg</v>
       </c>
       <c r="AJ50" s="6" t="s">
         <v>9</v>
@@ -6211,38 +6216,34 @@
     </row>
     <row r="51" spans="1:36">
       <c r="A51" s="5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E51" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(D51="","",LEFT(TRIM(D51),1)&amp;".")</f>
         <v>B.</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Jay Neil B. Oro</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C51,IF(E51&lt;&gt;"",IF(RIGHT(E51,1)=".",E51,E51&amp;"."),D51),B51,F51))</f>
+        <v>Claire B. Medillo</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J51" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>414</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
@@ -6266,15 +6267,15 @@
       <c r="AB51" s="6"/>
       <c r="AC51" s="6"/>
       <c r="AD51" s="6" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="AE51" s="6"/>
       <c r="AF51" s="6"/>
       <c r="AG51" s="6"/>
       <c r="AH51" s="6"/>
       <c r="AI51" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jay-neil-oro.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C51&amp;" "&amp;B51)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/claire-medillo.jpg</v>
       </c>
       <c r="AJ51" s="6" t="s">
         <v>9</v>
@@ -6282,25 +6283,25 @@
     </row>
     <row r="52" spans="1:36">
       <c r="A52" s="5">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E52" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>R.</v>
+        <f>IF(D52="","",LEFT(TRIM(D52),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Glendale R. Orocay</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C52,IF(E52&lt;&gt;"",IF(RIGHT(E52,1)=".",E52,E52&amp;"."),D52),B52,F52))</f>
+        <v>Elbert L. Misterio</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>12</v>
@@ -6309,10 +6310,10 @@
         <v>277</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
@@ -6322,13 +6323,13 @@
         <v>13</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>387</v>
+        <v>343</v>
       </c>
       <c r="S52" s="6" t="s">
-        <v>476</v>
+        <v>343</v>
       </c>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
@@ -6341,53 +6342,53 @@
       <c r="AB52" s="6"/>
       <c r="AC52" s="6"/>
       <c r="AD52" s="6" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="AE52" s="6"/>
       <c r="AF52" s="6"/>
       <c r="AG52" s="6"/>
       <c r="AH52" s="6"/>
       <c r="AI52" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/glendale-orocay.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C52&amp;" "&amp;B52)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/elbert-misterio.jpg</v>
       </c>
       <c r="AJ52" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="33.6">
+    <row r="53" spans="1:36">
       <c r="A53" s="5">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>57</v>
+        <v>195</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E53" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>J.</v>
+        <f>IF(D53="","",LEFT(TRIM(D53),1)&amp;".")</f>
+        <v>E.</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Marissa J. Pintuan</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C53,IF(E53&lt;&gt;"",IF(RIGHT(E53,1)=".",E53,E53&amp;"."),D53),B53,F53))</f>
+        <v>Joy E. Mortal</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>16</v>
+        <v>241</v>
       </c>
       <c r="I53" s="10" t="s">
         <v>277</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
@@ -6399,12 +6400,8 @@
       <c r="Q53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R53" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="S53" s="6" t="s">
-        <v>384</v>
-      </c>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6"/>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
       <c r="V53" s="6"/>
@@ -6423,8 +6420,8 @@
       <c r="AG53" s="6"/>
       <c r="AH53" s="6"/>
       <c r="AI53" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/marissa-pintuan.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C53&amp;" "&amp;B53)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/joy-mortal.jpg</v>
       </c>
       <c r="AJ53" s="6" t="s">
         <v>9</v>
@@ -6432,34 +6429,38 @@
     </row>
     <row r="54" spans="1:36">
       <c r="A54" s="5">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E54" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>B.</v>
+        <f>IF(D54="","",LEFT(TRIM(D54),1)&amp;".")</f>
+        <v>F.</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Ma. Lourdes B. Prajes</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C54,IF(E54&lt;&gt;"",IF(RIGHT(E54,1)=".",E54,E54&amp;"."),D54),B54,F54))</f>
+        <v>Gwendolyn F. Olo</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>413</v>
+      </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
@@ -6471,9 +6472,11 @@
         <v>17</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="S54" s="6"/>
+        <v>341</v>
+      </c>
+      <c r="S54" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="T54" s="6"/>
       <c r="U54" s="6"/>
       <c r="V54" s="6"/>
@@ -6485,15 +6488,15 @@
       <c r="AB54" s="6"/>
       <c r="AC54" s="6"/>
       <c r="AD54" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE54" s="6"/>
       <c r="AF54" s="6"/>
       <c r="AG54" s="6"/>
       <c r="AH54" s="6"/>
       <c r="AI54" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/ma.-lourdes-prajes.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C54&amp;" "&amp;B54)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/gwendolyn-olo.jpg</v>
       </c>
       <c r="AJ54" s="6" t="s">
         <v>9</v>
@@ -6501,25 +6504,25 @@
     </row>
     <row r="55" spans="1:36">
       <c r="A55" s="5">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E55" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>S.</v>
+        <f>IF(D55="","",LEFT(TRIM(D55),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Bret Kalvin S. Primacio</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C55,IF(E55&lt;&gt;"",IF(RIGHT(E55,1)=".",E55,E55&amp;"."),D55),B55,F55))</f>
+        <v>Jay Neil B. Oro</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>12</v>
@@ -6528,10 +6531,10 @@
         <v>277</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
@@ -6563,8 +6566,8 @@
       <c r="AG55" s="6"/>
       <c r="AH55" s="6"/>
       <c r="AI55" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/bret-kalvin-primacio.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C55&amp;" "&amp;B55)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jay-neil-oro.jpg</v>
       </c>
       <c r="AJ55" s="6" t="s">
         <v>9</v>
@@ -6572,34 +6575,38 @@
     </row>
     <row r="56" spans="1:36">
       <c r="A56" s="5">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E56" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>N.</v>
+        <f>IF(D56="","",LEFT(TRIM(D56),1)&amp;".")</f>
+        <v>R.</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Jhea N. Quiling</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C56,IF(E56&lt;&gt;"",IF(RIGHT(E56,1)=".",E56,E56&amp;"."),D56),B56,F56))</f>
+        <v>Glendale R. Orocay</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>423</v>
+      </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
@@ -6608,13 +6615,13 @@
         <v>13</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="S56" s="6" t="s">
-        <v>334</v>
+        <v>476</v>
       </c>
       <c r="T56" s="6"/>
       <c r="U56" s="6"/>
@@ -6627,50 +6634,54 @@
       <c r="AB56" s="6"/>
       <c r="AC56" s="6"/>
       <c r="AD56" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE56" s="6"/>
       <c r="AF56" s="6"/>
       <c r="AG56" s="6"/>
       <c r="AH56" s="6"/>
       <c r="AI56" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jhea-quiling.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C56&amp;" "&amp;B56)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/glendale-orocay.jpg</v>
       </c>
       <c r="AJ56" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" spans="1:36" ht="33.6">
       <c r="A57" s="5">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E57" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>C.</v>
+        <f>IF(D57="","",LEFT(TRIM(D57),1)&amp;".")</f>
+        <v>J.</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Joyce C. Racaza</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C57,IF(E57&lt;&gt;"",IF(RIGHT(E57,1)=".",E57,E57&amp;"."),D57),B57,F57))</f>
+        <v>Marissa J. Pintuan</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>420</v>
+      </c>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
@@ -6682,10 +6693,10 @@
         <v>17</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="S57" s="6" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="T57" s="6"/>
       <c r="U57" s="6"/>
@@ -6698,15 +6709,15 @@
       <c r="AB57" s="6"/>
       <c r="AC57" s="6"/>
       <c r="AD57" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE57" s="6"/>
       <c r="AF57" s="6"/>
       <c r="AG57" s="6"/>
       <c r="AH57" s="6"/>
       <c r="AI57" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/joyce-racaza.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C57&amp;" "&amp;B57)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/marissa-pintuan.jpg</v>
       </c>
       <c r="AJ57" s="6" t="s">
         <v>9</v>
@@ -6714,25 +6725,25 @@
     </row>
     <row r="58" spans="1:36">
       <c r="A58" s="5">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E58" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>P.</v>
+        <f>IF(D58="","",LEFT(TRIM(D58),1)&amp;".")</f>
+        <v>B.</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Cromwell P. Retuya</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C58,IF(E58&lt;&gt;"",IF(RIGHT(E58,1)=".",E58,E58&amp;"."),D58),B58,F58))</f>
+        <v>Ma. Lourdes B. Prajes</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>12</v>
@@ -6753,11 +6764,9 @@
         <v>17</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="S58" s="6" t="s">
-        <v>477</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="S58" s="6"/>
       <c r="T58" s="6"/>
       <c r="U58" s="6"/>
       <c r="V58" s="6"/>
@@ -6776,8 +6785,8 @@
       <c r="AG58" s="6"/>
       <c r="AH58" s="6"/>
       <c r="AI58" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/cromwell-retuya.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C58&amp;" "&amp;B58)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/ma.-lourdes-prajes.jpg</v>
       </c>
       <c r="AJ58" s="6" t="s">
         <v>9</v>
@@ -6785,34 +6794,38 @@
     </row>
     <row r="59" spans="1:36">
       <c r="A59" s="5">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E59" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>L.</v>
+        <f>IF(D59="","",LEFT(TRIM(D59),1)&amp;".")</f>
+        <v>S.</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Nancy L. Reyes</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C59,IF(E59&lt;&gt;"",IF(RIGHT(E59,1)=".",E59,E59&amp;"."),D59),B59,F59))</f>
+        <v>Bret Kalvin S. Primacio</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>415</v>
+      </c>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
@@ -6823,12 +6836,8 @@
       <c r="Q59" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R59" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="S59" s="6" t="s">
-        <v>384</v>
-      </c>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6"/>
       <c r="T59" s="6"/>
       <c r="U59" s="6"/>
       <c r="V59" s="6"/>
@@ -6840,17 +6849,15 @@
       <c r="AB59" s="6"/>
       <c r="AC59" s="6"/>
       <c r="AD59" s="6" t="s">
-        <v>367</v>
+        <v>277</v>
       </c>
       <c r="AE59" s="6"/>
       <c r="AF59" s="6"/>
-      <c r="AG59" s="6">
-        <v>5</v>
-      </c>
+      <c r="AG59" s="6"/>
       <c r="AH59" s="6"/>
       <c r="AI59" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/nancy-reyes.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C59&amp;" "&amp;B59)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/bret-kalvin-primacio.jpg</v>
       </c>
       <c r="AJ59" s="6" t="s">
         <v>9</v>
@@ -6858,38 +6865,34 @@
     </row>
     <row r="60" spans="1:36">
       <c r="A60" s="5">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E60" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>P.</v>
+        <f>IF(D60="","",LEFT(TRIM(D60),1)&amp;".")</f>
+        <v>N.</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Angelo P. Saavedra</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C60,IF(E60&lt;&gt;"",IF(RIGHT(E60,1)=".",E60,E60&amp;"."),D60),B60,F60))</f>
+        <v>Jhea N. Quiling</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="K60" s="10" t="s">
-        <v>416</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
@@ -6900,8 +6903,12 @@
       <c r="Q60" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
+      <c r="R60" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="S60" s="6" t="s">
+        <v>334</v>
+      </c>
       <c r="T60" s="6"/>
       <c r="U60" s="6"/>
       <c r="V60" s="6"/>
@@ -6913,15 +6920,15 @@
       <c r="AB60" s="6"/>
       <c r="AC60" s="6"/>
       <c r="AD60" s="6" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="AE60" s="6"/>
       <c r="AF60" s="6"/>
       <c r="AG60" s="6"/>
       <c r="AH60" s="6"/>
       <c r="AI60" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/angelo-saavedra.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C60&amp;" "&amp;B60)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jhea-quiling.jpg</v>
       </c>
       <c r="AJ60" s="6" t="s">
         <v>9</v>
@@ -6929,31 +6936,31 @@
     </row>
     <row r="61" spans="1:36">
       <c r="A61" s="5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E61" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>B.</v>
+        <f>IF(D61="","",LEFT(TRIM(D61),1)&amp;".")</f>
+        <v>C.</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Brendel B. Sacaris</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C61,IF(E61&lt;&gt;"",IF(RIGHT(E61,1)=".",E61,E61&amp;"."),D61),B61,F61))</f>
+        <v>Joyce C. Racaza</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>244</v>
+        <v>12</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
@@ -6968,10 +6975,10 @@
         <v>17</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>388</v>
+        <v>342</v>
       </c>
       <c r="S61" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="T61" s="6"/>
       <c r="U61" s="6"/>
@@ -6984,15 +6991,15 @@
       <c r="AB61" s="6"/>
       <c r="AC61" s="6"/>
       <c r="AD61" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AE61" s="6"/>
       <c r="AF61" s="6"/>
       <c r="AG61" s="6"/>
       <c r="AH61" s="6"/>
       <c r="AI61" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/brendel-sacaris.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C61&amp;" "&amp;B61)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/joyce-racaza.jpg</v>
       </c>
       <c r="AJ61" s="6" t="s">
         <v>9</v>
@@ -7000,38 +7007,34 @@
     </row>
     <row r="62" spans="1:36">
       <c r="A62" s="5">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E62" s="5" t="str">
         <f>IF(D62="","",LEFT(TRIM(D62),1)&amp;".")</f>
-        <v>T.</v>
+        <v>P.</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Bella Arquine T. Samontañez</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C62,IF(E62&lt;&gt;"",IF(RIGHT(E62,1)=".",E62,E62&amp;"."),D62),B62,F62))</f>
+        <v>Cromwell P. Retuya</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J62" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="K62" s="10" t="s">
-        <v>417</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
@@ -7042,7 +7045,9 @@
       <c r="Q62" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R62" s="6"/>
+      <c r="R62" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="S62" s="6" t="s">
         <v>477</v>
       </c>
@@ -7057,7 +7062,7 @@
       <c r="AB62" s="6"/>
       <c r="AC62" s="6"/>
       <c r="AD62" s="6" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="AE62" s="6"/>
       <c r="AF62" s="6"/>
@@ -7065,7 +7070,7 @@
       <c r="AH62" s="6"/>
       <c r="AI62" s="5" t="str">
         <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C62&amp;" "&amp;B62)," ","-"))&amp;".jpg"</f>
-        <v>/personnel/bella-arquine-samontañez.jpg</v>
+        <v>/personnel/cromwell-retuya.jpg</v>
       </c>
       <c r="AJ62" s="6" t="s">
         <v>9</v>
@@ -7073,38 +7078,34 @@
     </row>
     <row r="63" spans="1:36">
       <c r="A63" s="5">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E63" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>O.</v>
+        <f>IF(D63="","",LEFT(TRIM(D63),1)&amp;".")</f>
+        <v>L.</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Jevy Ann O. Uy</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C63,IF(E63&lt;&gt;"",IF(RIGHT(E63,1)=".",E63,E63&amp;"."),D63),B63,F63))</f>
+        <v>Nancy L. Reyes</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>249</v>
+        <v>12</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="K63" s="10" t="s">
-        <v>424</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
@@ -7113,13 +7114,13 @@
         <v>13</v>
       </c>
       <c r="Q63" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="S63" s="6" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
@@ -7132,15 +7133,17 @@
       <c r="AB63" s="6"/>
       <c r="AC63" s="6"/>
       <c r="AD63" s="6" t="s">
-        <v>277</v>
+        <v>367</v>
       </c>
       <c r="AE63" s="6"/>
       <c r="AF63" s="6"/>
-      <c r="AG63" s="6"/>
+      <c r="AG63" s="6">
+        <v>5</v>
+      </c>
       <c r="AH63" s="6"/>
       <c r="AI63" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/jevy-ann-uy.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C63&amp;" "&amp;B63)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/nancy-reyes.jpg</v>
       </c>
       <c r="AJ63" s="6" t="s">
         <v>9</v>
@@ -7148,34 +7151,38 @@
     </row>
     <row r="64" spans="1:36">
       <c r="A64" s="5">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>98</v>
+        <v>219</v>
       </c>
       <c r="E64" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>H.</v>
+        <f>IF(D64="","",LEFT(TRIM(D64),1)&amp;".")</f>
+        <v>P.</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Grace H. Vergara</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C64,IF(E64&lt;&gt;"",IF(RIGHT(E64,1)=".",E64,E64&amp;"."),D64),B64,F64))</f>
+        <v>Angelo P. Saavedra</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>416</v>
+      </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
@@ -7186,12 +7193,8 @@
       <c r="Q64" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R64" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="S64" s="6" t="s">
-        <v>342</v>
-      </c>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
       <c r="T64" s="6"/>
       <c r="U64" s="6"/>
       <c r="V64" s="6"/>
@@ -7203,15 +7206,15 @@
       <c r="AB64" s="6"/>
       <c r="AC64" s="6"/>
       <c r="AD64" s="6" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="AE64" s="6"/>
       <c r="AF64" s="6"/>
       <c r="AG64" s="6"/>
       <c r="AH64" s="6"/>
       <c r="AI64" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/grace-vergara.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C64&amp;" "&amp;B64)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/angelo-saavedra.jpg</v>
       </c>
       <c r="AJ64" s="6" t="s">
         <v>9</v>
@@ -7219,31 +7222,31 @@
     </row>
     <row r="65" spans="1:36">
       <c r="A65" s="5">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="E65" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(D65="","",LEFT(TRIM(D65),1)&amp;".")</f>
         <v>B.</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>Guillermo B. Villavelez</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C65,IF(E65&lt;&gt;"",IF(RIGHT(E65,1)=".",E65,E65&amp;"."),D65),B65,F65))</f>
+        <v>Brendel B. Sacaris</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>271</v>
+        <v>392</v>
       </c>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
@@ -7252,16 +7255,16 @@
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
       <c r="P65" s="6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q65" s="5" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="S65" s="6" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
@@ -7274,50 +7277,54 @@
       <c r="AB65" s="6"/>
       <c r="AC65" s="6"/>
       <c r="AD65" s="6" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="AE65" s="6"/>
       <c r="AF65" s="6"/>
       <c r="AG65" s="6"/>
       <c r="AH65" s="6"/>
       <c r="AI65" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/guillermo-villavelez.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C65&amp;" "&amp;B65)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/brendel-sacaris.jpg</v>
       </c>
       <c r="AJ65" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:36">
+    <row r="66" spans="1:36" ht="33.6">
       <c r="A66" s="5">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="E66" s="5" t="str">
-        <f t="shared" ref="E66:E71" si="6">IF(D66="","",LEFT(TRIM(D66),1)&amp;".")</f>
-        <v>A.</v>
+        <f>IF(D66="","",LEFT(TRIM(D66),1)&amp;".")</f>
+        <v>T.</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5" t="str">
-        <f t="shared" ref="G66:G67" si="7">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C66,IF(E66&lt;&gt;"",IF(RIGHT(E66,1)=".",E66,E66&amp;"."),D66),B66,F66))</f>
-        <v>Marilou A. Villaver</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C66,IF(E66&lt;&gt;"",IF(RIGHT(E66,1)=".",E66,E66&amp;"."),D66),B66,F66))</f>
+        <v>Bella Arquine T. Samontañez</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>417</v>
+      </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
@@ -7326,13 +7333,11 @@
         <v>13</v>
       </c>
       <c r="Q66" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="R66" s="6" t="s">
-        <v>339</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="R66" s="6"/>
       <c r="S66" s="6" t="s">
-        <v>339</v>
+        <v>477</v>
       </c>
       <c r="T66" s="6"/>
       <c r="U66" s="6"/>
@@ -7345,15 +7350,15 @@
       <c r="AB66" s="6"/>
       <c r="AC66" s="6"/>
       <c r="AD66" s="6" t="s">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="AE66" s="6"/>
       <c r="AF66" s="6"/>
       <c r="AG66" s="6"/>
       <c r="AH66" s="6"/>
       <c r="AI66" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>/personnel/marilou-villaver.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C66&amp;" "&amp;B66)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/bella-arquine-samontañez.jpg</v>
       </c>
       <c r="AJ66" s="6" t="s">
         <v>9</v>
@@ -7361,49 +7366,53 @@
     </row>
     <row r="67" spans="1:36">
       <c r="A67" s="5">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E67" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>Z.</v>
+        <f>IF(D67="","",LEFT(TRIM(D67),1)&amp;".")</f>
+        <v>O.</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>Markjil Z. Bacaltos</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C67,IF(E67&lt;&gt;"",IF(RIGHT(E67,1)=".",E67,E67&amp;"."),D67),B67,F67))</f>
+        <v>Jevy Ann O. Uy</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>424</v>
+      </c>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
       <c r="P67" s="6" t="s">
-        <v>372</v>
+        <v>13</v>
       </c>
       <c r="Q67" s="5" t="s">
-        <v>371</v>
+        <v>14</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="S67" s="6" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="T67" s="6"/>
       <c r="U67" s="6"/>
@@ -7416,15 +7425,15 @@
       <c r="AB67" s="6"/>
       <c r="AC67" s="6"/>
       <c r="AD67" s="6" t="s">
-        <v>370</v>
+        <v>277</v>
       </c>
       <c r="AE67" s="6"/>
       <c r="AF67" s="6"/>
       <c r="AG67" s="6"/>
       <c r="AH67" s="6"/>
       <c r="AI67" s="5" t="str">
-        <f t="shared" ref="AI67:AI68" si="8">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
-        <v>/personnel/markjil-bacaltos.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C67&amp;" "&amp;B67)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/jevy-ann-uy.jpg</v>
       </c>
       <c r="AJ67" s="6" t="s">
         <v>9</v>
@@ -7432,31 +7441,31 @@
     </row>
     <row r="68" spans="1:36">
       <c r="A68" s="5">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="E68" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>B.</v>
+        <f>IF(D68="","",LEFT(TRIM(D68),1)&amp;".")</f>
+        <v>H.</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5" t="str">
-        <f t="shared" ref="G68" si="9">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C68,IF(E68&lt;&gt;"",IF(RIGHT(E68,1)=".",E68,E68&amp;"."),D68),B68,F68))</f>
-        <v>Diocel B. Celocia</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C68,IF(E68&lt;&gt;"",IF(RIGHT(E68,1)=".",E68,E68&amp;"."),D68),B68,F68))</f>
+        <v>Grace H. Vergara</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>269</v>
+        <v>12</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
@@ -7465,16 +7474,16 @@
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
       <c r="P68" s="6" t="s">
-        <v>372</v>
+        <v>13</v>
       </c>
       <c r="Q68" s="5" t="s">
-        <v>371</v>
+        <v>17</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="S68" s="6" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="T68" s="6"/>
       <c r="U68" s="6"/>
@@ -7487,15 +7496,15 @@
       <c r="AB68" s="6"/>
       <c r="AC68" s="6"/>
       <c r="AD68" s="6" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AE68" s="6"/>
       <c r="AF68" s="6"/>
       <c r="AG68" s="6"/>
       <c r="AH68" s="6"/>
       <c r="AI68" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>/personnel/diocel-celocia.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C68&amp;" "&amp;B68)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/grace-vergara.jpg</v>
       </c>
       <c r="AJ68" s="6" t="s">
         <v>9</v>
@@ -7503,31 +7512,31 @@
     </row>
     <row r="69" spans="1:36">
       <c r="A69" s="5">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>373</v>
+        <v>230</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>376</v>
+        <v>231</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>198</v>
+        <v>104</v>
       </c>
       <c r="E69" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(D69="","",LEFT(TRIM(D69),1)&amp;".")</f>
         <v>B.</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5" t="str">
-        <f t="shared" ref="G69:G70" si="10">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C69,IF(E69&lt;&gt;"",IF(RIGHT(E69,1)=".",E69,E69&amp;"."),D69),B69,F69))</f>
-        <v>Luie B. Cabs</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C69,IF(E69&lt;&gt;"",IF(RIGHT(E69,1)=".",E69,E69&amp;"."),D69),B69,F69))</f>
+        <v>Guillermo B. Villavelez</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>370</v>
+        <v>271</v>
       </c>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
@@ -7536,16 +7545,16 @@
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
       <c r="P69" s="6" t="s">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="Q69" s="5" t="s">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>385</v>
       </c>
       <c r="S69" s="6" t="s">
-        <v>385</v>
+        <v>7</v>
       </c>
       <c r="T69" s="6"/>
       <c r="U69" s="6"/>
@@ -7558,15 +7567,15 @@
       <c r="AB69" s="6"/>
       <c r="AC69" s="6"/>
       <c r="AD69" s="6" t="s">
-        <v>370</v>
+        <v>271</v>
       </c>
       <c r="AE69" s="6"/>
       <c r="AF69" s="6"/>
       <c r="AG69" s="6"/>
       <c r="AH69" s="6"/>
       <c r="AI69" s="5" t="str">
-        <f t="shared" ref="AI69:AI70" si="11">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
-        <v>/personnel/luie-cabs.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C69&amp;" "&amp;B69)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/guillermo-villavelez.jpg</v>
       </c>
       <c r="AJ69" s="6" t="s">
         <v>9</v>
@@ -7574,31 +7583,31 @@
     </row>
     <row r="70" spans="1:36">
       <c r="A70" s="5">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>374</v>
+        <v>232</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>375</v>
+        <v>145</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="E70" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>B.</v>
+        <f>IF(D70="","",LEFT(TRIM(D70),1)&amp;".")</f>
+        <v>A.</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v>Luis B. Mans</v>
+        <f>TRIM(_xlfn.TEXTJOIN(" ",TRUE,C70,IF(E70&lt;&gt;"",IF(RIGHT(E70,1)=".",E70,E70&amp;"."),D70),B70,F70))</f>
+        <v>Marilou A. Villaver</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
@@ -7607,16 +7616,16 @@
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
       <c r="P70" s="6" t="s">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="Q70" s="5" t="s">
-        <v>371</v>
+        <v>14</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>385</v>
+        <v>339</v>
       </c>
       <c r="S70" s="6" t="s">
-        <v>385</v>
+        <v>339</v>
       </c>
       <c r="T70" s="6"/>
       <c r="U70" s="6"/>
@@ -7629,15 +7638,15 @@
       <c r="AB70" s="6"/>
       <c r="AC70" s="6"/>
       <c r="AD70" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AE70" s="6"/>
       <c r="AF70" s="6"/>
       <c r="AG70" s="6"/>
       <c r="AH70" s="6"/>
       <c r="AI70" s="5" t="str">
-        <f t="shared" si="11"/>
-        <v>/personnel/luis-mans.jpg</v>
+        <f>"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C70&amp;" "&amp;B70)," ","-"))&amp;".jpg"</f>
+        <v>/personnel/marilou-villaver.jpg</v>
       </c>
       <c r="AJ70" s="6" t="s">
         <v>9</v>
@@ -7651,7 +7660,7 @@
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(D71="","",LEFT(TRIM(D71),1)&amp;".")</f>
         <v/>
       </c>
       <c r="F71" s="5"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A4156A-61C5-4F35-A02A-3EF891CEF649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF7F748-A227-49A9-A125-900F3BE35132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="511">
   <si>
     <t>order</t>
   </si>
@@ -1378,9 +1378,6 @@
     <t>Araling Panlipunan Coordinator (SHS)</t>
   </si>
   <si>
-    <t>AP</t>
-  </si>
-  <si>
     <t>Araling Panlipunan 9</t>
   </si>
   <si>
@@ -1561,16 +1558,16 @@
     <t>"Everything is a process, don't skip, don't jump to the next level without the experience needed."</t>
   </si>
   <si>
-    <t>Grade Leader (Grade 10)</t>
-  </si>
-  <si>
-    <t>Grade Leader (Grade 9)</t>
-  </si>
-  <si>
-    <t>Grade Leader (Grade 8)</t>
-  </si>
-  <si>
-    <t>Grade Leader (Grade 7)</t>
+    <t>10th Grade - Grade Leader</t>
+  </si>
+  <si>
+    <t>9th Grade - Grade Leader</t>
+  </si>
+  <si>
+    <t>8th Grade - Grade Leader</t>
+  </si>
+  <si>
+    <t>7th Grade - Grade Leader</t>
   </si>
 </sst>
 </file>
@@ -2665,16 +2662,16 @@
         <v>419</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>470</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>471</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>420</v>
@@ -2710,10 +2707,10 @@
         <v>362</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AK1" s="5" t="s">
         <v>5</v>
@@ -2748,12 +2745,12 @@
         <v>10</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -2795,7 +2792,7 @@
       <c r="AH2" s="8"/>
       <c r="AI2" s="8"/>
       <c r="AJ2" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f t="shared" ref="AK2:AK33" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
@@ -2871,7 +2868,7 @@
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
       <c r="AC3" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>276</v>
@@ -2921,7 +2918,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -2943,7 +2940,7 @@
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
@@ -2961,7 +2958,7 @@
       <c r="AH4" s="8"/>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AK4" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3106,14 +3103,14 @@
         <v>434</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Y6" s="8" t="s">
         <v>435</v>
@@ -3190,17 +3187,17 @@
         <v>14</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
@@ -3218,7 +3215,7 @@
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AK7" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3323,7 +3320,7 @@
         <v>268</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -3413,17 +3410,17 @@
         <v>16</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -3609,7 +3606,7 @@
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AK12" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3660,7 +3657,7 @@
         <v>445</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="8" t="s">
@@ -3673,23 +3670,23 @@
         <v>341</v>
       </c>
       <c r="S13" s="8" t="s">
-        <v>447</v>
+        <v>341</v>
       </c>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y13" s="8" t="s">
         <v>448</v>
-      </c>
-      <c r="Y13" s="8" t="s">
-        <v>449</v>
       </c>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AD13" s="8" t="s">
         <v>276</v>
@@ -3700,7 +3697,7 @@
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AK13" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3736,7 +3733,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -3761,7 +3758,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
@@ -3822,7 +3819,7 @@
         <v>393</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -3844,16 +3841,16 @@
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AD15" s="8" t="s">
         <v>276</v>
@@ -3864,7 +3861,7 @@
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AK15" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3905,13 +3902,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="M16" s="7" t="s">
-        <v>459</v>
-      </c>
       <c r="N16" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="8" t="s">
@@ -3931,10 +3928,10 @@
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y16" s="8" t="s">
         <v>460</v>
-      </c>
-      <c r="Y16" s="8" t="s">
-        <v>461</v>
       </c>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
@@ -3953,7 +3950,7 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AK16" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3996,7 +3993,7 @@
         <v>411</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -4018,16 +4015,16 @@
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y17" s="8" t="s">
         <v>463</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>464</v>
       </c>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AD17" s="8" t="s">
         <v>276</v>
@@ -4103,7 +4100,7 @@
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AK18" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4210,7 +4207,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -4433,7 +4430,7 @@
         <v>266</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -4524,7 +4521,7 @@
         <v>382</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
@@ -4691,7 +4688,7 @@
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
       <c r="AJ26" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AK26" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4770,7 +4767,7 @@
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AK27" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4847,7 +4844,7 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AK28" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5033,7 +5030,7 @@
         <v>268</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -5204,7 +5201,7 @@
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
@@ -5299,7 +5296,7 @@
       <c r="AH34" s="8"/>
       <c r="AI34" s="8"/>
       <c r="AJ34" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AK34" s="7" t="str">
         <f t="shared" ref="AK34:AK70" si="5">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C34&amp;" "&amp;B34)," ","-"))&amp;".jpg"</f>
@@ -5350,17 +5347,17 @@
         <v>14</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
@@ -5412,7 +5409,7 @@
         <v>243</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -5502,10 +5499,10 @@
         <v>16</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
@@ -5901,7 +5898,7 @@
       <c r="AH42" s="8"/>
       <c r="AI42" s="8"/>
       <c r="AJ42" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AK42" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6112,7 +6109,7 @@
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
       <c r="AJ45" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AK45" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6148,7 +6145,7 @@
         <v>269</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
@@ -6239,14 +6236,14 @@
         <v>434</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
@@ -6262,7 +6259,7 @@
       <c r="AH47" s="8"/>
       <c r="AI47" s="8"/>
       <c r="AJ47" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AK47" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6446,7 +6443,7 @@
         <v>266</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
@@ -6694,7 +6691,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
@@ -6711,10 +6708,10 @@
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ53" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AK53" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6866,7 +6863,7 @@
       <c r="AH55" s="8"/>
       <c r="AI55" s="8"/>
       <c r="AJ55" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AK55" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6924,7 +6921,7 @@
         <v>434</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
@@ -7361,10 +7358,10 @@
         <v>16</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
@@ -7419,7 +7416,7 @@
         <v>243</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
@@ -7460,7 +7457,7 @@
       <c r="AH63" s="8"/>
       <c r="AI63" s="8"/>
       <c r="AJ63" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AK63" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7535,7 +7532,7 @@
       <c r="AH64" s="8"/>
       <c r="AI64" s="8"/>
       <c r="AJ64" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AK64" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7598,7 +7595,7 @@
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
       <c r="X65" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
@@ -7636,12 +7633,12 @@
         <v>222</v>
       </c>
       <c r="E66" s="7" t="str">
-        <f t="shared" ref="E66:E97" si="6">IF(D66="","",LEFT(TRIM(D66),1)&amp;".")</f>
+        <f t="shared" ref="E66:E71" si="6">IF(D66="","",LEFT(TRIM(D66),1)&amp;".")</f>
         <v>T.</v>
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7" t="str">
-        <f t="shared" ref="G66:G97" si="7">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C66,IF(E66&lt;&gt;"",IF(RIGHT(E66,1)=".",E66,E66&amp;"."),D66),B66,F66))</f>
+        <f t="shared" ref="G66:G70" si="7">TRIM(_xlfn.TEXTJOIN(" ",TRUE,C66,IF(E66&lt;&gt;"",IF(RIGHT(E66,1)=".",E66,E66&amp;"."),D66),B66,F66))</f>
         <v>Bella Arquine T. Samontañez</v>
       </c>
       <c r="H66" s="7" t="s">
@@ -7667,10 +7664,10 @@
         <v>16</v>
       </c>
       <c r="R66" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S66" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T66" s="8"/>
       <c r="U66" s="8"/>
@@ -7841,7 +7838,7 @@
       <c r="AH68" s="8"/>
       <c r="AI68" s="8"/>
       <c r="AJ68" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AK68" s="7" t="str">
         <f t="shared" si="5"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF7F748-A227-49A9-A125-900F3BE35132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A45A3-9911-49B0-87C1-CCDF7DF5E568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="517">
   <si>
     <t>order</t>
   </si>
@@ -1568,6 +1568,24 @@
   </si>
   <si>
     <t>7th Grade - Grade Leader</t>
+  </si>
+  <si>
+    <t>Hairdressing NCII</t>
+  </si>
+  <si>
+    <t>glendale.orocay@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>"I believe every learner can succeed with proper guidance, encouragement, and opportunities to grow. As a Hairdressing Teacher, I help students build skills, confidence, and creativity for lifelong success."</t>
+  </si>
+  <si>
+    <t>Guidance Designate for Junior High School</t>
+  </si>
+  <si>
+    <t>carolyn.delosreyes002@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>"My teaching philosophy us that every learner is capable of growth when given support, respect, and meaningful learning experiences. I believe teaching should be student-centered, where learners actively construct understanding through engagement, critical thinking, and real-life connections. My role is to guide, motivate, and create an inclusive environment where students feel safe to ask questions, make mistakes, and improve continuously."</t>
   </si>
 </sst>
 </file>
@@ -5156,7 +5174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:38">
+    <row r="33" spans="1:38" ht="218.4">
       <c r="A33" s="7">
         <v>29</v>
       </c>
@@ -5179,10 +5197,10 @@
         <v>Carolyn L. Delos Reyes</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>368</v>
+        <v>514</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -5219,8 +5237,12 @@
       <c r="AF33" s="8"/>
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
-      <c r="AI33" s="8"/>
-      <c r="AJ33" s="6"/>
+      <c r="AI33" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="AJ33" s="6" t="s">
+        <v>516</v>
+      </c>
       <c r="AK33" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/carolyn-delos-reyes.jpg</v>
@@ -6873,7 +6895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:38">
+    <row r="56" spans="1:38" ht="100.8">
       <c r="A56" s="7">
         <v>51</v>
       </c>
@@ -6927,7 +6949,9 @@
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
-      <c r="X56" s="8"/>
+      <c r="X56" s="8" t="s">
+        <v>511</v>
+      </c>
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
@@ -6940,8 +6964,12 @@
       <c r="AF56" s="8"/>
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
-      <c r="AI56" s="8"/>
-      <c r="AJ56" s="6"/>
+      <c r="AI56" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="AJ56" s="6" t="s">
+        <v>513</v>
+      </c>
       <c r="AK56" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/glendale-orocay.jpg</v>
@@ -8058,31 +8086,31 @@
           <x14:formula1>
             <xm:f>Dropdown_Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P70</xm:sqref>
+          <xm:sqref>P57:P70 P2:P32 P34:P55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{909FCDCA-C40C-4807-A52A-02A68E381F21}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$B$2:$B$35</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H70</xm:sqref>
+          <xm:sqref>H57:H70 H2:H32 H34:H55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>AL2:AL71</xm:sqref>
+          <xm:sqref>AL57:AL71 AL2:AL32 AL34:AL55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70D54F6E-2A67-40F0-92CA-B6E53F44843D}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$D$2:$D$61</xm:f>
           </x14:formula1>
-          <xm:sqref>AD2:AD71</xm:sqref>
+          <xm:sqref>AD57:AD71 AD2:AD32 AD34:AD55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7834D497-9733-4178-89DF-4B7895726F53}">
           <x14:formula1>
             <xm:f>Dropdown_Lists!$E$2:$E$60</xm:f>
           </x14:formula1>
-          <xm:sqref>AE2:AE71</xm:sqref>
+          <xm:sqref>AE57:AE71 AE2:AE32 AE34:AE55</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A45A3-9911-49B0-87C1-CCDF7DF5E568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E923B6-4374-43B9-99D9-399F4BF7BA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="517">
   <si>
     <t>order</t>
   </si>
@@ -1153,18 +1153,6 @@
     <t>Job Order/Support Personnel</t>
   </si>
   <si>
-    <t>Cabs</t>
-  </si>
-  <si>
-    <t>Mans</t>
-  </si>
-  <si>
-    <t>Luis</t>
-  </si>
-  <si>
-    <t>Luie</t>
-  </si>
-  <si>
     <t>Senior High School In-Charge</t>
   </si>
   <si>
@@ -1586,6 +1574,18 @@
   </si>
   <si>
     <t>"My teaching philosophy us that every learner is capable of growth when given support, respect, and meaningful learning experiences. I believe teaching should be student-centered, where learners actively construct understanding through engagement, critical thinking, and real-life connections. My role is to guide, motivate, and create an inclusive environment where students feel safe to ask questions, make mistakes, and improve continuously."</t>
+  </si>
+  <si>
+    <t>Caballero</t>
+  </si>
+  <si>
+    <t>Rocer</t>
+  </si>
+  <si>
+    <t>Rellon</t>
+  </si>
+  <si>
+    <t>Severino</t>
   </si>
 </sst>
 </file>
@@ -2650,10 +2650,10 @@
         <v>323</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>324</v>
@@ -2677,37 +2677,37 @@
         <v>4</v>
       </c>
       <c r="S1" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="X1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>421</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>425</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>359</v>
@@ -2725,10 +2725,10 @@
         <v>362</v>
       </c>
       <c r="AI1" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
         <v>473</v>
-      </c>
-      <c r="AJ1" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="AK1" s="5" t="s">
         <v>5</v>
@@ -2763,12 +2763,12 @@
         <v>10</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -2790,7 +2790,7 @@
       <c r="V2" s="8"/>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
@@ -2810,7 +2810,7 @@
       <c r="AH2" s="8"/>
       <c r="AI2" s="8"/>
       <c r="AJ2" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f t="shared" ref="AK2:AK33" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
@@ -2852,7 +2852,7 @@
         <v>352</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -2875,18 +2875,18 @@
       <c r="V3" s="8"/>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
       <c r="AC3" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>276</v>
@@ -2931,12 +2931,12 @@
         <v>240</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="7" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -2958,7 +2958,7 @@
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
@@ -2976,7 +2976,7 @@
       <c r="AH4" s="8"/>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AK4" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3018,13 +3018,13 @@
         <v>354</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -3045,10 +3045,10 @@
       <c r="V5" s="8"/>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
@@ -3105,7 +3105,7 @@
         <v>355</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -3118,20 +3118,20 @@
         <v>14</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
@@ -3188,13 +3188,13 @@
         <v>353</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -3205,17 +3205,17 @@
         <v>14</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
@@ -3233,7 +3233,7 @@
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AK7" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3282,7 +3282,7 @@
         <v>7</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
@@ -3338,7 +3338,7 @@
         <v>268</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -3353,10 +3353,10 @@
         <v>370</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
@@ -3411,12 +3411,12 @@
         <v>243</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="7" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -3428,17 +3428,17 @@
         <v>16</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -3496,13 +3496,13 @@
         <v>354</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -3513,17 +3513,17 @@
         <v>14</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
@@ -3581,10 +3581,10 @@
         <v>352</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -3606,7 +3606,7 @@
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
@@ -3624,7 +3624,7 @@
       <c r="AH12" s="8"/>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="6" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="AK12" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3666,16 +3666,16 @@
         <v>356</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="8" t="s">
@@ -3695,16 +3695,16 @@
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="Y13" s="8" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AD13" s="8" t="s">
         <v>276</v>
@@ -3715,7 +3715,7 @@
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
       <c r="AJ13" s="6" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="AK13" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3751,7 +3751,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -3776,7 +3776,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
@@ -3834,10 +3834,10 @@
         <v>351</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -3859,16 +3859,16 @@
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AD15" s="8" t="s">
         <v>276</v>
@@ -3879,7 +3879,7 @@
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AK15" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3920,13 +3920,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="8" t="s">
@@ -3946,10 +3946,10 @@
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Y16" s="8" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
@@ -3968,7 +3968,7 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="6" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="AK16" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4008,10 +4008,10 @@
         <v>351</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -4033,16 +4033,16 @@
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="Y17" s="8" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AD17" s="8" t="s">
         <v>276</v>
@@ -4118,7 +4118,7 @@
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AK18" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4154,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
@@ -4169,7 +4169,7 @@
         <v>14</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S19" s="8" t="s">
         <v>7</v>
@@ -4225,7 +4225,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -4304,7 +4304,7 @@
         <v>353</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
@@ -4381,7 +4381,7 @@
         <v>354</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -4427,28 +4427,26 @@
         <v>68</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>372</v>
+        <v>513</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="D23" s="7"/>
       <c r="E23" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>B.</v>
+        <v/>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>Luie B. Cabs</v>
+        <v>Rocer Caballero</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>266</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -4463,10 +4461,10 @@
         <v>370</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
@@ -4489,7 +4487,7 @@
       <c r="AJ23" s="6"/>
       <c r="AK23" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>/personnel/luie-cabs.jpg</v>
+        <v>/personnel/rocer-caballero.jpg</v>
       </c>
       <c r="AL23" s="8" t="s">
         <v>9</v>
@@ -4536,10 +4534,10 @@
         <v>7</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
@@ -4594,7 +4592,7 @@
         <v>248</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
@@ -4667,7 +4665,7 @@
         <v>15</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -4706,7 +4704,7 @@
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
       <c r="AJ26" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AK26" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4748,7 +4746,7 @@
         <v>351</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
@@ -4785,7 +4783,7 @@
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AK27" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4825,7 +4823,7 @@
         <v>353</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
@@ -4862,7 +4860,7 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="AK28" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4898,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
@@ -4913,7 +4911,7 @@
         <v>16</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S29" s="8" t="s">
         <v>7</v>
@@ -4977,7 +4975,7 @@
         <v>354</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
@@ -5048,7 +5046,7 @@
         <v>268</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -5063,10 +5061,10 @@
         <v>370</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
@@ -5129,7 +5127,7 @@
         <v>355</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
@@ -5200,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -5219,7 +5217,7 @@
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
@@ -5238,10 +5236,10 @@
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AJ33" s="6" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AK33" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5318,7 +5316,7 @@
       <c r="AH34" s="8"/>
       <c r="AI34" s="8"/>
       <c r="AJ34" s="6" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AK34" s="7" t="str">
         <f t="shared" ref="AK34:AK70" si="5">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C34&amp;" "&amp;B34)," ","-"))&amp;".jpg"</f>
@@ -5369,17 +5367,17 @@
         <v>14</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
@@ -5431,7 +5429,7 @@
         <v>243</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -5506,7 +5504,7 @@
         <v>12</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
@@ -5521,10 +5519,10 @@
         <v>16</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
@@ -5585,7 +5583,7 @@
         <v>352</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
@@ -5660,7 +5658,7 @@
         <v>352</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
@@ -5806,7 +5804,7 @@
         <v>351</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
@@ -5883,7 +5881,7 @@
         <v>354</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
@@ -5920,7 +5918,7 @@
       <c r="AH42" s="8"/>
       <c r="AI42" s="8"/>
       <c r="AJ42" s="6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="AK42" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6131,7 +6129,7 @@
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
       <c r="AJ45" s="6" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="AK45" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6167,7 +6165,7 @@
         <v>269</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
@@ -6236,7 +6234,7 @@
         <v>249</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
@@ -6255,17 +6253,17 @@
         <v>14</v>
       </c>
       <c r="R47" s="8" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
@@ -6281,7 +6279,7 @@
       <c r="AH47" s="8"/>
       <c r="AI47" s="8"/>
       <c r="AJ47" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AK47" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6394,7 +6392,7 @@
         <v>353</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
@@ -6444,28 +6442,26 @@
         <v>69</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>373</v>
+        <v>515</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="D50" s="7"/>
       <c r="E50" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>B.</v>
+        <v/>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7" t="str">
         <f t="shared" si="4"/>
-        <v>Luis B. Mans</v>
+        <v>Severino Rellon</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>266</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
@@ -6480,10 +6476,10 @@
         <v>370</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S50" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
@@ -6506,7 +6502,7 @@
       <c r="AJ50" s="6"/>
       <c r="AK50" s="7" t="str">
         <f t="shared" si="5"/>
-        <v>/personnel/luis-mans.jpg</v>
+        <v>/personnel/severino-rellon.jpg</v>
       </c>
       <c r="AL50" s="8" t="s">
         <v>9</v>
@@ -6613,7 +6609,7 @@
         <v>351</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
@@ -6690,7 +6686,7 @@
         <v>352</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
@@ -6713,7 +6709,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
@@ -6730,10 +6726,10 @@
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AJ53" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AK53" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6775,7 +6771,7 @@
         <v>351</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -6852,7 +6848,7 @@
         <v>354</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
@@ -6885,7 +6881,7 @@
       <c r="AH55" s="8"/>
       <c r="AI55" s="8"/>
       <c r="AJ55" s="6" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="AK55" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6927,7 +6923,7 @@
         <v>356</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
@@ -6940,17 +6936,17 @@
         <v>14</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
@@ -6965,10 +6961,10 @@
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="AK56" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7010,7 +7006,7 @@
         <v>355</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
@@ -7096,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="R58" s="8" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
@@ -7158,7 +7154,7 @@
         <v>352</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
@@ -7386,10 +7382,10 @@
         <v>16</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
@@ -7444,7 +7440,7 @@
         <v>243</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
@@ -7485,7 +7481,7 @@
       <c r="AH63" s="8"/>
       <c r="AI63" s="8"/>
       <c r="AJ63" s="6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AK63" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7527,7 +7523,7 @@
         <v>353</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
@@ -7560,7 +7556,7 @@
       <c r="AH64" s="8"/>
       <c r="AI64" s="8"/>
       <c r="AJ64" s="6" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AK64" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7596,7 +7592,7 @@
         <v>243</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
@@ -7617,13 +7613,13 @@
         <v>338</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="U65" s="8"/>
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
       <c r="X65" s="8" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
@@ -7679,7 +7675,7 @@
         <v>353</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
@@ -7692,10 +7688,10 @@
         <v>16</v>
       </c>
       <c r="R66" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="S66" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="T66" s="8"/>
       <c r="U66" s="8"/>
@@ -7756,7 +7752,7 @@
         <v>356</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
@@ -7827,7 +7823,7 @@
         <v>243</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
@@ -7866,7 +7862,7 @@
       <c r="AH68" s="8"/>
       <c r="AI68" s="8"/>
       <c r="AJ68" s="6" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AK68" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7917,7 +7913,7 @@
         <v>7</v>
       </c>
       <c r="R69" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="S69" s="8" t="s">
         <v>7</v>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E923B6-4374-43B9-99D9-399F4BF7BA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DA8D6D-E7D2-4E4D-9574-C8A55B642AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="518">
   <si>
     <t>order</t>
   </si>
@@ -1586,6 +1586,9 @@
   </si>
   <si>
     <t>Severino</t>
+  </si>
+  <si>
+    <t>Guildance Counselor</t>
   </si>
 </sst>
 </file>
@@ -4519,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>363</v>
+        <v>517</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DA8D6D-E7D2-4E4D-9574-C8A55B642AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81E1C55-E51B-4732-B64E-B2E8DD79EEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4169,7 +4169,7 @@
         <v>7</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R19" s="8" t="s">
         <v>378</v>
@@ -4911,7 +4911,7 @@
         <v>7</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R29" s="8" t="s">
         <v>378</v>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81E1C55-E51B-4732-B64E-B2E8DD79EEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4E8284-6376-43C0-9AD2-1022770DDD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="557">
   <si>
     <t>order</t>
   </si>
@@ -1363,9 +1363,6 @@
     <t>Boys Scout of the Philippines Coordinator</t>
   </si>
   <si>
-    <t>Araling Panlipunan Coordinator (SHS)</t>
-  </si>
-  <si>
     <t>Araling Panlipunan 9</t>
   </si>
   <si>
@@ -1387,18 +1384,12 @@
     <t>MAPEH 7 &amp; 10</t>
   </si>
   <si>
-    <t>SHS Mathematics Coordinator</t>
-  </si>
-  <si>
     <t>Mathematics 7 &amp; 8</t>
   </si>
   <si>
     <t>General Mathemathics</t>
   </si>
   <si>
-    <t>SHS English Coordinator</t>
-  </si>
-  <si>
     <t>Learning Action Cell (LAC) Coordinator for SHS</t>
   </si>
   <si>
@@ -1471,9 +1462,6 @@
     <t>Computer Programming (JAVA) 11 &amp; 12</t>
   </si>
   <si>
-    <t>English Coordinator</t>
-  </si>
-  <si>
     <t>Girl Scout of the Philippines (GSP) Coordinator</t>
   </si>
   <si>
@@ -1589,6 +1577,135 @@
   </si>
   <si>
     <t>Guildance Counselor</t>
+  </si>
+  <si>
+    <t>Cluster 9 Sports Coordinator</t>
+  </si>
+  <si>
+    <t>Araling Panlipunan 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>joseph.allosada@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>paz.abad001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>jake.barcenas@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>eljoy.barroca@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>angel.batuigas@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>maryjosephine.bawiga@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>gracelyn.cabunag@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>elsa.calunod@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>joan.cavite@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>lucille.echavez001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>metchiegay.azucenas@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>junnelyn.herbito@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>roxanmae.jao@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>richieryan.mabunay@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>jayneil.oro@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>lyka.mabanag@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>cromwell.retuya@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>angelo.saavedra@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>nancy.reyes006@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>grace.vergara006@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>jeralyn.gerra@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>ninakristine.alinsonorin@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>sharongay.alsa@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Homeroom Guidance Program 10</t>
+  </si>
+  <si>
+    <t>Homeroom Guidance Program 7</t>
+  </si>
+  <si>
+    <t>"Behind every lesson is a teacher who hopes, sacrifices, and believes in every learner. I teach not only to educate minds but also to touch hearts and help shape a better future."</t>
+  </si>
+  <si>
+    <t>hector.cabanca001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>“Great teachers don’t just teach subjects—they shape lives.”</t>
+  </si>
+  <si>
+    <t>"Teaching is touching hearts, opening minds, and building futures."</t>
+  </si>
+  <si>
+    <t>SMEA Coordinator</t>
+  </si>
+  <si>
+    <t>SugBusog Coordinator</t>
+  </si>
+  <si>
+    <t>Mathematics 10</t>
+  </si>
+  <si>
+    <t>Cultural Dance Troupe Coordinator</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (Science, SHS)</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (English)</t>
+  </si>
+  <si>
+    <t>Work Immersion Focal</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (Filipino)</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (Araling Panlipunan, SHS)</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator Mathematics, SHS)</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (English, SHS)</t>
+  </si>
+  <si>
+    <t>marilou.cabriana001@deped.gov.ph</t>
   </si>
 </sst>
 </file>
@@ -2617,7 +2734,8 @@
     <col min="18" max="23" width="45.19921875" style="11" customWidth="1"/>
     <col min="24" max="24" width="47.19921875" style="11" customWidth="1"/>
     <col min="25" max="29" width="45.19921875" style="11" customWidth="1"/>
-    <col min="30" max="35" width="24.19921875" style="11" customWidth="1"/>
+    <col min="30" max="34" width="24.19921875" style="11" customWidth="1"/>
+    <col min="35" max="35" width="37.69921875" style="11" customWidth="1"/>
     <col min="36" max="36" width="32.3984375" style="10" customWidth="1"/>
     <col min="37" max="37" width="36.69921875" style="9" customWidth="1"/>
     <col min="38" max="38" width="6.3984375" style="11" bestFit="1" customWidth="1"/>
@@ -2683,16 +2801,16 @@
         <v>415</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="W1" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>466</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>416</v>
@@ -2728,10 +2846,10 @@
         <v>362</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AK1" s="5" t="s">
         <v>5</v>
@@ -2766,12 +2884,12 @@
         <v>10</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>478</v>
+        <v>550</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -2811,9 +2929,11 @@
         <v>2</v>
       </c>
       <c r="AH2" s="8"/>
-      <c r="AI2" s="8"/>
+      <c r="AI2" s="8" t="s">
+        <v>517</v>
+      </c>
       <c r="AJ2" s="6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f t="shared" ref="AK2:AK33" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
@@ -2889,7 +3009,7 @@
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
       <c r="AC3" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>276</v>
@@ -2939,7 +3059,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="7" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -2961,7 +3081,7 @@
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
@@ -2977,9 +3097,11 @@
       <c r="AF4" s="8"/>
       <c r="AG4" s="8"/>
       <c r="AH4" s="8"/>
-      <c r="AI4" s="8"/>
+      <c r="AI4" s="8" t="s">
+        <v>516</v>
+      </c>
       <c r="AJ4" s="6" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AK4" s="7" t="str">
         <f t="shared" si="2"/>
@@ -2989,7 +3111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="33.6">
+    <row r="5" spans="1:38" ht="84">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -3053,7 +3175,9 @@
       <c r="Y5" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="Z5" s="8"/>
+      <c r="Z5" s="8" t="s">
+        <v>539</v>
+      </c>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
       <c r="AC5" s="8" t="s">
@@ -3066,8 +3190,12 @@
       <c r="AF5" s="8"/>
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
-      <c r="AI5" s="8"/>
-      <c r="AJ5" s="6"/>
+      <c r="AI5" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>541</v>
+      </c>
       <c r="AK5" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/sharon-gay-alsa.jpg</v>
@@ -3124,14 +3252,14 @@
         <v>430</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="Y6" s="8" t="s">
         <v>431</v>
@@ -3208,17 +3336,17 @@
         <v>14</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
@@ -3236,7 +3364,7 @@
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AK7" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3305,7 +3433,9 @@
       <c r="AF8" s="8"/>
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
-      <c r="AI8" s="8"/>
+      <c r="AI8" s="8" t="s">
+        <v>537</v>
+      </c>
       <c r="AJ8" s="6"/>
       <c r="AK8" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3341,7 +3471,7 @@
         <v>268</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -3431,17 +3561,17 @@
         <v>16</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -3542,7 +3672,9 @@
       <c r="AF11" s="8"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
+      <c r="AI11" s="8" t="s">
+        <v>518</v>
+      </c>
       <c r="AJ11" s="6"/>
       <c r="AK11" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3625,9 +3757,11 @@
       <c r="AF12" s="8"/>
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
+      <c r="AI12" s="8" t="s">
+        <v>519</v>
+      </c>
       <c r="AJ12" s="6" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="AK12" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3672,13 +3806,13 @@
         <v>411</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>442</v>
+        <v>553</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>441</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="8" t="s">
@@ -3698,16 +3832,16 @@
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="Y13" s="8" t="s">
         <v>443</v>
-      </c>
-      <c r="Y13" s="8" t="s">
-        <v>444</v>
       </c>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AD13" s="8" t="s">
         <v>276</v>
@@ -3716,9 +3850,11 @@
       <c r="AF13" s="8"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
-      <c r="AI13" s="8"/>
+      <c r="AI13" s="8" t="s">
+        <v>520</v>
+      </c>
       <c r="AJ13" s="6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="AK13" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3751,14 +3887,16 @@
         <v>Mary Josephine L. Bawiga</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
-      <c r="L14" s="7"/>
+      <c r="L14" s="7" t="s">
+        <v>514</v>
+      </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
@@ -3779,7 +3917,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
@@ -3795,7 +3933,9 @@
       <c r="AF14" s="8"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
+      <c r="AI14" s="8" t="s">
+        <v>521</v>
+      </c>
       <c r="AJ14" s="6"/>
       <c r="AK14" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3840,7 +3980,7 @@
         <v>389</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>450</v>
+        <v>554</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -3862,16 +4002,16 @@
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AD15" s="8" t="s">
         <v>276</v>
@@ -3882,7 +4022,7 @@
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="6" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AK15" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3923,13 +4063,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7" t="s">
-        <v>453</v>
+        <v>555</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="8" t="s">
@@ -3949,10 +4089,10 @@
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Y16" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
@@ -3971,7 +4111,7 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="6" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="AK16" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4014,7 +4154,7 @@
         <v>407</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -4036,16 +4176,16 @@
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="Y17" s="8" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AD17" s="8" t="s">
         <v>276</v>
@@ -4108,9 +4248,15 @@
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="X18" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="Y18" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="Z18" s="8" t="s">
+        <v>540</v>
+      </c>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
       <c r="AC18" s="8"/>
@@ -4121,7 +4267,7 @@
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AK18" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4202,7 +4348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:38">
+    <row r="20" spans="1:38" ht="33.6">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -4228,7 +4374,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -4265,8 +4411,12 @@
         <v>3</v>
       </c>
       <c r="AH20" s="8"/>
-      <c r="AI20" s="8"/>
-      <c r="AJ20" s="6"/>
+      <c r="AI20" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="AJ20" s="6" t="s">
+        <v>543</v>
+      </c>
       <c r="AK20" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/hector-cabanca.jpg</v>
@@ -4386,7 +4536,9 @@
       <c r="K22" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="L22" s="7"/>
+      <c r="L22" s="7" t="s">
+        <v>552</v>
+      </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -4396,13 +4548,19 @@
       <c r="Q22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
+      <c r="R22" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>338</v>
+      </c>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
+      <c r="X22" s="8" t="s">
+        <v>338</v>
+      </c>
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
@@ -4416,7 +4574,9 @@
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="8"/>
-      <c r="AJ22" s="6"/>
+      <c r="AJ22" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="AK22" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-cabriana.jpg</v>
@@ -4430,10 +4590,10 @@
         <v>68</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="str">
@@ -4449,7 +4609,7 @@
         <v>266</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -4522,7 +4682,7 @@
         <v>261</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
@@ -4540,7 +4700,7 @@
         <v>378</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
@@ -4632,7 +4792,9 @@
       <c r="AF25" s="8"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
-      <c r="AI25" s="8"/>
+      <c r="AI25" s="8" t="s">
+        <v>522</v>
+      </c>
       <c r="AJ25" s="6"/>
       <c r="AK25" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4705,9 +4867,11 @@
       <c r="AF26" s="8"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
-      <c r="AI26" s="8"/>
+      <c r="AI26" s="8" t="s">
+        <v>523</v>
+      </c>
       <c r="AJ26" s="6" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="AK26" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4786,7 +4950,7 @@
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="6" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="AK27" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4863,7 +5027,7 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AK28" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5013,7 +5177,9 @@
       <c r="AF30" s="8"/>
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
-      <c r="AI30" s="8"/>
+      <c r="AI30" s="8" t="s">
+        <v>524</v>
+      </c>
       <c r="AJ30" s="6"/>
       <c r="AK30" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5049,7 +5215,7 @@
         <v>268</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -5201,7 +5367,7 @@
         <v>15</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -5220,7 +5386,7 @@
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
@@ -5239,10 +5405,10 @@
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="AJ33" s="6" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AK33" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5317,9 +5483,11 @@
       <c r="AF34" s="8"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
-      <c r="AI34" s="8"/>
+      <c r="AI34" s="8" t="s">
+        <v>525</v>
+      </c>
       <c r="AJ34" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AK34" s="7" t="str">
         <f t="shared" ref="AK34:AK70" si="5">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C34&amp;" "&amp;B34)," ","-"))&amp;".jpg"</f>
@@ -5370,17 +5538,17 @@
         <v>14</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
@@ -5432,7 +5600,7 @@
         <v>243</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
@@ -5471,7 +5639,9 @@
         <v>4</v>
       </c>
       <c r="AH36" s="8"/>
-      <c r="AI36" s="8"/>
+      <c r="AI36" s="8" t="s">
+        <v>526</v>
+      </c>
       <c r="AJ36" s="6"/>
       <c r="AK36" s="7" t="str">
         <f t="shared" si="5"/>
@@ -5522,10 +5692,10 @@
         <v>16</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
@@ -5554,7 +5724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:38">
+    <row r="38" spans="1:38" ht="33.6">
       <c r="A38" s="7">
         <v>34</v>
       </c>
@@ -5619,8 +5789,12 @@
       <c r="AF38" s="8"/>
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
-      <c r="AI38" s="8"/>
-      <c r="AJ38" s="6"/>
+      <c r="AI38" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="AJ38" s="6" t="s">
+        <v>544</v>
+      </c>
       <c r="AK38" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/jeralyn-gerra.jpg</v>
@@ -5842,7 +6016,9 @@
       <c r="AF41" s="8"/>
       <c r="AG41" s="8"/>
       <c r="AH41" s="8"/>
-      <c r="AI41" s="8"/>
+      <c r="AI41" s="8" t="s">
+        <v>527</v>
+      </c>
       <c r="AJ41" s="6"/>
       <c r="AK41" s="7" t="str">
         <f t="shared" si="5"/>
@@ -5919,9 +6095,11 @@
       <c r="AF42" s="8"/>
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
-      <c r="AI42" s="8"/>
+      <c r="AI42" s="8" t="s">
+        <v>528</v>
+      </c>
       <c r="AJ42" s="6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="AK42" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6023,7 +6201,7 @@
         <v>Nerisa B. Lim</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>368</v>
@@ -6096,8 +6274,8 @@
       <c r="H45" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="6" t="s">
-        <v>368</v>
+      <c r="I45" s="7" t="s">
+        <v>545</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
@@ -6111,8 +6289,12 @@
       <c r="Q45" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R45" s="8"/>
-      <c r="S45" s="8"/>
+      <c r="R45" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="S45" s="8" t="s">
+        <v>340</v>
+      </c>
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
       <c r="V45" s="8"/>
@@ -6132,7 +6314,7 @@
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
       <c r="AJ45" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AK45" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6142,7 +6324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:38">
+    <row r="46" spans="1:38" ht="33.6">
       <c r="A46" s="7">
         <v>42</v>
       </c>
@@ -6168,12 +6350,16 @@
         <v>269</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>479</v>
+        <v>549</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
+      <c r="L46" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>551</v>
+      </c>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
       <c r="P46" s="8" t="s">
@@ -6182,13 +6368,19 @@
       <c r="Q46" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
+      <c r="R46" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="S46" s="8" t="s">
+        <v>340</v>
+      </c>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
       <c r="V46" s="8"/>
       <c r="W46" s="8"/>
-      <c r="X46" s="8"/>
+      <c r="X46" s="8" t="s">
+        <v>340</v>
+      </c>
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
@@ -6201,7 +6393,9 @@
       <c r="AF46" s="8"/>
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
-      <c r="AI46" s="8"/>
+      <c r="AI46" s="8" t="s">
+        <v>531</v>
+      </c>
       <c r="AJ46" s="6"/>
       <c r="AK46" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6259,14 +6453,14 @@
         <v>430</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
@@ -6280,9 +6474,11 @@
       <c r="AF47" s="8"/>
       <c r="AG47" s="8"/>
       <c r="AH47" s="8"/>
-      <c r="AI47" s="8"/>
+      <c r="AI47" s="8" t="s">
+        <v>529</v>
+      </c>
       <c r="AJ47" s="6" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="AK47" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6445,10 +6641,10 @@
         <v>69</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="str">
@@ -6464,7 +6660,7 @@
         <v>266</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
@@ -6712,7 +6908,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
@@ -6729,10 +6925,10 @@
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AJ53" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AK53" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6853,7 +7049,9 @@
       <c r="K55" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="L55" s="7"/>
+      <c r="L55" s="7" t="s">
+        <v>546</v>
+      </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
       <c r="O55" s="7"/>
@@ -6863,13 +7061,19 @@
       <c r="Q55" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
+      <c r="R55" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="S55" s="8" t="s">
+        <v>339</v>
+      </c>
       <c r="T55" s="8"/>
       <c r="U55" s="8"/>
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
-      <c r="X55" s="8"/>
+      <c r="X55" s="8" t="s">
+        <v>547</v>
+      </c>
       <c r="Y55" s="8"/>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
@@ -6882,9 +7086,11 @@
       <c r="AF55" s="8"/>
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
-      <c r="AI55" s="8"/>
+      <c r="AI55" s="8" t="s">
+        <v>530</v>
+      </c>
       <c r="AJ55" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AK55" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6942,14 +7148,14 @@
         <v>430</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
@@ -6964,10 +7170,10 @@
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AK56" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7367,7 +7573,7 @@
         <v>Cromwell P. Retuya</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>368</v>
@@ -7385,10 +7591,10 @@
         <v>16</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
@@ -7407,7 +7613,9 @@
       <c r="AF62" s="8"/>
       <c r="AG62" s="8"/>
       <c r="AH62" s="8"/>
-      <c r="AI62" s="8"/>
+      <c r="AI62" s="8" t="s">
+        <v>532</v>
+      </c>
       <c r="AJ62" s="6"/>
       <c r="AK62" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7443,7 +7651,7 @@
         <v>243</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
@@ -7482,9 +7690,11 @@
         <v>5</v>
       </c>
       <c r="AH63" s="8"/>
-      <c r="AI63" s="8"/>
+      <c r="AI63" s="8" t="s">
+        <v>534</v>
+      </c>
       <c r="AJ63" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="AK63" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7528,7 +7738,9 @@
       <c r="K64" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="L64" s="7"/>
+      <c r="L64" s="7" t="s">
+        <v>548</v>
+      </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
       <c r="O64" s="7"/>
@@ -7538,18 +7750,26 @@
       <c r="Q64" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8"/>
+      <c r="R64" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="S64" s="8" t="s">
+        <v>342</v>
+      </c>
       <c r="T64" s="8"/>
       <c r="U64" s="8"/>
       <c r="V64" s="8"/>
       <c r="W64" s="8"/>
-      <c r="X64" s="8"/>
+      <c r="X64" s="8" t="s">
+        <v>342</v>
+      </c>
       <c r="Y64" s="8"/>
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
       <c r="AB64" s="8"/>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD64" s="8" t="s">
         <v>276</v>
       </c>
@@ -7557,9 +7777,11 @@
       <c r="AF64" s="8"/>
       <c r="AG64" s="8"/>
       <c r="AH64" s="8"/>
-      <c r="AI64" s="8"/>
+      <c r="AI64" s="8" t="s">
+        <v>533</v>
+      </c>
       <c r="AJ64" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AK64" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7622,7 +7844,7 @@
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
       <c r="X65" s="8" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
@@ -7691,10 +7913,10 @@
         <v>16</v>
       </c>
       <c r="R66" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="S66" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="T66" s="8"/>
       <c r="U66" s="8"/>
@@ -7863,9 +8085,11 @@
       <c r="AF68" s="8"/>
       <c r="AG68" s="8"/>
       <c r="AH68" s="8"/>
-      <c r="AI68" s="8"/>
+      <c r="AI68" s="8" t="s">
+        <v>535</v>
+      </c>
       <c r="AJ68" s="6" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="AK68" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7971,7 +8195,7 @@
         <v>Marilou A. Villaver</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>368</v>
@@ -8069,8 +8293,9 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4E8284-6376-43C0-9AD2-1022770DDD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A192FB-C3FA-4E4F-AE7B-2268F351F74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="601">
   <si>
     <t>order</t>
   </si>
@@ -1168,9 +1168,6 @@
     <t>Canteen Coordinator</t>
   </si>
   <si>
-    <t>Health Aid Coordinator</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -1483,87 +1480,21 @@
     <t xml:space="preserve">William Arthur Ward: “The mediocre teacher tells. The good teacher explains. The superior teacher demonstrates. The great teacher inspires.”  </t>
   </si>
   <si>
-    <t>"I believe that quality education goes beyond delivering knowledge—it empowers students to think critically, grow confidently, and realize their potential. I am committed to creating a supportive and engaging learning environment where every student is encouraged to participate, develop self-confidence, and achieve excellence through meaningful learning experiences."</t>
-  </si>
-  <si>
-    <t>"I believe that learning becomes more meaningful when students are actively engaged in the process. Inspired by the idea of "learning by doing," I encourage students to explore, ask questions, collaborate with others, and apply what they learn to real-life situations. Through these experiences, students develop not only academic knowledge but also critical thinking, creativity, and problem-solving skills."</t>
-  </si>
-  <si>
-    <t>"I believe that every learner has the potential to succeed when provided with a supportive, engaging, and inclusive learning environment. As a teacher, my role is not only to deliver knowledge but also to guide, motivate, and inspire students to become lifelong learners."</t>
-  </si>
-  <si>
-    <t>"I believe that every learner can succeed when provided with a supportive, inclusive, and engaging learning environment. As a teacher, I strive to make learning meaningful, encourage active participation, and respect individual differences among students. I am committed to fostering critical thinking, lifelong learning, and positive values while helping learners reach their full potential academically and personally."</t>
-  </si>
-  <si>
-    <t>"In the end, our legacy is measured not by the achievements we accumulate, but by the minds we inspire to never stop learning."</t>
-  </si>
-  <si>
-    <t>"Teaching is not filling minds but inspiring hearts to learn"</t>
-  </si>
-  <si>
-    <t>"I believe teaching is about helping students learn with confidence and curiosity. In my AP classes, I see to it that I teach with a heart and give strong support to my students so that they can succeed. My goal is to prepare students not only for exams but also for life beyond school."</t>
-  </si>
-  <si>
-    <t>"Effective teaching is guided by beliefs that students are capable ,while learning is active and social that teachers serve as facilitators who creat safe ,engaging and inclusive learning environments. "</t>
-  </si>
-  <si>
-    <t>"I believe that students learn best when they are actively involved in the learning process and can connect lessons to their own experiences. As a teacher, I am aiming to create a classroom where learners feel safe to ask questions, share ideas, and learn from one another. Guided by the principles of constructivism, I see my role as a facilitator who encourages exploration, critical thinking, and collaboration. By making learning meaningful and relevant, I hope to help students develop confidence, take ownership of their learning, and become lifelong learners."</t>
-  </si>
-  <si>
-    <t>"I believe mathematics is not just about numbers and formulas, but about developing logical reasoning, problem-solving skills, and confidence in tackling challenges. As a Grade 9 mathematics teacher, my role is to guide students in seeing math as a language that explains patterns in the world around them. I strive to create a classroom environment where curiosity is encouraged, mistakes are embraced as part of learning, and every student feels capable of growth."</t>
-  </si>
-  <si>
-    <t>"Everything is empty in the mind of the students and the educators are the one who let them experience that makes their mind blowing."</t>
-  </si>
-  <si>
     <t>Teaching them to poke the universe with a stick to see what it does, but safely.</t>
   </si>
   <si>
-    <t>"Every problem has a solution."</t>
-  </si>
-  <si>
-    <t>"I believe every learner can succeed when given support, respect, and meaningful learning experiences."</t>
-  </si>
-  <si>
-    <t>"I believe every student can learn and succeed in a positive, inclusive, and supportive environment. My role is to inspire curiosity, develop critical thinking, and help learners become confident, responsible, and lifelong learners."</t>
-  </si>
-  <si>
-    <t>Teaching is the facilitation of "Meaningful, relevant, and inclusive experiences that empower learners to acquire knowledge, develop skills, build strong character, and become responsible, productive, and patriotic citizens in our country."</t>
-  </si>
-  <si>
-    <t>"Everything is a process, don't skip, don't jump to the next level without the experience needed."</t>
-  </si>
-  <si>
-    <t>10th Grade - Grade Leader</t>
-  </si>
-  <si>
-    <t>9th Grade - Grade Leader</t>
-  </si>
-  <si>
-    <t>8th Grade - Grade Leader</t>
-  </si>
-  <si>
-    <t>7th Grade - Grade Leader</t>
-  </si>
-  <si>
     <t>Hairdressing NCII</t>
   </si>
   <si>
     <t>glendale.orocay@deped.gov.ph</t>
   </si>
   <si>
-    <t>"I believe every learner can succeed with proper guidance, encouragement, and opportunities to grow. As a Hairdressing Teacher, I help students build skills, confidence, and creativity for lifelong success."</t>
-  </si>
-  <si>
     <t>Guidance Designate for Junior High School</t>
   </si>
   <si>
     <t>carolyn.delosreyes002@deped.gov.ph</t>
   </si>
   <si>
-    <t>"My teaching philosophy us that every learner is capable of growth when given support, respect, and meaningful learning experiences. I believe teaching should be student-centered, where learners actively construct understanding through engagement, critical thinking, and real-life connections. My role is to guide, motivate, and create an inclusive environment where students feel safe to ask questions, make mistakes, and improve continuously."</t>
-  </si>
-  <si>
     <t>Caballero</t>
   </si>
   <si>
@@ -1660,18 +1591,9 @@
     <t>Homeroom Guidance Program 7</t>
   </si>
   <si>
-    <t>"Behind every lesson is a teacher who hopes, sacrifices, and believes in every learner. I teach not only to educate minds but also to touch hearts and help shape a better future."</t>
-  </si>
-  <si>
     <t>hector.cabanca001@deped.gov.ph</t>
   </si>
   <si>
-    <t>“Great teachers don’t just teach subjects—they shape lives.”</t>
-  </si>
-  <si>
-    <t>"Teaching is touching hearts, opening minds, and building futures."</t>
-  </si>
-  <si>
     <t>SMEA Coordinator</t>
   </si>
   <si>
@@ -1706,13 +1628,223 @@
   </si>
   <si>
     <t>marilou.cabriana001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Girl Scout of the Philippines (GSP) Adviser</t>
+  </si>
+  <si>
+    <t>Teach and inspire with compassion, meaningful experiences, and values-centered.</t>
+  </si>
+  <si>
+    <t>Behind every lesson is a teacher who hopes, sacrifices, and believes in every learner. I teach not only to educate minds but also to touch hearts and help shape a better future.</t>
+  </si>
+  <si>
+    <t>I believe that every learner has the potential to succeed when provided with a supportive, engaging, and inclusive learning environment. As a teacher, my role is not only to deliver knowledge but also to guide, motivate, and inspire students to become lifelong learners.</t>
+  </si>
+  <si>
+    <t>I believe that every learner can succeed when provided with a supportive, inclusive, and engaging learning environment. As a teacher, I strive to make learning meaningful, encourage active participation, and respect individual differences among students. I am committed to fostering critical thinking, lifelong learning, and positive values while helping learners reach their full potential academically and personally.</t>
+  </si>
+  <si>
+    <t>In the end, our legacy is measured not by the achievements we accumulate, but by the minds we inspire to never stop learning.</t>
+  </si>
+  <si>
+    <t>Teaching is not filling minds but inspiring hearts to learn</t>
+  </si>
+  <si>
+    <t>I believe teaching is about helping students learn with confidence and curiosity. In my AP classes, I see to it that I teach with a heart and give strong support to my students so that they can succeed. My goal is to prepare students not only for exams but also for life beyond school.</t>
+  </si>
+  <si>
+    <t>Great teachers don’t just teach subjects—they shape lives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective teaching is guided by beliefs that students are capable ,while learning is active and social that teachers serve as facilitators who creat safe ,engaging and inclusive learning environments. </t>
+  </si>
+  <si>
+    <t>I believe that students learn best when they are actively involved in the learning process and can connect lessons to their own experiences. As a teacher, I am aiming to create a classroom where learners feel safe to ask questions, share ideas, and learn from one another. Guided by the principles of constructivism, I see my role as a facilitator who encourages exploration, critical thinking, and collaboration. By making learning meaningful and relevant, I hope to help students develop confidence, take ownership of their learning, and become lifelong learners.</t>
+  </si>
+  <si>
+    <t>I believe mathematics is not just about numbers and formulas, but about developing logical reasoning, problem-solving skills, and confidence in tackling challenges. As a Grade 9 mathematics teacher, my role is to guide students in seeing math as a language that explains patterns in the world around them. I strive to create a classroom environment where curiosity is encouraged, mistakes are embraced as part of learning, and every student feels capable of growth.</t>
+  </si>
+  <si>
+    <t>My teaching philosophy us that every learner is capable of growth when given support, respect, and meaningful learning experiences. I believe teaching should be student-centered, where learners actively construct understanding through engagement, critical thinking, and real-life connections. My role is to guide, motivate, and create an inclusive environment where students feel safe to ask questions, make mistakes, and improve continuously.</t>
+  </si>
+  <si>
+    <t>I believe that learning becomes more meaningful when students are actively engaged in the process. Inspired by the idea of "learning by doing," I encourage students to explore, ask questions, collaborate with others, and apply what they learn to real-life situations. Through these experiences, students develop not only academic knowledge but also critical thinking, creativity, and problem-solving skills.</t>
+  </si>
+  <si>
+    <t>Teaching is touching hearts, opening minds, and building futures.</t>
+  </si>
+  <si>
+    <t>I believe that quality education goes beyond delivering knowledge—it empowers students to think critically, grow confidently, and realize their potential. I am committed to creating a supportive and engaging learning environment where every student is encouraged to participate, develop self-confidence, and achieve excellence through meaningful learning experiences.</t>
+  </si>
+  <si>
+    <t>Everything is a process, don't skip, don't jump to the next level without the experience needed.</t>
+  </si>
+  <si>
+    <t>Everything is empty in the mind of the students and the educators are the one who let them experience that makes their mind blowing.</t>
+  </si>
+  <si>
+    <t>Every problem has a solution.</t>
+  </si>
+  <si>
+    <t>I believe every learner can succeed with proper guidance, encouragement, and opportunities to grow. As a Hairdressing Teacher, I help students build skills, confidence, and creativity for lifelong success.</t>
+  </si>
+  <si>
+    <t>I believe every learner can succeed when given support, respect, and meaningful learning experiences.</t>
+  </si>
+  <si>
+    <t>I believe every student can learn and succeed in a positive, inclusive, and supportive environment. My role is to inspire curiosity, develop critical thinking, and help learners become confident, responsible, and lifelong learners.</t>
+  </si>
+  <si>
+    <t>Teaching is the facilitation of "Meaningful, relevant, and inclusive experiences that empower learners to acquire knowledge, develop skills, build strong character, and become responsible, productive, and patriotic citizens in our country.</t>
+  </si>
+  <si>
+    <t>genesa.goc-ong@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Feeding Program Coordinator</t>
+  </si>
+  <si>
+    <t>bellaarquine.samontanez@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Teaching is not a job, it is a calling, being a teacher is a gift and gratitude as both gift and gratefulness.</t>
+  </si>
+  <si>
+    <t>I believe that learning shouldn't feel like a rigid, one-way lecture. It should feel like a meaningful conversation between peers. At the end of the day, I view myself not as an unapproachable expert, but as a helpful, knowledgeable peer who is here to tackle challenges right alongside you.</t>
+  </si>
+  <si>
+    <t>joan.cabalda@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>fernando.laspinas@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Life</t>
+  </si>
+  <si>
+    <t>joyce.racaza001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Registrar (Designate)</t>
+  </si>
+  <si>
+    <t>Araling Panlipunan 7</t>
+  </si>
+  <si>
+    <t>Technology and Livelihood Education (TLE) 7</t>
+  </si>
+  <si>
+    <t>Mathematics 7</t>
+  </si>
+  <si>
+    <t>Strive to use a variety of teaching methods, including collaborative activities, discussions, and real-world applications, to address diverse learning styles and needs.</t>
+  </si>
+  <si>
+    <t>jhea.quiling@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Contemporary Litrature, Life and Career Skill</t>
+  </si>
+  <si>
+    <t>Effective Communication</t>
+  </si>
+  <si>
+    <t>English 8</t>
+  </si>
+  <si>
+    <t>I follow the constructivist approach to teaching and learning, as I believe that my learners are active thinkers.</t>
+  </si>
+  <si>
+    <t>loner.andrade@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Assistant School Health Aide Coordinator</t>
+  </si>
+  <si>
+    <t>Assistant GSP Coordinator</t>
+  </si>
+  <si>
+    <t>marissa.abalo@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>I believe that education is a powerful tool that transforms lives and empowers individuals to reach their fullest potential. As a teacher, I am committed to fostering a learning environment where students feel valued, respected, and motivated to learn.</t>
+  </si>
+  <si>
+    <t>I believe that every student can learn when given a supportive, inclusive, and engaging environment that respects their unique strengths and needs. My role as a teacher is to inspire curiosity, encourage critical thinking, and help learners build confidence so they can reach their full potential.</t>
+  </si>
+  <si>
+    <t>jasmin.gerodias@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>English 7</t>
+  </si>
+  <si>
+    <t>I believe learning is an active, lifelong process where students construct meaning by connecting new ideas to their experiences, not just passively receiving information.</t>
+  </si>
+  <si>
+    <t>Create an environment that molds learners  and empowers them to construct knowledge , think critically  and be the best  version of themselves    with  compassionate heart someday.</t>
+  </si>
+  <si>
+    <t>nerisa.lim001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>I teach Values Education so that a student learns to live a life that is examined (Socrates), ordered toward love (Augustine), and free.</t>
+  </si>
+  <si>
+    <t>General Science</t>
+  </si>
+  <si>
+    <t>Biology 1</t>
+  </si>
+  <si>
+    <t>Scicence 8</t>
+  </si>
+  <si>
+    <t>Teaching is not merely passing knowledge—it is the continuation of your own learning. Love the path, and you will love walking it alongside others.</t>
+  </si>
+  <si>
+    <t>I believe that teaching MAPEH should develop the learner as a whole—mind, body, and creativity. Learning is best when students are actively involved through music, arts, physical activities, and health-related experiences. As a teacher, I aim to provide engaging, learner-centered activities that build skills, confidence, discipline, and healthy habits. My goal is to help students appreciate creativity, value physical fitness, and practice a healthy lifestyle in their daily lives.</t>
+  </si>
+  <si>
+    <t>Araling Panlipunan 9 &amp; 10</t>
+  </si>
+  <si>
+    <t>School JHS Filipino Reading Coordinator</t>
+  </si>
+  <si>
+    <t>Filipino 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>marilou.villaver001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The PASSION in teaching and learning has no expiration. </t>
+  </si>
+  <si>
+    <t>PHIL-IRI Coordinator (English)</t>
+  </si>
+  <si>
+    <t>ARAL Progam Coordinator</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (Math, JHS)</t>
+  </si>
+  <si>
+    <t>Subject Area Coordinator (Filipino, SHS)</t>
+  </si>
+  <si>
+    <t>School Paper Adviser (Filipino, SHS)</t>
+  </si>
+  <si>
+    <t>Fillipino 11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1750,6 +1882,12 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1773,10 +1911,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1807,8 +1946,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="41">
@@ -2512,6 +2655,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonnelRosterTable" displayName="PersonnelRosterTable" ref="A1:AL71" headerRowDxfId="40" dataDxfId="39" totalsRowDxfId="38">
+  <autoFilter ref="A1:AL71" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AL71">
     <sortCondition ref="B2:B71"/>
   </sortState>
@@ -2771,10 +2915,10 @@
         <v>323</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>382</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>383</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>324</v>
@@ -2798,37 +2942,37 @@
         <v>4</v>
       </c>
       <c r="S1" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="X1" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>359</v>
@@ -2846,10 +2990,10 @@
         <v>362</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AK1" s="5" t="s">
         <v>5</v>
@@ -2884,12 +3028,12 @@
         <v>10</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>499</v>
+        <v>326</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -2911,7 +3055,7 @@
       <c r="V2" s="8"/>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
@@ -2930,10 +3074,10 @@
       </c>
       <c r="AH2" s="8"/>
       <c r="AI2" s="8" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="AJ2" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f t="shared" ref="AK2:AK33" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
@@ -2943,7 +3087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" ht="134.4">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2975,10 +3119,14 @@
         <v>352</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+        <v>383</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>575</v>
+      </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="8" t="s">
@@ -2998,18 +3146,18 @@
       <c r="V3" s="8"/>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y3" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="Z3" s="8" t="s">
         <v>424</v>
-      </c>
-      <c r="Z3" s="8" t="s">
-        <v>425</v>
       </c>
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
       <c r="AC3" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>276</v>
@@ -3018,8 +3166,12 @@
       <c r="AF3" s="8"/>
       <c r="AG3" s="8"/>
       <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="6"/>
+      <c r="AI3" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
+        <v>577</v>
+      </c>
       <c r="AK3" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marissa-abalo.jpg</v>
@@ -3054,12 +3206,12 @@
         <v>240</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -3081,7 +3233,7 @@
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
@@ -3091,17 +3243,17 @@
         <v>16</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
       <c r="AG4" s="8"/>
       <c r="AH4" s="8"/>
       <c r="AI4" s="8" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="AJ4" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AK4" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3143,13 +3295,13 @@
         <v>354</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L5" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>427</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>428</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -3170,13 +3322,13 @@
       <c r="V5" s="8"/>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
@@ -3191,10 +3343,10 @@
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="AJ5" s="6" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="AK5" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3236,7 +3388,7 @@
         <v>355</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -3249,20 +3401,20 @@
         <v>14</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
@@ -3277,7 +3429,9 @@
       <c r="AF6" s="8"/>
       <c r="AG6" s="8"/>
       <c r="AH6" s="8"/>
-      <c r="AI6" s="8"/>
+      <c r="AI6" s="8" t="s">
+        <v>573</v>
+      </c>
       <c r="AJ6" s="6"/>
       <c r="AK6" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3319,13 +3473,13 @@
         <v>353</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L7" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>432</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>433</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -3336,17 +3490,17 @@
         <v>14</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
@@ -3364,7 +3518,7 @@
       <c r="AH7" s="8"/>
       <c r="AI7" s="8"/>
       <c r="AJ7" s="6" t="s">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="AK7" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3413,7 +3567,7 @@
         <v>7</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
@@ -3434,7 +3588,7 @@
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="8" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="AJ8" s="6"/>
       <c r="AK8" s="7" t="str">
@@ -3471,7 +3625,7 @@
         <v>268</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -3486,10 +3640,10 @@
         <v>370</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
@@ -3544,12 +3698,12 @@
         <v>243</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -3561,17 +3715,17 @@
         <v>16</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -3597,7 +3751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" ht="67.2">
       <c r="A11" s="7">
         <v>9</v>
       </c>
@@ -3629,13 +3783,13 @@
         <v>354</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L11" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>436</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>437</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -3646,17 +3800,17 @@
         <v>14</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
@@ -3673,9 +3827,11 @@
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="AJ11" s="6"/>
+        <v>495</v>
+      </c>
+      <c r="AJ11" s="6" t="s">
+        <v>584</v>
+      </c>
       <c r="AK11" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/jake-barcenas.jpg</v>
@@ -3716,10 +3872,10 @@
         <v>352</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -3741,7 +3897,7 @@
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
@@ -3758,10 +3914,10 @@
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="8" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="AJ12" s="6" t="s">
-        <v>485</v>
+        <v>535</v>
       </c>
       <c r="AK12" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3803,16 +3959,16 @@
         <v>356</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="8" t="s">
@@ -3832,16 +3988,16 @@
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y13" s="8" t="s">
         <v>442</v>
-      </c>
-      <c r="Y13" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AD13" s="8" t="s">
         <v>276</v>
@@ -3851,10 +4007,10 @@
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="AJ13" s="6" t="s">
-        <v>486</v>
+        <v>536</v>
       </c>
       <c r="AK13" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3864,7 +4020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="33.6">
+    <row r="14" spans="1:38" ht="218.4">
       <c r="A14" s="7">
         <v>12</v>
       </c>
@@ -3890,12 +4046,12 @@
         <v>15</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="7" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -3917,7 +4073,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
@@ -3927,16 +4083,18 @@
         <v>16</v>
       </c>
       <c r="AD14" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE14" s="8"/>
       <c r="AF14" s="8"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="AJ14" s="6"/>
+        <v>498</v>
+      </c>
+      <c r="AJ14" s="6" t="s">
+        <v>589</v>
+      </c>
       <c r="AK14" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/mary-josephine-bawiga.jpg</v>
@@ -3977,10 +4135,10 @@
         <v>351</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -4002,16 +4160,16 @@
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AD15" s="8" t="s">
         <v>276</v>
@@ -4022,7 +4180,7 @@
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="6" t="s">
-        <v>487</v>
+        <v>537</v>
       </c>
       <c r="AK15" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4063,13 +4221,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="8" t="s">
@@ -4089,10 +4247,10 @@
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="Y16" s="8" t="s">
         <v>452</v>
-      </c>
-      <c r="Y16" s="8" t="s">
-        <v>453</v>
       </c>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
@@ -4111,7 +4269,7 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AK16" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4151,10 +4309,10 @@
         <v>351</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -4176,16 +4334,16 @@
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y17" s="8" t="s">
         <v>455</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>456</v>
       </c>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AD17" s="8" t="s">
         <v>276</v>
@@ -4249,13 +4407,13 @@
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
@@ -4267,7 +4425,7 @@
       <c r="AH18" s="8"/>
       <c r="AI18" s="8"/>
       <c r="AJ18" s="6" t="s">
-        <v>488</v>
+        <v>538</v>
       </c>
       <c r="AK18" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4277,7 +4435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:38" ht="33.6">
+    <row r="19" spans="1:38" ht="134.4">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -4318,7 +4476,7 @@
         <v>7</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S19" s="8" t="s">
         <v>7</v>
@@ -4338,8 +4496,12 @@
       <c r="AF19" s="8"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
-      <c r="AI19" s="8"/>
-      <c r="AJ19" s="6"/>
+      <c r="AI19" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="AJ19" s="6" t="s">
+        <v>558</v>
+      </c>
       <c r="AK19" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/joan-cabalda.jpg</v>
@@ -4374,7 +4536,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>500</v>
+        <v>327</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -4412,10 +4574,10 @@
       </c>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="AJ20" s="6" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AK20" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4457,7 +4619,7 @@
         <v>353</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
@@ -4534,10 +4696,10 @@
         <v>354</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -4573,10 +4735,10 @@
       <c r="AF22" s="8"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
-      <c r="AI22" s="8"/>
-      <c r="AJ22" s="6" t="s">
-        <v>556</v>
-      </c>
+      <c r="AI22" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="AJ22" s="6"/>
       <c r="AK22" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-cabriana.jpg</v>
@@ -4590,10 +4752,10 @@
         <v>68</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="str">
@@ -4609,7 +4771,7 @@
         <v>266</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -4624,10 +4786,10 @@
         <v>370</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
@@ -4682,7 +4844,7 @@
         <v>261</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
@@ -4697,10 +4859,10 @@
         <v>7</v>
       </c>
       <c r="R24" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
@@ -4729,7 +4891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:38">
+    <row r="25" spans="1:38" ht="33.6">
       <c r="A25" s="7">
         <v>18</v>
       </c>
@@ -4755,9 +4917,11 @@
         <v>248</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="J25" s="6"/>
+        <v>598</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>599</v>
+      </c>
       <c r="K25" s="6"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
@@ -4779,7 +4943,9 @@
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
+      <c r="X25" s="8" t="s">
+        <v>600</v>
+      </c>
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
@@ -4793,7 +4959,7 @@
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="AJ25" s="6"/>
       <c r="AK25" s="7" t="str">
@@ -4830,7 +4996,7 @@
         <v>15</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -4861,17 +5027,17 @@
       <c r="AB26" s="8"/>
       <c r="AC26" s="8"/>
       <c r="AD26" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE26" s="8"/>
       <c r="AF26" s="8"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="AJ26" s="6" t="s">
-        <v>489</v>
+        <v>540</v>
       </c>
       <c r="AK26" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4913,7 +5079,7 @@
         <v>351</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
@@ -4950,7 +5116,7 @@
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="6" t="s">
-        <v>490</v>
+        <v>541</v>
       </c>
       <c r="AK27" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4960,7 +5126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:38" ht="235.2">
+    <row r="28" spans="1:38" ht="218.4">
       <c r="A28" s="7">
         <v>26</v>
       </c>
@@ -4990,7 +5156,7 @@
         <v>353</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
@@ -5027,7 +5193,7 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="6" t="s">
-        <v>491</v>
+        <v>542</v>
       </c>
       <c r="AK28" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5078,7 +5244,7 @@
         <v>7</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S29" s="8" t="s">
         <v>7</v>
@@ -5142,7 +5308,7 @@
         <v>354</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
@@ -5178,7 +5344,7 @@
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="8" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="AJ30" s="6"/>
       <c r="AK30" s="7" t="str">
@@ -5215,7 +5381,7 @@
         <v>268</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -5230,10 +5396,10 @@
         <v>370</v>
       </c>
       <c r="R31" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T31" s="8"/>
       <c r="U31" s="8"/>
@@ -5296,7 +5462,7 @@
         <v>355</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
@@ -5367,7 +5533,7 @@
         <v>15</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -5386,29 +5552,33 @@
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
-      <c r="X33" s="8"/>
+      <c r="X33" s="8" t="s">
+        <v>590</v>
+      </c>
       <c r="Y33" s="8"/>
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD33" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE33" s="8"/>
       <c r="AF33" s="8"/>
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="AJ33" s="6" t="s">
-        <v>508</v>
+        <v>543</v>
       </c>
       <c r="AK33" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5444,7 +5614,7 @@
         <v>15</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
@@ -5477,17 +5647,17 @@
         <v>16</v>
       </c>
       <c r="AD34" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE34" s="8"/>
       <c r="AF34" s="8"/>
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="8" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="AJ34" s="6" t="s">
-        <v>483</v>
+        <v>544</v>
       </c>
       <c r="AK34" s="7" t="str">
         <f t="shared" ref="AK34:AK70" si="5">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C34&amp;" "&amp;B34)," ","-"))&amp;".jpg"</f>
@@ -5538,17 +5708,17 @@
         <v>14</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
@@ -5574,7 +5744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:38">
+    <row r="36" spans="1:38" ht="84">
       <c r="A36" s="7">
         <v>32</v>
       </c>
@@ -5600,11 +5770,13 @@
         <v>243</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>501</v>
+        <v>328</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
-      <c r="L36" s="7"/>
+      <c r="L36" s="7" t="s">
+        <v>281</v>
+      </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
       <c r="O36" s="7"/>
@@ -5624,9 +5796,15 @@
       <c r="U36" s="8"/>
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="8"/>
-      <c r="Z36" s="8"/>
+      <c r="X36" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="Y36" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="Z36" s="8" t="s">
+        <v>587</v>
+      </c>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
@@ -5640,9 +5818,11 @@
       </c>
       <c r="AH36" s="8"/>
       <c r="AI36" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="AJ36" s="6"/>
+        <v>503</v>
+      </c>
+      <c r="AJ36" s="6" t="s">
+        <v>588</v>
+      </c>
       <c r="AK36" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/metchie-gay-gastanes.jpg</v>
@@ -5651,7 +5831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:38">
+    <row r="37" spans="1:38" ht="134.4">
       <c r="A37" s="7">
         <v>33</v>
       </c>
@@ -5674,7 +5854,7 @@
         <v>Jasmin B. Gerodias</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>376</v>
@@ -5692,16 +5872,18 @@
         <v>16</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
-      <c r="X37" s="8"/>
+      <c r="X37" s="8" t="s">
+        <v>565</v>
+      </c>
       <c r="Y37" s="8"/>
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
@@ -5714,8 +5896,12 @@
       <c r="AF37" s="8"/>
       <c r="AG37" s="8"/>
       <c r="AH37" s="8"/>
-      <c r="AI37" s="8"/>
-      <c r="AJ37" s="6"/>
+      <c r="AI37" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="AJ37" s="6" t="s">
+        <v>578</v>
+      </c>
       <c r="AK37" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/jasmin-gerodias.jpg</v>
@@ -5756,10 +5942,14 @@
         <v>352</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
+        <v>394</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>596</v>
+      </c>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
       <c r="P38" s="8" t="s">
@@ -5771,7 +5961,9 @@
       <c r="R38" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="S38" s="8"/>
+      <c r="S38" s="8" t="s">
+        <v>333</v>
+      </c>
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
       <c r="V38" s="8"/>
@@ -5790,10 +5982,10 @@
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="8" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="AJ38" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AK38" s="7" t="str">
         <f t="shared" si="5"/>
@@ -5803,7 +5995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:38">
+    <row r="39" spans="1:38" ht="50.4">
       <c r="A39" s="7">
         <v>35</v>
       </c>
@@ -5826,7 +6018,7 @@
         <v>Genesa D. Goc-ong</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>276</v>
@@ -5835,9 +6027,11 @@
         <v>352</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="L39" s="7"/>
+        <v>395</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>531</v>
+      </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
@@ -5850,17 +6044,23 @@
       <c r="R39" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="S39" s="8"/>
+      <c r="S39" s="8" t="s">
+        <v>341</v>
+      </c>
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
       <c r="V39" s="8"/>
       <c r="W39" s="8"/>
-      <c r="X39" s="8"/>
+      <c r="X39" s="8" t="s">
+        <v>341</v>
+      </c>
       <c r="Y39" s="8"/>
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD39" s="8" t="s">
         <v>276</v>
       </c>
@@ -5868,8 +6068,12 @@
       <c r="AF39" s="8"/>
       <c r="AG39" s="8"/>
       <c r="AH39" s="8"/>
-      <c r="AI39" s="8"/>
-      <c r="AJ39" s="6"/>
+      <c r="AI39" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="AJ39" s="6" t="s">
+        <v>532</v>
+      </c>
       <c r="AK39" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/genesa-goc-ong.jpg</v>
@@ -5904,7 +6108,7 @@
         <v>240</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
@@ -5933,7 +6137,7 @@
       <c r="AB40" s="8"/>
       <c r="AC40" s="8"/>
       <c r="AD40" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE40" s="8"/>
       <c r="AF40" s="8"/>
@@ -5981,7 +6185,7 @@
         <v>351</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
@@ -6003,12 +6207,16 @@
       <c r="U41" s="8"/>
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
-      <c r="X41" s="8"/>
+      <c r="X41" s="8" t="s">
+        <v>580</v>
+      </c>
       <c r="Y41" s="8"/>
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD41" s="8" t="s">
         <v>276</v>
       </c>
@@ -6017,7 +6225,7 @@
       <c r="AG41" s="8"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="AJ41" s="6"/>
       <c r="AK41" s="7" t="str">
@@ -6060,7 +6268,7 @@
         <v>354</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
@@ -6096,10 +6304,10 @@
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="8" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="AJ42" s="6" t="s">
-        <v>482</v>
+        <v>546</v>
       </c>
       <c r="AK42" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6132,10 +6340,10 @@
         <v>Fernando H. Laspiñas</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>368</v>
+        <v>295</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
@@ -6149,9 +6357,15 @@
       <c r="Q43" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
+      <c r="R43" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="S43" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="T43" s="8" t="s">
+        <v>561</v>
+      </c>
       <c r="U43" s="8"/>
       <c r="V43" s="8"/>
       <c r="W43" s="8"/>
@@ -6162,13 +6376,15 @@
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
       <c r="AD43" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE43" s="8"/>
       <c r="AF43" s="8"/>
       <c r="AG43" s="8"/>
       <c r="AH43" s="8"/>
-      <c r="AI43" s="8"/>
+      <c r="AI43" s="8" t="s">
+        <v>560</v>
+      </c>
       <c r="AJ43" s="6"/>
       <c r="AK43" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6178,7 +6394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:38">
+    <row r="44" spans="1:38" ht="84">
       <c r="A44" s="7">
         <v>40</v>
       </c>
@@ -6204,7 +6420,7 @@
         <v>240</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
@@ -6235,14 +6451,18 @@
       <c r="AB44" s="8"/>
       <c r="AC44" s="8"/>
       <c r="AD44" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE44" s="8"/>
       <c r="AF44" s="8"/>
       <c r="AG44" s="8"/>
       <c r="AH44" s="8"/>
-      <c r="AI44" s="8"/>
-      <c r="AJ44" s="6"/>
+      <c r="AI44" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="AJ44" s="6" t="s">
+        <v>582</v>
+      </c>
       <c r="AK44" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/nerisa-lim.jpg</v>
@@ -6275,7 +6495,7 @@
         <v>15</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
@@ -6306,7 +6526,7 @@
       <c r="AB45" s="8"/>
       <c r="AC45" s="8"/>
       <c r="AD45" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE45" s="8"/>
       <c r="AF45" s="8"/>
@@ -6314,7 +6534,7 @@
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
       <c r="AJ45" s="6" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="AK45" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6350,15 +6570,15 @@
         <v>269</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="L46" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -6394,7 +6614,7 @@
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="8" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="AJ46" s="6"/>
       <c r="AK46" s="7" t="str">
@@ -6450,17 +6670,17 @@
         <v>14</v>
       </c>
       <c r="R47" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
@@ -6475,10 +6695,10 @@
       <c r="AG47" s="8"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="8" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="AJ47" s="6" t="s">
-        <v>498</v>
+        <v>547</v>
       </c>
       <c r="AK47" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6514,7 +6734,7 @@
         <v>15</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
@@ -6543,7 +6763,7 @@
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE48" s="8"/>
       <c r="AF48" s="8"/>
@@ -6591,7 +6811,7 @@
         <v>353</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
@@ -6641,10 +6861,10 @@
         <v>69</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="str">
@@ -6660,7 +6880,7 @@
         <v>266</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
@@ -6675,10 +6895,10 @@
         <v>370</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S50" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T50" s="8"/>
       <c r="U50" s="8"/>
@@ -6733,7 +6953,7 @@
         <v>12</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
@@ -6760,7 +6980,7 @@
       <c r="AB51" s="8"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE51" s="8"/>
       <c r="AF51" s="8"/>
@@ -6808,7 +7028,7 @@
         <v>351</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
@@ -6837,7 +7057,7 @@
       <c r="AB52" s="8"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8"/>
@@ -6885,7 +7105,7 @@
         <v>352</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
@@ -6908,7 +7128,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
@@ -6925,10 +7145,10 @@
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AJ53" s="6" t="s">
-        <v>492</v>
+        <v>548</v>
       </c>
       <c r="AK53" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6970,7 +7190,7 @@
         <v>351</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -7047,10 +7267,10 @@
         <v>354</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -7072,7 +7292,7 @@
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
       <c r="X55" s="8" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="Y55" s="8"/>
       <c r="Z55" s="8"/>
@@ -7087,10 +7307,10 @@
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="8" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="AJ55" s="6" t="s">
-        <v>494</v>
+        <v>549</v>
       </c>
       <c r="AK55" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7132,7 +7352,7 @@
         <v>356</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
@@ -7145,17 +7365,17 @@
         <v>14</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8" t="s">
-        <v>503</v>
+        <v>482</v>
       </c>
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
@@ -7170,10 +7390,10 @@
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="AK56" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7215,7 +7435,7 @@
         <v>355</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
@@ -7286,7 +7506,7 @@
         <v>12</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -7301,7 +7521,7 @@
         <v>16</v>
       </c>
       <c r="R58" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="S58" s="8"/>
       <c r="T58" s="8"/>
@@ -7315,7 +7535,7 @@
       <c r="AB58" s="8"/>
       <c r="AC58" s="8"/>
       <c r="AD58" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE58" s="8"/>
       <c r="AF58" s="8"/>
@@ -7363,7 +7583,7 @@
         <v>352</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
@@ -7404,7 +7624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:38">
+    <row r="60" spans="1:38" ht="50.4">
       <c r="A60" s="7">
         <v>55</v>
       </c>
@@ -7430,7 +7650,7 @@
         <v>15</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
@@ -7454,21 +7674,33 @@
       <c r="U60" s="8"/>
       <c r="V60" s="8"/>
       <c r="W60" s="8"/>
-      <c r="X60" s="8"/>
-      <c r="Y60" s="8"/>
-      <c r="Z60" s="8"/>
+      <c r="X60" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="Y60" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="Z60" s="8" t="s">
+        <v>571</v>
+      </c>
       <c r="AA60" s="8"/>
       <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8" t="s">
+        <v>467</v>
+      </c>
       <c r="AD60" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE60" s="8"/>
       <c r="AF60" s="8"/>
       <c r="AG60" s="8"/>
       <c r="AH60" s="8"/>
-      <c r="AI60" s="8"/>
-      <c r="AJ60" s="6"/>
+      <c r="AI60" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="AJ60" s="6" t="s">
+        <v>572</v>
+      </c>
       <c r="AK60" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/jhea-quiling.jpg</v>
@@ -7477,7 +7709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:38">
+    <row r="61" spans="1:38" ht="84">
       <c r="A61" s="7">
         <v>56</v>
       </c>
@@ -7500,10 +7732,10 @@
         <v>Joyce C. Racaza</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>368</v>
+        <v>563</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
@@ -7527,21 +7759,29 @@
       <c r="U61" s="8"/>
       <c r="V61" s="8"/>
       <c r="W61" s="8"/>
-      <c r="X61" s="8"/>
+      <c r="X61" s="8" t="s">
+        <v>564</v>
+      </c>
       <c r="Y61" s="8"/>
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
       <c r="AB61" s="8"/>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD61" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE61" s="8"/>
       <c r="AF61" s="8"/>
       <c r="AG61" s="8"/>
       <c r="AH61" s="8"/>
-      <c r="AI61" s="8"/>
-      <c r="AJ61" s="6"/>
+      <c r="AI61" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="AJ61" s="6" t="s">
+        <v>567</v>
+      </c>
       <c r="AK61" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/joyce-racaza.jpg</v>
@@ -7550,7 +7790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:38">
+    <row r="62" spans="1:38" ht="84">
       <c r="A62" s="7">
         <v>57</v>
       </c>
@@ -7576,7 +7816,7 @@
         <v>15</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
@@ -7591,32 +7831,38 @@
         <v>16</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
       <c r="V62" s="8"/>
       <c r="W62" s="8"/>
-      <c r="X62" s="8"/>
+      <c r="X62" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="Y62" s="8"/>
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
       <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD62" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE62" s="8"/>
       <c r="AF62" s="8"/>
       <c r="AG62" s="8"/>
       <c r="AH62" s="8"/>
       <c r="AI62" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="AJ62" s="6"/>
+        <v>509</v>
+      </c>
+      <c r="AJ62" s="6" t="s">
+        <v>581</v>
+      </c>
       <c r="AK62" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/cromwell-retuya.jpg</v>
@@ -7651,11 +7897,13 @@
         <v>243</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>502</v>
+        <v>329</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
-      <c r="L63" s="7"/>
+      <c r="L63" s="7" t="s">
+        <v>597</v>
+      </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
@@ -7675,12 +7923,16 @@
       <c r="U63" s="8"/>
       <c r="V63" s="8"/>
       <c r="W63" s="8"/>
-      <c r="X63" s="8"/>
+      <c r="X63" s="8" t="s">
+        <v>566</v>
+      </c>
       <c r="Y63" s="8"/>
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
       <c r="AB63" s="8"/>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD63" s="8" t="s">
         <v>366</v>
       </c>
@@ -7691,10 +7943,10 @@
       </c>
       <c r="AH63" s="8"/>
       <c r="AI63" s="8" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="AJ63" s="6" t="s">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="AK63" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7736,10 +7988,10 @@
         <v>353</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
@@ -7778,10 +8030,10 @@
       <c r="AG64" s="8"/>
       <c r="AH64" s="8"/>
       <c r="AI64" s="8" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="AJ64" s="6" t="s">
-        <v>496</v>
+        <v>552</v>
       </c>
       <c r="AK64" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7817,7 +8069,7 @@
         <v>243</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
@@ -7838,13 +8090,13 @@
         <v>338</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U65" s="8"/>
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
       <c r="X65" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
@@ -7868,7 +8120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:38" ht="33.6">
+    <row r="66" spans="1:38" ht="50.4">
       <c r="A66" s="7">
         <v>61</v>
       </c>
@@ -7900,9 +8152,11 @@
         <v>353</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="L66" s="7"/>
+        <v>405</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>555</v>
+      </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
@@ -7913,10 +8167,10 @@
         <v>16</v>
       </c>
       <c r="R66" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S66" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T66" s="8"/>
       <c r="U66" s="8"/>
@@ -7927,7 +8181,9 @@
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
       <c r="AB66" s="8"/>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD66" s="8" t="s">
         <v>276</v>
       </c>
@@ -7935,8 +8191,12 @@
       <c r="AF66" s="8"/>
       <c r="AG66" s="8"/>
       <c r="AH66" s="8"/>
-      <c r="AI66" s="8"/>
-      <c r="AJ66" s="6"/>
+      <c r="AI66" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="AJ66" s="6" t="s">
+        <v>557</v>
+      </c>
       <c r="AK66" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/bella-arquine-samontañez.jpg</v>
@@ -7977,7 +8237,7 @@
         <v>356</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
@@ -8086,10 +8346,10 @@
       <c r="AG68" s="8"/>
       <c r="AH68" s="8"/>
       <c r="AI68" s="8" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="AJ68" s="6" t="s">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="AK68" s="7" t="str">
         <f t="shared" si="5"/>
@@ -8140,7 +8400,7 @@
         <v>7</v>
       </c>
       <c r="R69" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S69" s="8" t="s">
         <v>7</v>
@@ -8172,7 +8432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:38">
+    <row r="70" spans="1:38" ht="33.6">
       <c r="A70" s="7">
         <v>65</v>
       </c>
@@ -8198,7 +8458,7 @@
         <v>241</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>368</v>
+        <v>591</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
@@ -8210,7 +8470,7 @@
         <v>13</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R70" s="8" t="s">
         <v>338</v>
@@ -8222,21 +8482,29 @@
       <c r="U70" s="8"/>
       <c r="V70" s="8"/>
       <c r="W70" s="8"/>
-      <c r="X70" s="8"/>
+      <c r="X70" s="8" t="s">
+        <v>592</v>
+      </c>
       <c r="Y70" s="8"/>
       <c r="Z70" s="8"/>
       <c r="AA70" s="8"/>
       <c r="AB70" s="8"/>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="AD70" s="8" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AE70" s="8"/>
       <c r="AF70" s="8"/>
       <c r="AG70" s="8"/>
       <c r="AH70" s="8"/>
-      <c r="AI70" s="8"/>
-      <c r="AJ70" s="6"/>
+      <c r="AI70" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="AJ70" s="6" t="s">
+        <v>594</v>
+      </c>
       <c r="AK70" s="7" t="str">
         <f t="shared" si="5"/>
         <v>/personnel/marilou-villaver.jpg</v>
@@ -8292,10 +8560,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="AI37" r:id="rId1" xr:uid="{AC97A290-C386-4362-9CB5-796D78A2AFBC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A192FB-C3FA-4E4F-AE7B-2268F351F74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FDB805-0840-411E-BF10-C97A694F9C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="610">
   <si>
     <t>order</t>
   </si>
@@ -1312,9 +1312,6 @@
     <t>Values Education 8</t>
   </si>
   <si>
-    <t>School Facilities Assistant Coordinator</t>
-  </si>
-  <si>
     <t>School Sports Assistant Coordinator</t>
   </si>
   <si>
@@ -1838,6 +1835,36 @@
   </si>
   <si>
     <t>Fillipino 11</t>
+  </si>
+  <si>
+    <t>allanraul.aparicio@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>Empowering students to reach their fullest potential.</t>
+  </si>
+  <si>
+    <t>ruth.briones010@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>sharon.bronola001@deped.gov.ph</t>
+  </si>
+  <si>
+    <t>(Senior Bookkeeper)</t>
+  </si>
+  <si>
+    <t>SNED</t>
+  </si>
+  <si>
+    <t>LAC Leader</t>
+  </si>
+  <si>
+    <t>MAPEH 8 &amp; 9</t>
+  </si>
+  <si>
+    <t>I believe that every learner has the potential to succeed when given guidance, encouragement, and meaningful learning experiences. As a teacher, I strive to create an inclusive and engaging environment that promotes curiosity, critical thinking, and respect. My goal is to inspire students to become confident, responsible, and lifelong learners.</t>
+  </si>
+  <si>
+    <t>o everything there is a season, and a time to every purpose under heaven.” — Ecclesiastes 3:1</t>
   </si>
 </sst>
 </file>
@@ -2868,7 +2895,7 @@
     <col min="7" max="7" width="23.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.69921875" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40.796875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="19.296875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="27.09765625" style="10" customWidth="1"/>
     <col min="11" max="11" width="30.69921875" style="10" customWidth="1"/>
     <col min="12" max="12" width="31" style="9" customWidth="1"/>
     <col min="13" max="14" width="28" style="9" customWidth="1"/>
@@ -2945,16 +2972,16 @@
         <v>414</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>462</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>415</v>
@@ -2990,10 +3017,10 @@
         <v>362</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AK1" s="5" t="s">
         <v>5</v>
@@ -3033,7 +3060,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -3074,10 +3101,10 @@
       </c>
       <c r="AH2" s="8"/>
       <c r="AI2" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AJ2" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f t="shared" ref="AK2:AK33" si="2">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C2&amp;" "&amp;B2)," ","-"))&amp;".jpg"</f>
@@ -3122,10 +3149,10 @@
         <v>383</v>
       </c>
       <c r="L3" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>574</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>575</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
@@ -3157,7 +3184,7 @@
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
       <c r="AC3" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>276</v>
@@ -3167,10 +3194,10 @@
       <c r="AG3" s="8"/>
       <c r="AH3" s="8"/>
       <c r="AI3" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
         <v>576</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
-        <v>577</v>
       </c>
       <c r="AK3" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3205,14 +3232,12 @@
       <c r="H4" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>425</v>
+      <c r="I4" s="7" t="s">
+        <v>474</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="7" t="s">
-        <v>475</v>
-      </c>
+      <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -3233,7 +3258,7 @@
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
@@ -3250,10 +3275,10 @@
       <c r="AG4" s="8"/>
       <c r="AH4" s="8"/>
       <c r="AI4" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AJ4" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AK4" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3298,10 +3323,10 @@
         <v>384</v>
       </c>
       <c r="L5" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>426</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>427</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
@@ -3322,13 +3347,13 @@
       <c r="V5" s="8"/>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y5" s="8" t="s">
         <v>422</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
@@ -3343,10 +3368,10 @@
       <c r="AG5" s="8"/>
       <c r="AH5" s="8"/>
       <c r="AI5" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AJ5" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AK5" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3401,20 +3426,20 @@
         <v>14</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
@@ -3430,7 +3455,7 @@
       <c r="AG6" s="8"/>
       <c r="AH6" s="8"/>
       <c r="AI6" s="8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AJ6" s="6"/>
       <c r="AK6" s="7" t="str">
@@ -3476,10 +3501,10 @@
         <v>385</v>
       </c>
       <c r="L7" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>431</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>432</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -3490,17 +3515,17 @@
         <v>14</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
@@ -3516,9 +3541,11 @@
       <c r="AF7" s="8"/>
       <c r="AG7" s="8"/>
       <c r="AH7" s="8"/>
-      <c r="AI7" s="8"/>
+      <c r="AI7" s="8" t="s">
+        <v>600</v>
+      </c>
       <c r="AJ7" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AK7" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3528,7 +3555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" ht="50.4">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -3588,9 +3615,11 @@
       <c r="AG8" s="8"/>
       <c r="AH8" s="8"/>
       <c r="AI8" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="AJ8" s="6"/>
+        <v>513</v>
+      </c>
+      <c r="AJ8" s="6" t="s">
+        <v>609</v>
+      </c>
       <c r="AK8" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/niña-kristine-ayos.jpg</v>
@@ -3625,7 +3654,7 @@
         <v>268</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -3698,12 +3727,12 @@
         <v>243</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -3715,17 +3744,17 @@
         <v>16</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
@@ -3786,10 +3815,10 @@
         <v>386</v>
       </c>
       <c r="L11" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>435</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>436</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -3810,7 +3839,7 @@
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
@@ -3827,10 +3856,10 @@
       <c r="AG11" s="8"/>
       <c r="AH11" s="8"/>
       <c r="AI11" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AJ11" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AK11" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3875,7 +3904,7 @@
         <v>387</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -3897,7 +3926,7 @@
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
@@ -3914,10 +3943,10 @@
       <c r="AG12" s="8"/>
       <c r="AH12" s="8"/>
       <c r="AI12" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AJ12" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AK12" s="7" t="str">
         <f t="shared" si="2"/>
@@ -3962,13 +3991,13 @@
         <v>410</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="8" t="s">
@@ -3988,16 +4017,16 @@
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="Y13" s="8" t="s">
         <v>441</v>
-      </c>
-      <c r="Y13" s="8" t="s">
-        <v>442</v>
       </c>
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AD13" s="8" t="s">
         <v>276</v>
@@ -4007,10 +4036,10 @@
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AJ13" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AK13" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4046,12 +4075,12 @@
         <v>15</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
@@ -4073,7 +4102,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
@@ -4090,10 +4119,10 @@
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
       <c r="AI14" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AJ14" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AK14" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4138,7 +4167,7 @@
         <v>388</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -4160,16 +4189,16 @@
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AD15" s="8" t="s">
         <v>276</v>
@@ -4180,7 +4209,7 @@
       <c r="AH15" s="8"/>
       <c r="AI15" s="8"/>
       <c r="AJ15" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AK15" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4221,13 +4250,13 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="8" t="s">
@@ -4247,10 +4276,10 @@
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="Y16" s="8" t="s">
         <v>451</v>
-      </c>
-      <c r="Y16" s="8" t="s">
-        <v>452</v>
       </c>
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
@@ -4269,7 +4298,7 @@
       <c r="AH16" s="8"/>
       <c r="AI16" s="8"/>
       <c r="AJ16" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AK16" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4312,7 +4341,7 @@
         <v>406</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
@@ -4334,16 +4363,16 @@
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="Y17" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AD17" s="8" t="s">
         <v>276</v>
@@ -4352,8 +4381,12 @@
       <c r="AF17" s="8"/>
       <c r="AG17" s="8"/>
       <c r="AH17" s="8"/>
-      <c r="AI17" s="8"/>
-      <c r="AJ17" s="6"/>
+      <c r="AI17" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="AJ17" s="6" t="s">
+        <v>601</v>
+      </c>
       <c r="AK17" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/ruth-briones.jpg</v>
@@ -4407,13 +4440,13 @@
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Y18" s="8" t="s">
         <v>424</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
@@ -4423,9 +4456,11 @@
       <c r="AF18" s="8"/>
       <c r="AG18" s="8"/>
       <c r="AH18" s="8"/>
-      <c r="AI18" s="8"/>
+      <c r="AI18" s="8" t="s">
+        <v>603</v>
+      </c>
       <c r="AJ18" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AK18" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4458,14 +4493,16 @@
         <v>Joan A. Cabalda</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>372</v>
+        <v>604</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
-      <c r="L19" s="7"/>
+      <c r="L19" s="7" t="s">
+        <v>372</v>
+      </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -4497,10 +4534,10 @@
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AJ19" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AK19" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4540,8 +4577,12 @@
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
+      <c r="L20" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>606</v>
+      </c>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
       <c r="P20" s="8" t="s">
@@ -4560,13 +4601,19 @@
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
+      <c r="X20" s="8" t="s">
+        <v>607</v>
+      </c>
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
+      <c r="AC20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD20" s="8" t="s">
+        <v>365</v>
+      </c>
       <c r="AE20" s="8"/>
       <c r="AF20" s="8"/>
       <c r="AG20" s="8">
@@ -4574,10 +4621,10 @@
       </c>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AJ20" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AK20" s="7" t="str">
         <f t="shared" si="2"/>
@@ -4664,7 +4711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:38" ht="168">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -4699,7 +4746,7 @@
         <v>390</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -4736,9 +4783,11 @@
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
       <c r="AI22" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="AJ22" s="6"/>
+        <v>529</v>
+      </c>
+      <c r="AJ22" s="6" t="s">
+        <v>608</v>
+      </c>
       <c r="AK22" s="7" t="str">
         <f t="shared" si="2"/>
         <v>/personnel/marilou-cabriana.jpg</v>
@@ -4752,10 +4801,10 @@
         <v>68</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>486</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>487</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="str">
@@ -4771,7 +4820,7 @@
         <v>266</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
@@ -4844,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
@@ -4862,7 +4911,7 @@
         <v>377</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
@@ -4917,10 +4966,10 @@
         <v>248</v>
       </c>
       <c r="I25" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>598</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>599</v>
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="7"/>
@@ -4944,7 +4993,7 @@
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
       <c r="X25" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
@@ -4959,7 +5008,7 @@
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AJ25" s="6"/>
       <c r="AK25" s="7" t="str">
@@ -5034,10 +5083,10 @@
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AJ26" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AK26" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5116,7 +5165,7 @@
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
       <c r="AJ27" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AK27" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5193,7 +5242,7 @@
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AK28" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5344,7 +5393,7 @@
       <c r="AG30" s="8"/>
       <c r="AH30" s="8"/>
       <c r="AI30" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AJ30" s="6"/>
       <c r="AK30" s="7" t="str">
@@ -5381,7 +5430,7 @@
         <v>268</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -5533,7 +5582,7 @@
         <v>15</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -5552,13 +5601,13 @@
       </c>
       <c r="S33" s="8"/>
       <c r="T33" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="U33" s="8"/>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
       <c r="X33" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Y33" s="8"/>
       <c r="Z33" s="8"/>
@@ -5575,10 +5624,10 @@
       <c r="AG33" s="8"/>
       <c r="AH33" s="8"/>
       <c r="AI33" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AJ33" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AK33" s="7" t="str">
         <f t="shared" si="2"/>
@@ -5654,10 +5703,10 @@
       <c r="AG34" s="8"/>
       <c r="AH34" s="8"/>
       <c r="AI34" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AJ34" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AK34" s="7" t="str">
         <f t="shared" ref="AK34:AK70" si="5">"/personnel/"&amp;LOWER(SUBSTITUTE(TRIM(C34&amp;" "&amp;B34)," ","-"))&amp;".jpg"</f>
@@ -5708,17 +5757,17 @@
         <v>14</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
       <c r="V35" s="8"/>
       <c r="W35" s="8"/>
       <c r="X35" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
@@ -5797,13 +5846,13 @@
       <c r="V36" s="8"/>
       <c r="W36" s="8"/>
       <c r="X36" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="Y36" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="Y36" s="8" t="s">
+      <c r="Z36" s="8" t="s">
         <v>586</v>
-      </c>
-      <c r="Z36" s="8" t="s">
-        <v>587</v>
       </c>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
@@ -5818,10 +5867,10 @@
       </c>
       <c r="AH36" s="8"/>
       <c r="AI36" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AJ36" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AK36" s="7" t="str">
         <f t="shared" si="5"/>
@@ -5831,7 +5880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="134.4">
+    <row r="37" spans="1:38" ht="151.19999999999999">
       <c r="A37" s="7">
         <v>33</v>
       </c>
@@ -5872,17 +5921,17 @@
         <v>16</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
       <c r="V37" s="8"/>
       <c r="W37" s="8"/>
       <c r="X37" s="8" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Y37" s="8"/>
       <c r="Z37" s="8"/>
@@ -5897,10 +5946,10 @@
       <c r="AG37" s="8"/>
       <c r="AH37" s="8"/>
       <c r="AI37" s="12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AJ37" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AK37" s="7" t="str">
         <f t="shared" si="5"/>
@@ -5945,10 +5994,10 @@
         <v>394</v>
       </c>
       <c r="L38" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="M38" s="7" t="s">
         <v>595</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>596</v>
       </c>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
@@ -5982,10 +6031,10 @@
       <c r="AG38" s="8"/>
       <c r="AH38" s="8"/>
       <c r="AI38" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AJ38" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AK38" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6030,7 +6079,7 @@
         <v>395</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
@@ -6069,10 +6118,10 @@
       <c r="AG39" s="8"/>
       <c r="AH39" s="8"/>
       <c r="AI39" s="8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AJ39" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AK39" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6208,7 +6257,7 @@
       <c r="V41" s="8"/>
       <c r="W41" s="8"/>
       <c r="X41" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Y41" s="8"/>
       <c r="Z41" s="8"/>
@@ -6225,7 +6274,7 @@
       <c r="AG41" s="8"/>
       <c r="AH41" s="8"/>
       <c r="AI41" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AJ41" s="6"/>
       <c r="AK41" s="7" t="str">
@@ -6304,10 +6353,10 @@
       <c r="AG42" s="8"/>
       <c r="AH42" s="8"/>
       <c r="AI42" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AJ42" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AK42" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6364,7 +6413,7 @@
         <v>340</v>
       </c>
       <c r="T43" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="U43" s="8"/>
       <c r="V43" s="8"/>
@@ -6383,7 +6432,7 @@
       <c r="AG43" s="8"/>
       <c r="AH43" s="8"/>
       <c r="AI43" s="8" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AJ43" s="6"/>
       <c r="AK43" s="7" t="str">
@@ -6458,10 +6507,10 @@
       <c r="AG44" s="8"/>
       <c r="AH44" s="8"/>
       <c r="AI44" s="8" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AJ44" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AK44" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6495,7 +6544,7 @@
         <v>15</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
@@ -6534,7 +6583,7 @@
       <c r="AH45" s="8"/>
       <c r="AI45" s="8"/>
       <c r="AJ45" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AK45" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6570,15 +6619,15 @@
         <v>269</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="L46" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -6614,7 +6663,7 @@
       <c r="AG46" s="8"/>
       <c r="AH46" s="8"/>
       <c r="AI46" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AJ46" s="6"/>
       <c r="AK46" s="7" t="str">
@@ -6670,17 +6719,17 @@
         <v>14</v>
       </c>
       <c r="R47" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
       <c r="V47" s="8"/>
       <c r="W47" s="8"/>
       <c r="X47" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
@@ -6695,10 +6744,10 @@
       <c r="AG47" s="8"/>
       <c r="AH47" s="8"/>
       <c r="AI47" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AJ47" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AK47" s="7" t="str">
         <f t="shared" si="5"/>
@@ -6861,10 +6910,10 @@
         <v>69</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="str">
@@ -6880,7 +6929,7 @@
         <v>266</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
@@ -7128,7 +7177,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="8"/>
       <c r="X53" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
@@ -7145,10 +7194,10 @@
       <c r="AG53" s="8"/>
       <c r="AH53" s="8"/>
       <c r="AI53" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AJ53" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK53" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7270,7 +7319,7 @@
         <v>402</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
@@ -7292,7 +7341,7 @@
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
       <c r="X55" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Y55" s="8"/>
       <c r="Z55" s="8"/>
@@ -7307,10 +7356,10 @@
       <c r="AG55" s="8"/>
       <c r="AH55" s="8"/>
       <c r="AI55" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AJ55" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AK55" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7365,17 +7414,17 @@
         <v>14</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T56" s="8"/>
       <c r="U56" s="8"/>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
       <c r="X56" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
@@ -7390,10 +7439,10 @@
       <c r="AG56" s="8"/>
       <c r="AH56" s="8"/>
       <c r="AI56" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AJ56" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AK56" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7675,18 +7724,18 @@
       <c r="V60" s="8"/>
       <c r="W60" s="8"/>
       <c r="X60" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="Y60" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="Y60" s="8" t="s">
+      <c r="Z60" s="8" t="s">
         <v>570</v>
-      </c>
-      <c r="Z60" s="8" t="s">
-        <v>571</v>
       </c>
       <c r="AA60" s="8"/>
       <c r="AB60" s="8"/>
       <c r="AC60" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AD60" s="8" t="s">
         <v>379</v>
@@ -7696,10 +7745,10 @@
       <c r="AG60" s="8"/>
       <c r="AH60" s="8"/>
       <c r="AI60" s="8" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AJ60" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AK60" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7735,7 +7784,7 @@
         <v>241</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
@@ -7760,7 +7809,7 @@
       <c r="V61" s="8"/>
       <c r="W61" s="8"/>
       <c r="X61" s="8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="Y61" s="8"/>
       <c r="Z61" s="8"/>
@@ -7777,10 +7826,10 @@
       <c r="AG61" s="8"/>
       <c r="AH61" s="8"/>
       <c r="AI61" s="8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AJ61" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AK61" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7831,17 +7880,17 @@
         <v>16</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
       <c r="V62" s="8"/>
       <c r="W62" s="8"/>
       <c r="X62" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y62" s="8"/>
       <c r="Z62" s="8"/>
@@ -7858,10 +7907,10 @@
       <c r="AG62" s="8"/>
       <c r="AH62" s="8"/>
       <c r="AI62" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AJ62" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AK62" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7902,7 +7951,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
       <c r="L63" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
@@ -7924,7 +7973,7 @@
       <c r="V63" s="8"/>
       <c r="W63" s="8"/>
       <c r="X63" s="8" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Y63" s="8"/>
       <c r="Z63" s="8"/>
@@ -7943,10 +7992,10 @@
       </c>
       <c r="AH63" s="8"/>
       <c r="AI63" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AJ63" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AK63" s="7" t="str">
         <f t="shared" si="5"/>
@@ -7991,7 +8040,7 @@
         <v>404</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M64" s="7"/>
       <c r="N64" s="7"/>
@@ -8030,10 +8079,10 @@
       <c r="AG64" s="8"/>
       <c r="AH64" s="8"/>
       <c r="AI64" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AJ64" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AK64" s="7" t="str">
         <f t="shared" si="5"/>
@@ -8090,13 +8139,13 @@
         <v>338</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="U65" s="8"/>
       <c r="V65" s="8"/>
       <c r="W65" s="8"/>
       <c r="X65" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
@@ -8155,7 +8204,7 @@
         <v>405</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
@@ -8167,10 +8216,10 @@
         <v>16</v>
       </c>
       <c r="R66" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S66" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T66" s="8"/>
       <c r="U66" s="8"/>
@@ -8192,10 +8241,10 @@
       <c r="AG66" s="8"/>
       <c r="AH66" s="8"/>
       <c r="AI66" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="AJ66" s="6" t="s">
         <v>556</v>
-      </c>
-      <c r="AJ66" s="6" t="s">
-        <v>557</v>
       </c>
       <c r="AK66" s="7" t="str">
         <f t="shared" si="5"/>
@@ -8346,10 +8395,10 @@
       <c r="AG68" s="8"/>
       <c r="AH68" s="8"/>
       <c r="AI68" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AJ68" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AK68" s="7" t="str">
         <f t="shared" si="5"/>
@@ -8458,7 +8507,7 @@
         <v>241</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
@@ -8483,7 +8532,7 @@
       <c r="V70" s="8"/>
       <c r="W70" s="8"/>
       <c r="X70" s="8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Y70" s="8"/>
       <c r="Z70" s="8"/>
@@ -8500,10 +8549,10 @@
       <c r="AG70" s="8"/>
       <c r="AH70" s="8"/>
       <c r="AI70" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="AJ70" s="6" t="s">
         <v>593</v>
-      </c>
-      <c r="AJ70" s="6" t="s">
-        <v>594</v>
       </c>
       <c r="AK70" s="7" t="str">
         <f t="shared" si="5"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FDB805-0840-411E-BF10-C97A694F9C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22944" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>

--- a/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
+++ b/public/data/Tabunoc_NHS_Personnel_Roster_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\tabunoc-nhs-website\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FDB805-0840-411E-BF10-C97A694F9C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49573153-BB3D-4ABC-8E25-F9BA397E93F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22944" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personnel" sheetId="1" r:id="rId1"/>
@@ -1864,7 +1864,7 @@
     <t>I believe that every learner has the potential to succeed when given guidance, encouragement, and meaningful learning experiences. As a teacher, I strive to create an inclusive and engaging environment that promotes curiosity, critical thinking, and respect. My goal is to inspire students to become confident, responsible, and lifelong learners.</t>
   </si>
   <si>
-    <t>o everything there is a season, and a time to every purpose under heaven.” — Ecclesiastes 3:1</t>
+    <t>To everything there is a season, and a time to every purpose under heaven.” — Ecclesiastes 3:1</t>
   </si>
 </sst>
 </file>
